--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="96">
   <si>
     <t>date</t>
   </si>
@@ -133,7 +133,7 @@
     <t>08/29/2026</t>
   </si>
   <si>
-    <t>Carlos Rodon</t>
+    <t>Jake Bennett</t>
   </si>
   <si>
     <t>Boston Red Sox @ New York Yankees</t>
@@ -142,75 +142,120 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>Max Fried</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
+    <t>Blake Snell</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>6-7</t>
   </si>
   <si>
     <t>Keider Montero</t>
   </si>
   <si>
-    <t>Los Angeles Dodgers @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Blake Snell</t>
+    <t>Erick Fedde</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago Cubs</t>
   </si>
   <si>
     <t>Kevin Gausman</t>
   </si>
   <si>
-    <t>Cincinnati Reds @ Chicago Cubs</t>
-  </si>
-  <si>
     <t>&gt;=7</t>
   </si>
   <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>Jose Soriano</t>
+    <t>José Soriano</t>
   </si>
   <si>
     <t>Seattle Mariners @ Toronto Blue Jays</t>
   </si>
   <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>team_season_vs_hand</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Washington Nationals</t>
+  </si>
+  <si>
     <t>Cade Cavalli</t>
   </si>
   <si>
-    <t>Miami Marlins @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
+    <t>Daniel Lynch IV</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Cleveland Guardians</t>
   </si>
   <si>
     <t>Foster Griffin</t>
   </si>
   <si>
-    <t>Kansas City Royals @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Daniel Lynch IV</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
+    <t>Bennett Sousa</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Mets</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
   </si>
   <si>
     <t>Nolan McLean</t>
   </si>
   <si>
-    <t>Houston Astros @ New York Mets</t>
-  </si>
-  <si>
     <t>Walker Buehler</t>
   </si>
   <si>
@@ -220,6 +265,15 @@
     <t>Nick Martinez</t>
   </si>
   <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
     <t>Cal Quantrill</t>
   </si>
   <si>
@@ -229,55 +283,22 @@
     <t>Shane Drohan</t>
   </si>
   <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Athletics</t>
+  </si>
+  <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Los Angeles Angels</t>
+  </si>
+  <si>
     <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Cristopher Sanchez</t>
-  </si>
-  <si>
-    <t>Max Fried</t>
-  </si>
-  <si>
-    <t>Erick Fedde</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>Bennett Sousa</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Athletics</t>
   </si>
 </sst>
 </file>
@@ -658,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM28"/>
+  <dimension ref="A1:AM31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -791,13 +812,13 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-108</v>
+        <v>-116</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -809,7 +830,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -821,43 +842,43 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>0.2544</v>
+        <v>0.1903</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="P2">
-        <v>4.2</v>
+        <v>4.02</v>
       </c>
       <c r="Q2">
-        <v>0.2424</v>
+        <v>0.2033</v>
       </c>
       <c r="R2">
-        <v>0.331</v>
+        <v>0.381</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1883</v>
+        <v>0.2529</v>
       </c>
       <c r="U2">
-        <v>0.1838</v>
+        <v>0.2729</v>
       </c>
       <c r="V2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2101</v>
+        <v>0.2486</v>
       </c>
       <c r="X2">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y2">
-        <v>0.9769</v>
+        <v>1.0351</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -866,22 +887,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.49</v>
+        <v>5.5</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2504</v>
+        <v>0.1953</v>
       </c>
       <c r="AG2">
-        <v>0.8855</v>
+        <v>1.1592</v>
       </c>
       <c r="AH2">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>4.73</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -892,13 +913,13 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
-        <v>-116</v>
+        <v>-108</v>
       </c>
       <c r="E3">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -910,7 +931,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -922,43 +943,43 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>0.1903</v>
+        <v>0.2544</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="P3">
-        <v>4.02</v>
+        <v>4.2</v>
       </c>
       <c r="Q3">
-        <v>0.2033</v>
+        <v>0.2424</v>
       </c>
       <c r="R3">
-        <v>0.381</v>
+        <v>0.331</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2363</v>
+        <v>0.1914</v>
       </c>
       <c r="U3">
-        <v>0.2475</v>
+        <v>0.1846</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2486</v>
+        <v>0.2101</v>
       </c>
       <c r="X3">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y3">
-        <v>0.9866</v>
+        <v>0.9697</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -967,22 +988,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.02</v>
+        <v>4.42</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1953</v>
+        <v>0.2504</v>
       </c>
       <c r="AG3">
-        <v>1.1114</v>
+        <v>0.8775</v>
       </c>
       <c r="AH3">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM3">
-        <v>5.26</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -992,26 +1013,17 @@
       <c r="B4" t="s">
         <v>47</v>
       </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-      <c r="D4">
-        <v>-108</v>
-      </c>
-      <c r="E4">
-        <v>-115</v>
-      </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>824230</v>
+        <v>823501</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1020,46 +1032,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.1664</v>
+        <v>0.238</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q4">
-        <v>0.0948</v>
+        <v>0.3152</v>
       </c>
       <c r="R4">
-        <v>0.367</v>
+        <v>0.315</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T4">
-        <v>0.2397</v>
+        <v>0.1883</v>
       </c>
       <c r="U4">
-        <v>0.2051</v>
+        <v>0.1838</v>
       </c>
       <c r="V4">
         <v>8</v>
       </c>
       <c r="W4">
-        <v>0.2062</v>
+        <v>0.2101</v>
       </c>
       <c r="X4">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y4">
-        <v>1.0032</v>
+        <v>0.9794</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1068,22 +1080,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.64</v>
+        <v>4.91</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1414</v>
+        <v>0.2623</v>
       </c>
       <c r="AG4">
-        <v>1.1272</v>
+        <v>0.8631</v>
       </c>
       <c r="AH4">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM4">
-        <v>3.88</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1103,7 +1115,7 @@
         <v>-105</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>824230</v>
@@ -1145,22 +1157,22 @@
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1843</v>
+        <v>0.2179</v>
       </c>
       <c r="U5">
-        <v>0.2012</v>
+        <v>0.211</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>0.2294</v>
       </c>
       <c r="X5">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y5">
-        <v>0.9731</v>
+        <v>0.9742</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1169,22 +1181,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.48</v>
+        <v>6.33</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF5">
         <v>0.2989</v>
       </c>
       <c r="AG5">
-        <v>0.8668</v>
+        <v>0.9989</v>
       </c>
       <c r="AH5">
-        <v>0.24</v>
+        <v>-0.55</v>
       </c>
       <c r="AM5">
-        <v>5.72</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1192,28 +1204,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6">
+        <v>3.5</v>
+      </c>
+      <c r="D6">
+        <v>-108</v>
+      </c>
+      <c r="E6">
+        <v>-115</v>
+      </c>
+      <c r="F6" t="s">
         <v>50</v>
       </c>
-      <c r="C6">
-        <v>6.5</v>
-      </c>
-      <c r="D6">
-        <v>112</v>
-      </c>
-      <c r="E6">
-        <v>-130</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
       <c r="G6">
-        <v>824637</v>
+        <v>824230</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1225,43 +1237,43 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>0.2354</v>
+        <v>0.1664</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P6">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>0.2203</v>
+        <v>0.0948</v>
       </c>
       <c r="R6">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2644</v>
+        <v>0.2129</v>
       </c>
       <c r="U6">
-        <v>0.2658</v>
+        <v>0.2125</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2542</v>
+        <v>0.2062</v>
       </c>
       <c r="X6">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y6">
-        <v>1.0806</v>
+        <v>0.991</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1270,22 +1282,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>7.24</v>
+        <v>3.11</v>
       </c>
       <c r="AE6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2298</v>
+        <v>0.1414</v>
       </c>
       <c r="AG6">
-        <v>1.2432</v>
+        <v>0.9759</v>
       </c>
       <c r="AH6">
-        <v>-0.95</v>
+        <v>0.22</v>
       </c>
       <c r="AM6">
-        <v>6.29</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1295,26 +1307,17 @@
       <c r="B7" t="s">
         <v>53</v>
       </c>
-      <c r="C7">
-        <v>3.5</v>
-      </c>
-      <c r="D7">
-        <v>-156</v>
-      </c>
-      <c r="E7">
-        <v>126</v>
-      </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>824637</v>
+        <v>823665</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1323,46 +1326,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0.181</v>
+        <v>0.1641</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="P7">
         <v>4.33</v>
       </c>
       <c r="Q7">
-        <v>0.16</v>
+        <v>0.2043</v>
       </c>
       <c r="R7">
-        <v>0.385</v>
+        <v>0.317</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2097</v>
+        <v>0.2021</v>
       </c>
       <c r="U7">
-        <v>0.206</v>
+        <v>0.1907</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2192</v>
+        <v>0.2072</v>
       </c>
       <c r="X7">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y7">
-        <v>0.9886</v>
+        <v>0.936</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1371,22 +1374,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.93</v>
+        <v>3.19</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.1729</v>
+        <v>0.1768</v>
       </c>
       <c r="AG7">
-        <v>0.9861</v>
+        <v>0.9264</v>
       </c>
       <c r="AH7">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM7">
-        <v>4.17</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1394,28 +1397,19 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
         <v>54</v>
       </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-      <c r="D8">
-        <v>102</v>
-      </c>
-      <c r="E8">
-        <v>-130</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
       <c r="G8">
-        <v>822770</v>
+        <v>823665</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1424,46 +1418,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>0.2371</v>
+        <v>0.1619</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="P8">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="Q8">
-        <v>0.1875</v>
+        <v>0.1217</v>
       </c>
       <c r="R8">
-        <v>0.359</v>
+        <v>0.365</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2296</v>
+        <v>0.2522</v>
       </c>
       <c r="U8">
-        <v>0.2262</v>
+        <v>0.2525</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2259</v>
+        <v>0.2363</v>
       </c>
       <c r="X8">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y8">
-        <v>1.0018</v>
+        <v>1.0323</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1472,22 +1466,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>5.5</v>
+        <v>4.02</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2193</v>
+        <v>0.1473</v>
       </c>
       <c r="AG8">
-        <v>1.0796</v>
+        <v>1.1561</v>
       </c>
       <c r="AH8">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>5.74</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1497,74 +1491,65 @@
       <c r="B9" t="s">
         <v>56</v>
       </c>
-      <c r="C9">
-        <v>6.5</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>-128</v>
-      </c>
       <c r="F9" t="s">
         <v>57</v>
       </c>
       <c r="G9">
-        <v>822690</v>
+        <v>823011</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I9">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>0.2708</v>
+        <v>0.25</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q9">
-        <v>0.3223</v>
+        <v>0.2766</v>
       </c>
       <c r="R9">
-        <v>0.377</v>
+        <v>0.19</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2086</v>
+        <v>0.2511</v>
       </c>
       <c r="U9">
-        <v>0.1957</v>
+        <v>0.2169</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2107</v>
+        <v>0.2158</v>
       </c>
       <c r="X9">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y9">
-        <v>0.9726</v>
+        <v>0.8961</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1573,22 +1558,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>6.17</v>
+        <v>2.52</v>
       </c>
       <c r="AE9" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2902</v>
+        <v>0.2551</v>
       </c>
       <c r="AG9">
-        <v>0.9812</v>
+        <v>1.1509</v>
       </c>
       <c r="AH9">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
       <c r="AM9">
-        <v>5.59</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1598,26 +1583,17 @@
       <c r="B10" t="s">
         <v>59</v>
       </c>
-      <c r="C10">
-        <v>4.5</v>
-      </c>
-      <c r="D10">
-        <v>118</v>
-      </c>
-      <c r="E10">
-        <v>-150</v>
-      </c>
       <c r="F10" t="s">
         <v>57</v>
       </c>
       <c r="G10">
-        <v>822690</v>
+        <v>823011</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1626,46 +1602,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.181</v>
+        <v>0.2166</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="P10">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="Q10">
-        <v>0.1667</v>
+        <v>0.2727</v>
       </c>
       <c r="R10">
-        <v>0.398</v>
+        <v>0.331</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2298</v>
+        <v>0.2509</v>
       </c>
       <c r="U10">
-        <v>0.2342</v>
+        <v>0.2463</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2064</v>
+        <v>0.2373</v>
       </c>
       <c r="X10">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y10">
-        <v>1.0068</v>
+        <v>1.0293</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1674,22 +1650,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>5.16</v>
+        <v>5.91</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1753</v>
+        <v>0.2352</v>
       </c>
       <c r="AG10">
-        <v>1.0808</v>
+        <v>1.1501</v>
       </c>
       <c r="AH10">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM10">
-        <v>5.4</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1700,25 +1676,25 @@
         <v>60</v>
       </c>
       <c r="C11">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D11">
-        <v>-119</v>
+        <v>-156</v>
       </c>
       <c r="E11">
-        <v>-108</v>
+        <v>126</v>
       </c>
       <c r="F11" t="s">
         <v>61</v>
       </c>
       <c r="G11">
-        <v>824392</v>
+        <v>824637</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1727,25 +1703,25 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>0.2209</v>
+        <v>0.181</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="P11">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
-        <v>0.1964</v>
+        <v>0.16</v>
       </c>
       <c r="R11">
-        <v>0.359</v>
+        <v>0.385</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1754,19 +1730,19 @@
         <v>0.1662</v>
       </c>
       <c r="U11">
-        <v>0.1815</v>
+        <v>0.1874</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2139</v>
+        <v>0.2192</v>
       </c>
       <c r="X11">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y11">
-        <v>0.9746</v>
+        <v>0.8905</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1775,22 +1751,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2121</v>
+        <v>0.1729</v>
       </c>
       <c r="AG11">
-        <v>0.7813</v>
+        <v>0.762</v>
       </c>
       <c r="AH11">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM11">
-        <v>4.04</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1801,73 +1777,73 @@
         <v>62</v>
       </c>
       <c r="C12">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="D12">
-        <v>-120</v>
+        <v>112</v>
       </c>
       <c r="E12">
-        <v>-107</v>
+        <v>-130</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
       </c>
       <c r="G12">
-        <v>824392</v>
+        <v>824637</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>0.183</v>
+        <v>0.2354</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="P12">
-        <v>4.03</v>
+        <v>4.21</v>
       </c>
       <c r="Q12">
-        <v>0.1538</v>
+        <v>0.2203</v>
       </c>
       <c r="R12">
-        <v>0.206</v>
+        <v>0.371</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2135</v>
+        <v>0.2556</v>
       </c>
       <c r="U12">
-        <v>0.1892</v>
+        <v>0.2652</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2241</v>
+        <v>0.2542</v>
       </c>
       <c r="X12">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y12">
-        <v>0.959</v>
+        <v>1.12</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1876,22 +1852,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.06</v>
+        <v>7.07</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="AF12">
-        <v>0.177</v>
+        <v>0.2298</v>
       </c>
       <c r="AG12">
-        <v>1.0041</v>
+        <v>1.1717</v>
       </c>
       <c r="AH12">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>2.3</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1905,22 +1881,22 @@
         <v>5.5</v>
       </c>
       <c r="D13">
-        <v>-148</v>
+        <v>102</v>
       </c>
       <c r="E13">
-        <v>116</v>
+        <v>-130</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
       </c>
       <c r="G13">
-        <v>823582</v>
+        <v>822770</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1929,46 +1905,46 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>0.2718</v>
+        <v>0.2371</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="P13">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="Q13">
-        <v>0.2131</v>
+        <v>0.1875</v>
       </c>
       <c r="R13">
-        <v>0.379</v>
+        <v>0.359</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2162</v>
+        <v>0.2675</v>
       </c>
       <c r="U13">
-        <v>0.2071</v>
+        <v>0.233</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2191</v>
+        <v>0.2259</v>
       </c>
       <c r="X13">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y13">
-        <v>0.9893</v>
+        <v>0.9726</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1977,22 +1953,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>5.97</v>
+        <v>6.07</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF13">
-        <v>0.2496</v>
+        <v>0.2193</v>
       </c>
       <c r="AG13">
-        <v>1.0166</v>
+        <v>1.2262</v>
       </c>
       <c r="AH13">
-        <v>0.24</v>
+        <v>-0.55</v>
       </c>
       <c r="AM13">
-        <v>6.21</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2002,26 +1978,17 @@
       <c r="B14" t="s">
         <v>66</v>
       </c>
-      <c r="C14">
-        <v>3.5</v>
-      </c>
-      <c r="D14">
-        <v>106</v>
-      </c>
-      <c r="E14">
-        <v>-122</v>
-      </c>
       <c r="F14" t="s">
         <v>67</v>
       </c>
       <c r="G14">
-        <v>822936</v>
+        <v>823177</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2030,46 +1997,40 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>0.2007</v>
+        <v>0.1492</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="P14">
-        <v>4.26</v>
+        <v>4.38</v>
       </c>
       <c r="Q14">
-        <v>0.1635</v>
+        <v>0.1453</v>
       </c>
       <c r="R14">
-        <v>0.342</v>
+        <v>0.369</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
-      </c>
-      <c r="T14">
-        <v>0.1566</v>
-      </c>
-      <c r="U14">
-        <v>0.1504</v>
+        <v>68</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>0.1865</v>
+        <v>0.2049</v>
       </c>
       <c r="X14">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y14">
-        <v>0.8976</v>
+        <v>0.9806</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2078,22 +2039,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>2.57</v>
+        <v>3.34</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.188</v>
+        <v>0.1477</v>
       </c>
       <c r="AG14">
-        <v>0.7363</v>
+        <v>0.9377</v>
       </c>
       <c r="AH14">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM14">
-        <v>2.81</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2101,28 +2062,19 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15">
-        <v>3.5</v>
-      </c>
-      <c r="D15">
-        <v>-110</v>
-      </c>
-      <c r="E15">
-        <v>-111</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
         <v>67</v>
       </c>
       <c r="G15">
-        <v>822936</v>
+        <v>823176</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="I15">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2131,46 +2083,40 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>0.1467</v>
+        <v>0.1591</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="P15">
-        <v>4.02</v>
+        <v>4.44</v>
       </c>
       <c r="Q15">
-        <v>0.1667</v>
+        <v>0.1818</v>
       </c>
       <c r="R15">
-        <v>0.375</v>
+        <v>0.331</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
-      </c>
-      <c r="T15">
-        <v>0.1905</v>
-      </c>
-      <c r="U15">
-        <v>0.1926</v>
+        <v>68</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>0.2154</v>
+        <v>0.2353</v>
       </c>
       <c r="X15">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y15">
-        <v>0.9999</v>
+        <v>1.0233</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2179,22 +2125,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1542</v>
+        <v>0.1666</v>
       </c>
       <c r="AG15">
-        <v>0.8958</v>
+        <v>1.0398</v>
       </c>
       <c r="AH15">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM15">
-        <v>3.52</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2202,28 +2148,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C16">
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E16">
-        <v>-170</v>
+        <v>-150</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G16">
-        <v>823741</v>
+        <v>822690</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2235,43 +2181,43 @@
         <v>2</v>
       </c>
       <c r="M16">
-        <v>0.1729</v>
+        <v>0.181</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="P16">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="Q16">
-        <v>0.2456</v>
+        <v>0.1667</v>
       </c>
       <c r="R16">
-        <v>0.363</v>
+        <v>0.398</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T16">
-        <v>0.2081</v>
+        <v>0.2298</v>
       </c>
       <c r="U16">
-        <v>0.2138</v>
+        <v>0.2342</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2135</v>
+        <v>0.2064</v>
       </c>
       <c r="X16">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y16">
-        <v>0.9961</v>
+        <v>1.0076</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2280,22 +2226,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.05</v>
+        <v>5.03</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.1988</v>
+        <v>0.1753</v>
       </c>
       <c r="AG16">
-        <v>0.9787</v>
+        <v>1.0535</v>
       </c>
       <c r="AH16">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM16">
-        <v>4.29</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2303,28 +2249,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C17">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D17">
-        <v>-113</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>-113</v>
+        <v>-128</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G17">
-        <v>823741</v>
+        <v>822690</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2336,43 +2282,43 @@
         <v>2</v>
       </c>
       <c r="M17">
-        <v>0.2342</v>
+        <v>0.2708</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P17">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>0.2288</v>
+        <v>0.3223</v>
       </c>
       <c r="R17">
-        <v>0.371</v>
+        <v>0.377</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T17">
-        <v>0.2381</v>
+        <v>0.2086</v>
       </c>
       <c r="U17">
-        <v>0.2401</v>
+        <v>0.1957</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2412</v>
+        <v>0.2107</v>
       </c>
       <c r="X17">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y17">
-        <v>1.0385</v>
+        <v>0.9719</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2381,22 +2327,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF17">
-        <v>0.2322</v>
+        <v>0.2902</v>
       </c>
       <c r="AG17">
-        <v>1.1198</v>
+        <v>0.9564</v>
       </c>
       <c r="AH17">
-        <v>0.24</v>
+        <v>-0.55</v>
       </c>
       <c r="AM17">
-        <v>6.21</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2404,76 +2350,76 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D18">
-        <v>102</v>
+        <v>-120</v>
       </c>
       <c r="E18">
-        <v>-130</v>
+        <v>-107</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G18">
-        <v>823986</v>
+        <v>824392</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I18">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>0.1695</v>
+        <v>0.183</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="P18">
-        <v>4.38</v>
+        <v>4.03</v>
       </c>
       <c r="Q18">
-        <v>0.1509</v>
+        <v>0.1538</v>
       </c>
       <c r="R18">
-        <v>0.346</v>
+        <v>0.206</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.1509</v>
+        <v>0.1994</v>
       </c>
       <c r="U18">
-        <v>0.1533</v>
+        <v>0.1738</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2218</v>
+        <v>0.2241</v>
       </c>
       <c r="X18">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y18">
-        <v>0.9977</v>
+        <v>0.88</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2482,22 +2428,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.1631</v>
+        <v>0.177</v>
       </c>
       <c r="AG18">
-        <v>0.7096</v>
+        <v>0.9139</v>
       </c>
       <c r="AH18">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM18">
-        <v>2.67</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2505,28 +2451,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C19">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D19">
-        <v>-146</v>
+        <v>-119</v>
       </c>
       <c r="E19">
-        <v>115</v>
+        <v>-108</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G19">
-        <v>823986</v>
+        <v>824392</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2535,46 +2481,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>0.2767</v>
+        <v>0.2209</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="P19">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="Q19">
-        <v>0.3008</v>
+        <v>0.1964</v>
       </c>
       <c r="R19">
-        <v>0.381</v>
+        <v>0.359</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2695</v>
+        <v>0.2084</v>
       </c>
       <c r="U19">
-        <v>0.2462</v>
+        <v>0.207</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2498</v>
+        <v>0.2139</v>
       </c>
       <c r="X19">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y19">
-        <v>1.0313</v>
+        <v>1.0087</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2583,22 +2529,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>9.7</v>
+        <v>4.8</v>
       </c>
       <c r="AE19" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2859</v>
+        <v>0.2121</v>
       </c>
       <c r="AG19">
-        <v>1.2674</v>
+        <v>0.955</v>
       </c>
       <c r="AH19">
-        <v>-0.95</v>
+        <v>0.22</v>
       </c>
       <c r="AM19">
-        <v>8.75</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2606,22 +2552,22 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="G20">
-        <v>823501</v>
+        <v>823582</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="I20">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -2630,43 +2576,31 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0.238</v>
-      </c>
-      <c r="N20">
-        <v>5</v>
-      </c>
-      <c r="O20">
-        <v>92</v>
+        <v>0.2386</v>
       </c>
       <c r="P20">
-        <v>3.85</v>
-      </c>
-      <c r="Q20">
-        <v>0.3152</v>
-      </c>
-      <c r="R20">
-        <v>0.315</v>
+        <v>4.71</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.1883</v>
+        <v>0.2425</v>
       </c>
       <c r="U20">
-        <v>0.1838</v>
+        <v>0.237</v>
       </c>
       <c r="V20">
         <v>8</v>
       </c>
       <c r="W20">
-        <v>0.2101</v>
+        <v>0.2339</v>
       </c>
       <c r="X20">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y20">
-        <v>0.978</v>
+        <v>0.9768</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2675,22 +2609,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.03</v>
+        <v>5.5</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2623</v>
+        <v>0.2386</v>
       </c>
       <c r="AG20">
-        <v>0.8855</v>
+        <v>1.1118</v>
       </c>
       <c r="AH20">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM20">
-        <v>5.27</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2698,19 +2632,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="C21">
+        <v>5.5</v>
+      </c>
+      <c r="D21">
+        <v>-148</v>
+      </c>
+      <c r="E21">
+        <v>116</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21">
-        <v>823665</v>
+        <v>823582</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2719,46 +2662,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>0.1641</v>
+        <v>0.2718</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="P21">
-        <v>4.33</v>
+        <v>4.16</v>
       </c>
       <c r="Q21">
-        <v>0.2043</v>
+        <v>0.2131</v>
       </c>
       <c r="R21">
-        <v>0.317</v>
+        <v>0.379</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T21">
-        <v>0.1931</v>
+        <v>0.2162</v>
       </c>
       <c r="U21">
-        <v>0.1887</v>
+        <v>0.2071</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2072</v>
+        <v>0.2191</v>
       </c>
       <c r="X21">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y21">
-        <v>0.9917</v>
+        <v>0.9883</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2767,22 +2710,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.1768</v>
+        <v>0.2496</v>
       </c>
       <c r="AG21">
-        <v>0.9079</v>
+        <v>0.9909</v>
       </c>
       <c r="AH21">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM21">
-        <v>3.55</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2790,19 +2733,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>81</v>
+      </c>
+      <c r="C22">
+        <v>3.5</v>
+      </c>
+      <c r="D22">
+        <v>106</v>
+      </c>
+      <c r="E22">
+        <v>-122</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G22">
-        <v>823665</v>
+        <v>822936</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2811,46 +2763,46 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22">
-        <v>0.1619</v>
+        <v>0.2007</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="P22">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="Q22">
-        <v>0.1217</v>
+        <v>0.1635</v>
       </c>
       <c r="R22">
-        <v>0.365</v>
+        <v>0.342</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2213</v>
+        <v>0.1524</v>
       </c>
       <c r="U22">
-        <v>0.2432</v>
+        <v>0.1519</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2363</v>
+        <v>0.1865</v>
       </c>
       <c r="X22">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y22">
-        <v>1.0128</v>
+        <v>0.88</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2859,22 +2811,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>3.55</v>
+        <v>2.39</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.1473</v>
+        <v>0.188</v>
       </c>
       <c r="AG22">
-        <v>1.0405</v>
+        <v>0.6984</v>
       </c>
       <c r="AH22">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM22">
-        <v>3.79</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2882,67 +2834,76 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+      <c r="C23">
+        <v>3.5</v>
+      </c>
+      <c r="D23">
+        <v>-110</v>
+      </c>
+      <c r="E23">
+        <v>-111</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G23">
-        <v>823011</v>
+        <v>822936</v>
       </c>
       <c r="H23" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="I23">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23">
-        <v>0.25</v>
+        <v>0.1467</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="P23">
-        <v>4.11</v>
+        <v>4.02</v>
       </c>
       <c r="Q23">
-        <v>0.2766</v>
+        <v>0.1667</v>
       </c>
       <c r="R23">
-        <v>0.19</v>
+        <v>0.375</v>
       </c>
       <c r="S23" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T23">
-        <v>0.235</v>
+        <v>0.1905</v>
       </c>
       <c r="U23">
-        <v>0.2087</v>
+        <v>0.1926</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>0.2158</v>
+        <v>0.2154</v>
       </c>
       <c r="X23">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y23">
-        <v>0.9458</v>
+        <v>0.9981</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2951,22 +2912,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.56</v>
+        <v>3.19</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2551</v>
+        <v>0.1542</v>
       </c>
       <c r="AG23">
-        <v>1.1052</v>
+        <v>0.8732</v>
       </c>
       <c r="AH23">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM23">
-        <v>2.8</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2974,19 +2935,19 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G24">
-        <v>823011</v>
+        <v>824874</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2998,43 +2959,43 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0.2166</v>
+        <v>0.1606</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="P24">
-        <v>4.2</v>
+        <v>4.46</v>
       </c>
       <c r="Q24">
-        <v>0.2727</v>
+        <v>0.125</v>
       </c>
       <c r="R24">
-        <v>0.331</v>
+        <v>0.39</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T24">
-        <v>0.2007</v>
+        <v>0.225</v>
       </c>
       <c r="U24">
-        <v>0.2364</v>
+        <v>0.2215</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2373</v>
+        <v>0.2205</v>
       </c>
       <c r="X24">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y24">
-        <v>1.0163</v>
+        <v>0.9749</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3043,22 +3004,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>4.79</v>
+        <v>3.21</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.2352</v>
+        <v>0.1467</v>
       </c>
       <c r="AG24">
-        <v>0.9437</v>
+        <v>1.0312</v>
       </c>
       <c r="AH24">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM24">
-        <v>5.03</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3066,22 +3027,22 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="G25">
-        <v>823582</v>
+        <v>824874</v>
       </c>
       <c r="H25" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="I25">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3090,31 +3051,43 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.2386</v>
+        <v>0.1789</v>
+      </c>
+      <c r="N25">
+        <v>5</v>
+      </c>
+      <c r="O25">
+        <v>102</v>
       </c>
       <c r="P25">
-        <v>4.71</v>
+        <v>4.12</v>
+      </c>
+      <c r="Q25">
+        <v>0.1569</v>
+      </c>
+      <c r="R25">
+        <v>0.338</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2425</v>
+        <v>0.241</v>
       </c>
       <c r="U25">
-        <v>0.237</v>
+        <v>0.2256</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2339</v>
+        <v>0.2484</v>
       </c>
       <c r="X25">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y25">
-        <v>0.9875</v>
+        <v>1.0258</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3123,22 +3096,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>5.7</v>
+        <v>4.04</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.2386</v>
+        <v>0.1715</v>
       </c>
       <c r="AG25">
-        <v>1.1406</v>
+        <v>1.1045</v>
       </c>
       <c r="AH25">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM25">
-        <v>5.94</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3146,19 +3119,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="C26">
+        <v>4.5</v>
+      </c>
+      <c r="D26">
+        <v>132</v>
+      </c>
+      <c r="E26">
+        <v>-170</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>824874</v>
+        <v>823741</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3167,46 +3149,46 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26">
-        <v>0.1606</v>
+        <v>0.1729</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="P26">
-        <v>4.46</v>
+        <v>4.15</v>
       </c>
       <c r="Q26">
-        <v>0.125</v>
+        <v>0.2456</v>
       </c>
       <c r="R26">
-        <v>0.39</v>
+        <v>0.363</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T26">
-        <v>0.225</v>
+        <v>0.2081</v>
       </c>
       <c r="U26">
-        <v>0.2215</v>
+        <v>0.2138</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2205</v>
+        <v>0.2135</v>
       </c>
       <c r="X26">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y26">
-        <v>0.9753</v>
+        <v>0.9955</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3215,22 +3197,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.1467</v>
+        <v>0.1988</v>
       </c>
       <c r="AG26">
-        <v>1.058</v>
+        <v>0.954</v>
       </c>
       <c r="AH26">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM26">
-        <v>3.54</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3238,19 +3220,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>89</v>
+      </c>
+      <c r="C27">
+        <v>5.5</v>
+      </c>
+      <c r="D27">
+        <v>-113</v>
+      </c>
+      <c r="E27">
+        <v>-113</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>824874</v>
+        <v>823741</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3259,46 +3250,46 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>0.1789</v>
+        <v>0.2342</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="P27">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="Q27">
-        <v>0.1569</v>
+        <v>0.2288</v>
       </c>
       <c r="R27">
-        <v>0.338</v>
+        <v>0.371</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T27">
-        <v>0.2113</v>
+        <v>0.2381</v>
       </c>
       <c r="U27">
-        <v>0.2003</v>
+        <v>0.2401</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>0.2484</v>
+        <v>0.2412</v>
       </c>
       <c r="X27">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y27">
-        <v>1.0009</v>
+        <v>1.039</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3307,22 +3298,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.54</v>
+        <v>5.82</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.1715</v>
+        <v>0.2322</v>
       </c>
       <c r="AG27">
-        <v>0.9934</v>
+        <v>1.0915</v>
       </c>
       <c r="AH27">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AM27">
-        <v>3.78</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3330,10 +3321,10 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G28">
         <v>824961</v>
@@ -3372,25 +3363,25 @@
         <v>0.373</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="T28">
-        <v>0.258</v>
+        <v>0.2561</v>
       </c>
       <c r="U28">
-        <v>0.2287</v>
+        <v>0.2265</v>
       </c>
       <c r="V28">
         <v>8</v>
       </c>
       <c r="W28">
-        <v>0.2148</v>
+        <v>0.2143</v>
       </c>
       <c r="X28">
-        <v>0.2127</v>
+        <v>0.2182</v>
       </c>
       <c r="Y28">
-        <v>1.0562</v>
+        <v>1.0571</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3399,22 +3390,316 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>6.96</v>
+        <v>6.74</v>
       </c>
       <c r="AE28" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="AF28">
         <v>0.219</v>
       </c>
       <c r="AG28">
-        <v>1.2133</v>
+        <v>1.1737</v>
       </c>
       <c r="AH28">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="AM28">
-        <v>6.38</v>
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29">
+        <v>824961</v>
+      </c>
+      <c r="H29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29">
+        <v>4.6</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0.253</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29">
+        <v>112</v>
+      </c>
+      <c r="P29">
+        <v>4.55</v>
+      </c>
+      <c r="Q29">
+        <v>0.1964</v>
+      </c>
+      <c r="R29">
+        <v>0.359</v>
+      </c>
+      <c r="S29" t="s">
+        <v>48</v>
+      </c>
+      <c r="T29">
+        <v>0.2634</v>
+      </c>
+      <c r="U29">
+        <v>0.2467</v>
+      </c>
+      <c r="V29">
+        <v>9</v>
+      </c>
+      <c r="W29">
+        <v>0.237</v>
+      </c>
+      <c r="X29">
+        <v>0.2182</v>
+      </c>
+      <c r="Y29">
+        <v>1.0246</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD29">
+        <v>6.03</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF29">
+        <v>0.2327</v>
+      </c>
+      <c r="AG29">
+        <v>1.2076</v>
+      </c>
+      <c r="AH29">
+        <v>-0.55</v>
+      </c>
+      <c r="AM29">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30">
+        <v>7.5</v>
+      </c>
+      <c r="D30">
+        <v>-146</v>
+      </c>
+      <c r="E30">
+        <v>115</v>
+      </c>
+      <c r="F30" t="s">
+        <v>94</v>
+      </c>
+      <c r="G30">
+        <v>823986</v>
+      </c>
+      <c r="H30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30">
+        <v>6.2</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>2</v>
+      </c>
+      <c r="M30">
+        <v>0.2767</v>
+      </c>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30">
+        <v>123</v>
+      </c>
+      <c r="P30">
+        <v>4.16</v>
+      </c>
+      <c r="Q30">
+        <v>0.3008</v>
+      </c>
+      <c r="R30">
+        <v>0.381</v>
+      </c>
+      <c r="S30" t="s">
+        <v>48</v>
+      </c>
+      <c r="T30">
+        <v>0.2658</v>
+      </c>
+      <c r="U30">
+        <v>0.2427</v>
+      </c>
+      <c r="V30">
+        <v>9</v>
+      </c>
+      <c r="W30">
+        <v>0.2492</v>
+      </c>
+      <c r="X30">
+        <v>0.2182</v>
+      </c>
+      <c r="Y30">
+        <v>1.0306</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD30">
+        <v>9.32</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF30">
+        <v>0.2859</v>
+      </c>
+      <c r="AG30">
+        <v>1.2183</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31">
+        <v>3.5</v>
+      </c>
+      <c r="D31">
+        <v>102</v>
+      </c>
+      <c r="E31">
+        <v>-130</v>
+      </c>
+      <c r="F31" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31">
+        <v>823986</v>
+      </c>
+      <c r="H31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31">
+        <v>4.8</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>0.1695</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>106</v>
+      </c>
+      <c r="P31">
+        <v>4.38</v>
+      </c>
+      <c r="Q31">
+        <v>0.1509</v>
+      </c>
+      <c r="R31">
+        <v>0.346</v>
+      </c>
+      <c r="S31" t="s">
+        <v>48</v>
+      </c>
+      <c r="T31">
+        <v>0.1503</v>
+      </c>
+      <c r="U31">
+        <v>0.153</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.222</v>
+      </c>
+      <c r="X31">
+        <v>0.2182</v>
+      </c>
+      <c r="Y31">
+        <v>0.9978</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD31">
+        <v>2.36</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF31">
+        <v>0.1631</v>
+      </c>
+      <c r="AG31">
+        <v>0.6891</v>
+      </c>
+      <c r="AH31">
+        <v>0.22</v>
+      </c>
+      <c r="AM31">
+        <v>2.58</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -133,24 +133,48 @@
     <t>08/29/2026</t>
   </si>
   <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Matt Wilkinson</t>
+  </si>
+  <si>
+    <t>Martin Perez</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>team_season_vs_hand</t>
+  </si>
+  <si>
     <t>Jake Bennett</t>
   </si>
   <si>
     <t>Boston Red Sox @ New York Yankees</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Carlos Rodón</t>
   </si>
   <si>
@@ -211,21 +235,6 @@
     <t>Seattle Mariners @ Toronto Blue Jays</t>
   </si>
   <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>team_season_vs_hand</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
     <t>Sandy Alcantara</t>
   </si>
   <si>
@@ -265,40 +274,37 @@
     <t>Nick Martinez</t>
   </si>
   <si>
+    <t>Zach Agnos</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Shane Drohan</t>
+  </si>
+  <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Athletics</t>
+  </si>
+  <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
     <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Shane Drohan</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Athletics</t>
-  </si>
-  <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
   </si>
 </sst>
 </file>
@@ -679,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -815,22 +821,22 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-116</v>
+        <v>134</v>
       </c>
       <c r="E2">
-        <v>-106</v>
+        <v>-170</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823539</v>
+        <v>823177</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -839,46 +845,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>0.1903</v>
+        <v>0.1492</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P2">
-        <v>4.02</v>
+        <v>4.38</v>
       </c>
       <c r="Q2">
-        <v>0.2033</v>
+        <v>0.1453</v>
       </c>
       <c r="R2">
-        <v>0.381</v>
+        <v>0.369</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2529</v>
+        <v>0.2333</v>
       </c>
       <c r="U2">
-        <v>0.2729</v>
+        <v>0.2173</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2486</v>
+        <v>0.2049</v>
       </c>
       <c r="X2">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y2">
-        <v>1.0351</v>
+        <v>0.9313</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -887,22 +893,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>5.5</v>
+        <v>3.61</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1953</v>
+        <v>0.1477</v>
       </c>
       <c r="AG2">
-        <v>1.1592</v>
+        <v>1.0672</v>
       </c>
       <c r="AH2">
         <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>5.72</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -913,73 +919,31 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-108</v>
+        <v>134</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>-155</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3">
-        <v>823539</v>
+      <c r="G3" t="s">
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3">
-        <v>4.9</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>0.2544</v>
-      </c>
-      <c r="N3">
-        <v>5</v>
-      </c>
-      <c r="O3">
-        <v>99</v>
-      </c>
-      <c r="P3">
-        <v>4.2</v>
-      </c>
-      <c r="Q3">
-        <v>0.2424</v>
-      </c>
-      <c r="R3">
-        <v>0.331</v>
+        <v>6</v>
       </c>
       <c r="S3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3">
-        <v>0.1914</v>
-      </c>
-      <c r="U3">
-        <v>0.1846</v>
-      </c>
-      <c r="V3">
-        <v>9</v>
-      </c>
-      <c r="W3">
-        <v>0.2101</v>
-      </c>
-      <c r="X3">
-        <v>0.2182</v>
-      </c>
-      <c r="Y3">
-        <v>0.9697</v>
+        <v>44</v>
+      </c>
+      <c r="V3" t="s">
+        <v>44</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -987,23 +951,8 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
-      <c r="AD3">
-        <v>4.42</v>
-      </c>
       <c r="AE3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF3">
-        <v>0.2504</v>
-      </c>
-      <c r="AG3">
-        <v>0.8775</v>
-      </c>
-      <c r="AH3">
-        <v>0.22</v>
-      </c>
-      <c r="AM3">
-        <v>4.64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1013,17 +962,26 @@
       <c r="B4" t="s">
         <v>47</v>
       </c>
+      <c r="C4">
+        <v>4.5</v>
+      </c>
+      <c r="D4">
+        <v>110</v>
+      </c>
+      <c r="E4">
+        <v>-107</v>
+      </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G4">
-        <v>823501</v>
+        <v>824874</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1032,46 +990,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>0.238</v>
+        <v>0.1789</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="P4">
-        <v>3.85</v>
+        <v>4.12</v>
       </c>
       <c r="Q4">
-        <v>0.3152</v>
+        <v>0.1569</v>
       </c>
       <c r="R4">
-        <v>0.315</v>
+        <v>0.338</v>
       </c>
       <c r="S4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1883</v>
+        <v>0.241</v>
       </c>
       <c r="U4">
-        <v>0.1838</v>
+        <v>0.2256</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2101</v>
+        <v>0.2484</v>
       </c>
       <c r="X4">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y4">
-        <v>0.9794</v>
+        <v>1.0258</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1080,22 +1038,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.91</v>
+        <v>4.03</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2623</v>
+        <v>0.1715</v>
       </c>
       <c r="AG4">
-        <v>0.8631</v>
+        <v>1.1021</v>
       </c>
       <c r="AH4">
         <v>0.22</v>
       </c>
       <c r="AM4">
-        <v>5.13</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1106,25 +1064,25 @@
         <v>49</v>
       </c>
       <c r="C5">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D5">
-        <v>-120</v>
+        <v>-138</v>
       </c>
       <c r="E5">
-        <v>-105</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5">
+        <v>823176</v>
+      </c>
+      <c r="H5" t="s">
         <v>50</v>
       </c>
-      <c r="G5">
-        <v>824230</v>
-      </c>
-      <c r="H5" t="s">
-        <v>42</v>
-      </c>
       <c r="I5">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1133,46 +1091,40 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>0.2989</v>
+        <v>0.1591</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="P5">
-        <v>4.14</v>
+        <v>4.44</v>
       </c>
       <c r="Q5">
-        <v>0.2989</v>
+        <v>0.1818</v>
       </c>
       <c r="R5">
-        <v>0.303</v>
+        <v>0.331</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
-      </c>
-      <c r="T5">
-        <v>0.2179</v>
-      </c>
-      <c r="U5">
-        <v>0.211</v>
+        <v>51</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.2294</v>
+        <v>0.2353</v>
       </c>
       <c r="X5">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y5">
-        <v>0.9742</v>
+        <v>1.0233</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1181,22 +1133,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.33</v>
+        <v>3.47</v>
       </c>
       <c r="AE5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2989</v>
+        <v>0.1666</v>
       </c>
       <c r="AG5">
-        <v>0.9989</v>
+        <v>1.0398</v>
       </c>
       <c r="AH5">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM5">
-        <v>5.78</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1207,19 +1159,19 @@
         <v>52</v>
       </c>
       <c r="C6">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D6">
-        <v>-108</v>
+        <v>-116</v>
       </c>
       <c r="E6">
-        <v>-115</v>
+        <v>-106</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6">
-        <v>824230</v>
+        <v>823539</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
@@ -1234,46 +1186,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>0.1664</v>
+        <v>0.1967</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="Q6">
-        <v>0.0948</v>
+        <v>0.2364</v>
       </c>
       <c r="R6">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2129</v>
+        <v>0.2529</v>
       </c>
       <c r="U6">
-        <v>0.2125</v>
+        <v>0.2729</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2062</v>
+        <v>0.2486</v>
       </c>
       <c r="X6">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y6">
-        <v>0.991</v>
+        <v>1.0351</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1282,22 +1234,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.11</v>
+        <v>5.77</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1414</v>
+        <v>0.2108</v>
       </c>
       <c r="AG6">
-        <v>0.9759</v>
+        <v>1.1567</v>
       </c>
       <c r="AH6">
         <v>0.22</v>
       </c>
       <c r="AM6">
-        <v>3.33</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1305,19 +1257,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+      <c r="D7">
+        <v>-108</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
       <c r="G7">
-        <v>823665</v>
+        <v>823539</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1326,46 +1287,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>0.1641</v>
+        <v>0.2551</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P7">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="Q7">
-        <v>0.2043</v>
+        <v>0.2292</v>
       </c>
       <c r="R7">
-        <v>0.317</v>
+        <v>0.324</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2021</v>
+        <v>0.1914</v>
       </c>
       <c r="U7">
-        <v>0.1907</v>
+        <v>0.1846</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2072</v>
+        <v>0.2101</v>
       </c>
       <c r="X7">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y7">
-        <v>0.936</v>
+        <v>0.9697</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1374,22 +1335,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.19</v>
+        <v>4.31</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.1768</v>
+        <v>0.2467</v>
       </c>
       <c r="AG7">
-        <v>0.9264</v>
+        <v>0.8756</v>
       </c>
       <c r="AH7">
         <v>0.22</v>
       </c>
       <c r="AM7">
-        <v>3.41</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1400,16 +1361,16 @@
         <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
-        <v>823665</v>
+        <v>823501</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1421,43 +1382,43 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0.1619</v>
+        <v>0.238</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="P8">
-        <v>4.22</v>
+        <v>3.85</v>
       </c>
       <c r="Q8">
-        <v>0.1217</v>
+        <v>0.3152</v>
       </c>
       <c r="R8">
-        <v>0.365</v>
+        <v>0.315</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T8">
-        <v>0.2522</v>
+        <v>0.1883</v>
       </c>
       <c r="U8">
-        <v>0.2525</v>
+        <v>0.1838</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2363</v>
+        <v>0.2101</v>
       </c>
       <c r="X8">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y8">
-        <v>1.0323</v>
+        <v>0.9794</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1466,22 +1427,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.02</v>
+        <v>4.9</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1473</v>
+        <v>0.2623</v>
       </c>
       <c r="AG8">
-        <v>1.1561</v>
+        <v>0.8613</v>
       </c>
       <c r="AH8">
         <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>4.24</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1489,67 +1450,76 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="C9">
+        <v>6.5</v>
+      </c>
+      <c r="D9">
+        <v>-120</v>
+      </c>
+      <c r="E9">
+        <v>-105</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>823011</v>
+        <v>824230</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>0.25</v>
+        <v>0.3241</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="P9">
-        <v>4.11</v>
+        <v>4.21</v>
       </c>
       <c r="Q9">
-        <v>0.2766</v>
+        <v>0.3271</v>
       </c>
       <c r="R9">
-        <v>0.19</v>
+        <v>0.349</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2511</v>
+        <v>0.2179</v>
       </c>
       <c r="U9">
-        <v>0.2169</v>
+        <v>0.211</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2158</v>
+        <v>0.2294</v>
       </c>
       <c r="X9">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y9">
-        <v>0.8961</v>
+        <v>0.9742</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1558,22 +1528,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>2.52</v>
+        <v>6.82</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="AF9">
-        <v>0.2551</v>
+        <v>0.3251</v>
       </c>
       <c r="AG9">
-        <v>1.1509</v>
+        <v>0.9967</v>
       </c>
       <c r="AH9">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM9">
-        <v>2.74</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1581,19 +1551,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="C10">
+        <v>3.5</v>
+      </c>
+      <c r="D10">
+        <v>-108</v>
+      </c>
+      <c r="E10">
+        <v>-115</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>823011</v>
+        <v>824230</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1602,46 +1581,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>0.2166</v>
+        <v>0.1667</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="P10">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="Q10">
-        <v>0.2727</v>
+        <v>0.1193</v>
       </c>
       <c r="R10">
-        <v>0.331</v>
+        <v>0.353</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2509</v>
+        <v>0.2129</v>
       </c>
       <c r="U10">
-        <v>0.2463</v>
+        <v>0.2125</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2373</v>
+        <v>0.2062</v>
       </c>
       <c r="X10">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y10">
-        <v>1.0293</v>
+        <v>0.991</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1650,22 +1629,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>5.91</v>
+        <v>3.26</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2352</v>
+        <v>0.1499</v>
       </c>
       <c r="AG10">
-        <v>1.1501</v>
+        <v>0.9738</v>
       </c>
       <c r="AH10">
         <v>0.22</v>
       </c>
       <c r="AM10">
-        <v>6.13</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1673,28 +1652,19 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11">
-        <v>3.5</v>
-      </c>
-      <c r="D11">
-        <v>-156</v>
-      </c>
-      <c r="E11">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11">
-        <v>824637</v>
+        <v>823665</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I11">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1703,46 +1673,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>0.181</v>
+        <v>0.1631</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="P11">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="Q11">
-        <v>0.16</v>
+        <v>0.2237</v>
       </c>
       <c r="R11">
-        <v>0.385</v>
+        <v>0.275</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.1662</v>
+        <v>0.2021</v>
       </c>
       <c r="U11">
-        <v>0.1874</v>
+        <v>0.1907</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2192</v>
+        <v>0.2072</v>
       </c>
       <c r="X11">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y11">
-        <v>0.8905</v>
+        <v>0.936</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1751,22 +1721,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>2.74</v>
+        <v>2.99</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1729</v>
+        <v>0.1798</v>
       </c>
       <c r="AG11">
-        <v>0.762</v>
+        <v>0.9244</v>
       </c>
       <c r="AH11">
         <v>0.22</v>
       </c>
       <c r="AM11">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1774,28 +1744,19 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
         <v>62</v>
       </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-      <c r="D12">
-        <v>112</v>
-      </c>
-      <c r="E12">
-        <v>-130</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
       <c r="G12">
-        <v>824637</v>
+        <v>823665</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1804,46 +1765,46 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>0.2354</v>
+        <v>0.162</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="P12">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="Q12">
-        <v>0.2203</v>
+        <v>0.1237</v>
       </c>
       <c r="R12">
-        <v>0.371</v>
+        <v>0.327</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2556</v>
+        <v>0.2522</v>
       </c>
       <c r="U12">
-        <v>0.2652</v>
+        <v>0.2525</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2542</v>
+        <v>0.2363</v>
       </c>
       <c r="X12">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y12">
-        <v>1.12</v>
+        <v>1.0323</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1852,22 +1813,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>7.07</v>
+        <v>3.92</v>
       </c>
       <c r="AE12" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2298</v>
+        <v>0.1495</v>
       </c>
       <c r="AG12">
-        <v>1.1717</v>
+        <v>1.1536</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AM12">
-        <v>7.07</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1877,74 +1838,65 @@
       <c r="B13" t="s">
         <v>64</v>
       </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-      <c r="D13">
-        <v>102</v>
-      </c>
-      <c r="E13">
-        <v>-130</v>
-      </c>
       <c r="F13" t="s">
         <v>65</v>
       </c>
       <c r="G13">
-        <v>822770</v>
+        <v>823011</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="I13">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>0.2371</v>
+        <v>0.2508</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="P13">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="Q13">
-        <v>0.1875</v>
+        <v>0.2683</v>
       </c>
       <c r="R13">
-        <v>0.359</v>
+        <v>0.17</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2675</v>
+        <v>0.2511</v>
       </c>
       <c r="U13">
-        <v>0.233</v>
+        <v>0.2169</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2259</v>
+        <v>0.2158</v>
       </c>
       <c r="X13">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y13">
-        <v>0.9726</v>
+        <v>0.8961</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1953,22 +1905,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>6.07</v>
+        <v>2.29</v>
       </c>
       <c r="AE13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2193</v>
+        <v>0.2538</v>
       </c>
       <c r="AG13">
-        <v>1.2262</v>
+        <v>1.1484</v>
       </c>
       <c r="AH13">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM13">
-        <v>5.52</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1976,19 +1928,19 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G14">
-        <v>823177</v>
+        <v>823011</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2000,37 +1952,43 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0.1492</v>
+        <v>0.216</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="P14">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="Q14">
-        <v>0.1453</v>
+        <v>0.3125</v>
       </c>
       <c r="R14">
-        <v>0.369</v>
+        <v>0.286</v>
       </c>
       <c r="S14" t="s">
-        <v>68</v>
+        <v>43</v>
+      </c>
+      <c r="T14">
+        <v>0.2509</v>
+      </c>
+      <c r="U14">
+        <v>0.2463</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2049</v>
+        <v>0.2373</v>
       </c>
       <c r="X14">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y14">
-        <v>0.9806</v>
+        <v>1.0293</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2039,22 +1997,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.34</v>
+        <v>5.94</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.1477</v>
+        <v>0.2436</v>
       </c>
       <c r="AG14">
-        <v>0.9377</v>
+        <v>1.1476</v>
       </c>
       <c r="AH14">
         <v>0.22</v>
       </c>
       <c r="AM14">
-        <v>3.56</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2062,19 +2020,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15">
+        <v>3.5</v>
+      </c>
+      <c r="D15">
+        <v>-156</v>
+      </c>
+      <c r="E15">
+        <v>126</v>
+      </c>
+      <c r="F15" t="s">
         <v>69</v>
       </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
       <c r="G15">
-        <v>823176</v>
+        <v>824637</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2083,40 +2050,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M15">
-        <v>0.1591</v>
+        <v>0.1792</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="P15">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="Q15">
-        <v>0.1818</v>
+        <v>0.1776</v>
       </c>
       <c r="R15">
-        <v>0.331</v>
+        <v>0.349</v>
       </c>
       <c r="S15" t="s">
-        <v>68</v>
+        <v>43</v>
+      </c>
+      <c r="T15">
+        <v>0.1662</v>
+      </c>
+      <c r="U15">
+        <v>0.1874</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2353</v>
+        <v>0.2192</v>
       </c>
       <c r="X15">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y15">
-        <v>1.0233</v>
+        <v>0.8905</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2125,22 +2098,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.47</v>
+        <v>2.75</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1666</v>
+        <v>0.1787</v>
       </c>
       <c r="AG15">
-        <v>1.0398</v>
+        <v>0.7603</v>
       </c>
       <c r="AH15">
         <v>0.22</v>
       </c>
       <c r="AM15">
-        <v>3.69</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2148,28 +2121,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D16">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E16">
-        <v>-150</v>
+        <v>-130</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G16">
-        <v>822690</v>
+        <v>824637</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2178,46 +2151,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>0.181</v>
+        <v>0.2374</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="P16">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="Q16">
-        <v>0.1667</v>
+        <v>0.25</v>
       </c>
       <c r="R16">
-        <v>0.398</v>
+        <v>0.324</v>
       </c>
       <c r="S16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2298</v>
+        <v>0.2556</v>
       </c>
       <c r="U16">
-        <v>0.2342</v>
+        <v>0.2652</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2064</v>
+        <v>0.2542</v>
       </c>
       <c r="X16">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y16">
-        <v>1.0076</v>
+        <v>1.12</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2226,22 +2199,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.03</v>
+        <v>7.18</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="AF16">
-        <v>0.1753</v>
+        <v>0.2415</v>
       </c>
       <c r="AG16">
-        <v>1.0535</v>
+        <v>1.1691</v>
       </c>
       <c r="AH16">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>5.25</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2249,28 +2222,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17">
+        <v>5.5</v>
+      </c>
+      <c r="D17">
+        <v>102</v>
+      </c>
+      <c r="E17">
+        <v>-130</v>
+      </c>
+      <c r="F17" t="s">
         <v>73</v>
       </c>
-      <c r="C17">
-        <v>6.5</v>
-      </c>
-      <c r="D17">
-        <v>100</v>
-      </c>
-      <c r="E17">
-        <v>-128</v>
-      </c>
-      <c r="F17" t="s">
-        <v>72</v>
-      </c>
       <c r="G17">
-        <v>822690</v>
+        <v>822770</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2279,46 +2252,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>0.2708</v>
+        <v>0.2371</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="P17">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="Q17">
-        <v>0.3223</v>
+        <v>0.1875</v>
       </c>
       <c r="R17">
-        <v>0.377</v>
+        <v>0.359</v>
       </c>
       <c r="S17" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2086</v>
+        <v>0.2675</v>
       </c>
       <c r="U17">
-        <v>0.1957</v>
+        <v>0.233</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2107</v>
+        <v>0.2259</v>
       </c>
       <c r="X17">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y17">
-        <v>0.9719</v>
+        <v>0.9726</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2327,22 +2300,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>6.01</v>
+        <v>6.05</v>
       </c>
       <c r="AE17" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="AF17">
-        <v>0.2902</v>
+        <v>0.2193</v>
       </c>
       <c r="AG17">
-        <v>0.9564</v>
+        <v>1.2236</v>
       </c>
       <c r="AH17">
         <v>-0.55</v>
       </c>
       <c r="AM17">
-        <v>5.46</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2353,73 +2326,73 @@
         <v>74</v>
       </c>
       <c r="C18">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-120</v>
+        <v>118</v>
       </c>
       <c r="E18">
-        <v>-107</v>
+        <v>-150</v>
       </c>
       <c r="F18" t="s">
         <v>75</v>
       </c>
       <c r="G18">
-        <v>824392</v>
+        <v>822690</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18">
-        <v>0.183</v>
+        <v>0.181</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="P18">
-        <v>4.03</v>
+        <v>4.12</v>
       </c>
       <c r="Q18">
-        <v>0.1538</v>
+        <v>0.1667</v>
       </c>
       <c r="R18">
-        <v>0.206</v>
+        <v>0.398</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.1994</v>
+        <v>0.2314</v>
       </c>
       <c r="U18">
-        <v>0.1738</v>
+        <v>0.2363</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2241</v>
+        <v>0.2064</v>
       </c>
       <c r="X18">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y18">
-        <v>0.88</v>
+        <v>0.9921</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2428,22 +2401,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>1.72</v>
+        <v>4.98</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.177</v>
+        <v>0.1753</v>
       </c>
       <c r="AG18">
-        <v>0.9139</v>
+        <v>1.0583</v>
       </c>
       <c r="AH18">
         <v>0.22</v>
       </c>
       <c r="AM18">
-        <v>1.94</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2454,25 +2427,25 @@
         <v>76</v>
       </c>
       <c r="C19">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D19">
-        <v>-119</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>-108</v>
+        <v>-128</v>
       </c>
       <c r="F19" t="s">
         <v>75</v>
       </c>
       <c r="G19">
-        <v>824392</v>
+        <v>822690</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2481,46 +2454,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19">
-        <v>0.2209</v>
+        <v>0.2708</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P19">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>0.1964</v>
+        <v>0.3223</v>
       </c>
       <c r="R19">
-        <v>0.359</v>
+        <v>0.377</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2084</v>
+        <v>0.2086</v>
       </c>
       <c r="U19">
-        <v>0.207</v>
+        <v>0.1957</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2139</v>
+        <v>0.2107</v>
       </c>
       <c r="X19">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y19">
-        <v>1.0087</v>
+        <v>0.9439</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2529,22 +2502,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.8</v>
+        <v>5.83</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2121</v>
+        <v>0.2902</v>
       </c>
       <c r="AG19">
-        <v>0.955</v>
+        <v>0.9543</v>
       </c>
       <c r="AH19">
         <v>0.22</v>
       </c>
       <c r="AM19">
-        <v>5.02</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2554,17 +2527,26 @@
       <c r="B20" t="s">
         <v>77</v>
       </c>
+      <c r="C20">
+        <v>2.5</v>
+      </c>
+      <c r="D20">
+        <v>-120</v>
+      </c>
+      <c r="E20">
+        <v>-107</v>
+      </c>
       <c r="F20" t="s">
         <v>78</v>
       </c>
       <c r="G20">
-        <v>823582</v>
+        <v>824392</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="I20">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -2573,34 +2555,46 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>0.2386</v>
+        <v>0.183</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>52</v>
       </c>
       <c r="P20">
-        <v>4.71</v>
+        <v>4.03</v>
+      </c>
+      <c r="Q20">
+        <v>0.1538</v>
+      </c>
+      <c r="R20">
+        <v>0.206</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2425</v>
+        <v>0.1994</v>
       </c>
       <c r="U20">
-        <v>0.237</v>
+        <v>0.1738</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2339</v>
+        <v>0.2241</v>
       </c>
       <c r="X20">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y20">
-        <v>0.9768</v>
+        <v>0.88</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2609,22 +2603,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.5</v>
+        <v>1.72</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2386</v>
+        <v>0.177</v>
       </c>
       <c r="AG20">
-        <v>1.1118</v>
+        <v>0.9119</v>
       </c>
       <c r="AH20">
         <v>0.22</v>
       </c>
       <c r="AM20">
-        <v>5.72</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2632,22 +2626,22 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21">
         <v>5.5</v>
       </c>
       <c r="D21">
-        <v>-148</v>
+        <v>-119</v>
       </c>
       <c r="E21">
-        <v>116</v>
+        <v>-108</v>
       </c>
       <c r="F21" t="s">
         <v>78</v>
       </c>
       <c r="G21">
-        <v>823582</v>
+        <v>824392</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
@@ -2662,46 +2656,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>0.2718</v>
+        <v>0.2209</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="P21">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="Q21">
-        <v>0.2131</v>
+        <v>0.1964</v>
       </c>
       <c r="R21">
-        <v>0.379</v>
+        <v>0.359</v>
       </c>
       <c r="S21" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2162</v>
+        <v>0.2084</v>
       </c>
       <c r="U21">
-        <v>0.2071</v>
+        <v>0.207</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2191</v>
+        <v>0.2139</v>
       </c>
       <c r="X21">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y21">
-        <v>0.9883</v>
+        <v>1.0087</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2710,22 +2704,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.81</v>
+        <v>4.79</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2496</v>
+        <v>0.2121</v>
       </c>
       <c r="AG21">
-        <v>0.9909</v>
+        <v>0.953</v>
       </c>
       <c r="AH21">
         <v>0.22</v>
       </c>
       <c r="AM21">
-        <v>6.03</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2733,76 +2727,55 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" t="s">
         <v>81</v>
       </c>
-      <c r="C22">
-        <v>3.5</v>
-      </c>
-      <c r="D22">
-        <v>106</v>
-      </c>
-      <c r="E22">
-        <v>-122</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22">
+        <v>823582</v>
+      </c>
+      <c r="H22" t="s">
         <v>82</v>
       </c>
-      <c r="G22">
-        <v>822936</v>
-      </c>
-      <c r="H22" t="s">
-        <v>42</v>
-      </c>
       <c r="I22">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>0.2007</v>
-      </c>
-      <c r="N22">
-        <v>5</v>
-      </c>
-      <c r="O22">
-        <v>104</v>
+        <v>0.2386</v>
       </c>
       <c r="P22">
-        <v>4.26</v>
-      </c>
-      <c r="Q22">
-        <v>0.1635</v>
-      </c>
-      <c r="R22">
-        <v>0.342</v>
+        <v>4.71</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.1524</v>
+        <v>0.2425</v>
       </c>
       <c r="U22">
-        <v>0.1519</v>
+        <v>0.237</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>0.1865</v>
+        <v>0.2339</v>
       </c>
       <c r="X22">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y22">
-        <v>0.88</v>
+        <v>0.9768</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2811,22 +2784,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>2.39</v>
+        <v>5.49</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.188</v>
+        <v>0.2386</v>
       </c>
       <c r="AG22">
-        <v>0.6984</v>
+        <v>1.1094</v>
       </c>
       <c r="AH22">
         <v>0.22</v>
       </c>
       <c r="AM22">
-        <v>2.61</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2837,25 +2810,25 @@
         <v>83</v>
       </c>
       <c r="C23">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D23">
-        <v>-110</v>
+        <v>-148</v>
       </c>
       <c r="E23">
-        <v>-111</v>
+        <v>116</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G23">
-        <v>822936</v>
+        <v>823582</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2864,46 +2837,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23">
-        <v>0.1467</v>
+        <v>0.2718</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P23">
-        <v>4.02</v>
+        <v>4.16</v>
       </c>
       <c r="Q23">
-        <v>0.1667</v>
+        <v>0.2131</v>
       </c>
       <c r="R23">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="S23" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.1905</v>
+        <v>0.2057</v>
       </c>
       <c r="U23">
-        <v>0.1926</v>
+        <v>0.2018</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2154</v>
+        <v>0.2191</v>
       </c>
       <c r="X23">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y23">
-        <v>0.9981</v>
+        <v>0.9509</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2912,22 +2885,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>3.19</v>
+        <v>5.31</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.1542</v>
+        <v>0.2496</v>
       </c>
       <c r="AG23">
-        <v>0.8732</v>
+        <v>0.9406</v>
       </c>
       <c r="AH23">
         <v>0.22</v>
       </c>
       <c r="AM23">
-        <v>3.41</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2937,11 +2910,20 @@
       <c r="B24" t="s">
         <v>84</v>
       </c>
+      <c r="C24">
+        <v>3.5</v>
+      </c>
+      <c r="D24">
+        <v>106</v>
+      </c>
+      <c r="E24">
+        <v>-122</v>
+      </c>
       <c r="F24" t="s">
         <v>85</v>
       </c>
       <c r="G24">
-        <v>824874</v>
+        <v>822936</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
@@ -2956,46 +2938,46 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24">
-        <v>0.1606</v>
+        <v>0.2007</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="P24">
-        <v>4.46</v>
+        <v>4.26</v>
       </c>
       <c r="Q24">
-        <v>0.125</v>
+        <v>0.1635</v>
       </c>
       <c r="R24">
-        <v>0.39</v>
+        <v>0.342</v>
       </c>
       <c r="S24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="T24">
-        <v>0.225</v>
+        <v>0.1524</v>
       </c>
       <c r="U24">
-        <v>0.2215</v>
+        <v>0.1519</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2205</v>
+        <v>0.1865</v>
       </c>
       <c r="X24">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y24">
-        <v>0.9749</v>
+        <v>0.88</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3004,22 +2986,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>3.21</v>
+        <v>2.39</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.1467</v>
+        <v>0.188</v>
       </c>
       <c r="AG24">
-        <v>1.0312</v>
+        <v>0.6968</v>
       </c>
       <c r="AH24">
         <v>0.22</v>
       </c>
       <c r="AM24">
-        <v>3.43</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3029,17 +3011,26 @@
       <c r="B25" t="s">
         <v>86</v>
       </c>
+      <c r="C25">
+        <v>3.5</v>
+      </c>
+      <c r="D25">
+        <v>-110</v>
+      </c>
+      <c r="E25">
+        <v>-111</v>
+      </c>
       <c r="F25" t="s">
         <v>85</v>
       </c>
       <c r="G25">
-        <v>824874</v>
+        <v>822936</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3048,46 +3039,46 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>0.1789</v>
+        <v>0.1467</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="P25">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="Q25">
-        <v>0.1569</v>
+        <v>0.1667</v>
       </c>
       <c r="R25">
-        <v>0.338</v>
+        <v>0.375</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.241</v>
+        <v>0.1918</v>
       </c>
       <c r="U25">
-        <v>0.2256</v>
+        <v>0.1995</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2484</v>
+        <v>0.2154</v>
       </c>
       <c r="X25">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y25">
-        <v>1.0258</v>
+        <v>1.0075</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3096,22 +3087,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.04</v>
+        <v>3.23</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.1715</v>
+        <v>0.1542</v>
       </c>
       <c r="AG25">
-        <v>1.1045</v>
+        <v>0.8773</v>
       </c>
       <c r="AH25">
         <v>0.22</v>
       </c>
       <c r="AM25">
-        <v>4.26</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3121,26 +3112,17 @@
       <c r="B26" t="s">
         <v>87</v>
       </c>
-      <c r="C26">
-        <v>4.5</v>
-      </c>
-      <c r="D26">
-        <v>132</v>
-      </c>
-      <c r="E26">
-        <v>-170</v>
-      </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="G26">
-        <v>823741</v>
+        <v>824874</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3149,46 +3131,46 @@
         <v>0</v>
       </c>
       <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0.1522</v>
+      </c>
+      <c r="N26">
         <v>2</v>
       </c>
-      <c r="M26">
-        <v>0.1729</v>
-      </c>
-      <c r="N26">
-        <v>5</v>
-      </c>
       <c r="O26">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="P26">
-        <v>4.15</v>
+        <v>4.41</v>
       </c>
       <c r="Q26">
-        <v>0.2456</v>
+        <v>0.1563</v>
       </c>
       <c r="R26">
-        <v>0.363</v>
+        <v>0.138</v>
       </c>
       <c r="S26" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2081</v>
+        <v>0.2331</v>
       </c>
       <c r="U26">
-        <v>0.2138</v>
+        <v>0.2231</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2135</v>
+        <v>0.2205</v>
       </c>
       <c r="X26">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y26">
-        <v>0.9955</v>
+        <v>0.988</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3197,22 +3179,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.94</v>
+        <v>2.84</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.1988</v>
+        <v>0.1528</v>
       </c>
       <c r="AG26">
-        <v>0.954</v>
+        <v>1.0663</v>
       </c>
       <c r="AH26">
         <v>0.22</v>
       </c>
       <c r="AM26">
-        <v>4.16</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3220,19 +3202,19 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27">
+        <v>4.5</v>
+      </c>
+      <c r="D27">
+        <v>132</v>
+      </c>
+      <c r="E27">
+        <v>-170</v>
+      </c>
+      <c r="F27" t="s">
         <v>89</v>
-      </c>
-      <c r="C27">
-        <v>5.5</v>
-      </c>
-      <c r="D27">
-        <v>-113</v>
-      </c>
-      <c r="E27">
-        <v>-113</v>
-      </c>
-      <c r="F27" t="s">
-        <v>88</v>
       </c>
       <c r="G27">
         <v>823741</v>
@@ -3241,7 +3223,7 @@
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3253,43 +3235,43 @@
         <v>2</v>
       </c>
       <c r="M27">
-        <v>0.2342</v>
+        <v>0.1729</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P27">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="Q27">
-        <v>0.2288</v>
+        <v>0.2456</v>
       </c>
       <c r="R27">
-        <v>0.371</v>
+        <v>0.363</v>
       </c>
       <c r="S27" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="T27">
-        <v>0.2381</v>
+        <v>0.2081</v>
       </c>
       <c r="U27">
-        <v>0.2401</v>
+        <v>0.2138</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2412</v>
+        <v>0.2135</v>
       </c>
       <c r="X27">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y27">
-        <v>1.039</v>
+        <v>0.9955</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3298,22 +3280,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>5.82</v>
+        <v>3.93</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.2322</v>
+        <v>0.1988</v>
       </c>
       <c r="AG27">
-        <v>1.0915</v>
+        <v>0.9519</v>
       </c>
       <c r="AH27">
         <v>0.22</v>
       </c>
       <c r="AM27">
-        <v>6.04</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3323,17 +3305,26 @@
       <c r="B28" t="s">
         <v>90</v>
       </c>
+      <c r="C28">
+        <v>5.5</v>
+      </c>
+      <c r="D28">
+        <v>-113</v>
+      </c>
+      <c r="E28">
+        <v>-113</v>
+      </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G28">
-        <v>824961</v>
+        <v>823741</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3342,46 +3333,46 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28">
-        <v>0.2093</v>
+        <v>0.2342</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P28">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="Q28">
-        <v>0.2353</v>
+        <v>0.2288</v>
       </c>
       <c r="R28">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="S28" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="T28">
-        <v>0.2561</v>
+        <v>0.2381</v>
       </c>
       <c r="U28">
-        <v>0.2265</v>
+        <v>0.2401</v>
       </c>
       <c r="V28">
         <v>8</v>
       </c>
       <c r="W28">
-        <v>0.2143</v>
+        <v>0.2412</v>
       </c>
       <c r="X28">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y28">
-        <v>1.0571</v>
+        <v>1.039</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3390,22 +3381,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>6.74</v>
+        <v>5.81</v>
       </c>
       <c r="AE28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.219</v>
+        <v>0.2322</v>
       </c>
       <c r="AG28">
-        <v>1.1737</v>
+        <v>1.0891</v>
       </c>
       <c r="AH28">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM28">
-        <v>6.19</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3413,10 +3404,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" t="s">
         <v>92</v>
-      </c>
-      <c r="F29" t="s">
-        <v>91</v>
       </c>
       <c r="G29">
         <v>824961</v>
@@ -3425,7 +3416,7 @@
         <v>42</v>
       </c>
       <c r="I29">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3437,43 +3428,43 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0.253</v>
+        <v>0.2093</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="P29">
-        <v>4.55</v>
+        <v>4.26</v>
       </c>
       <c r="Q29">
-        <v>0.1964</v>
+        <v>0.2353</v>
       </c>
       <c r="R29">
-        <v>0.359</v>
+        <v>0.373</v>
       </c>
       <c r="S29" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="T29">
-        <v>0.2634</v>
+        <v>0.2561</v>
       </c>
       <c r="U29">
-        <v>0.2467</v>
+        <v>0.2265</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>0.237</v>
+        <v>0.2143</v>
       </c>
       <c r="X29">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y29">
-        <v>1.0246</v>
+        <v>1.0571</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3482,22 +3473,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>6.03</v>
+        <v>6.73</v>
       </c>
       <c r="AE29" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="AF29">
-        <v>0.2327</v>
+        <v>0.219</v>
       </c>
       <c r="AG29">
-        <v>1.2076</v>
+        <v>1.1711</v>
       </c>
       <c r="AH29">
         <v>-0.55</v>
       </c>
       <c r="AM29">
-        <v>5.48</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3507,26 +3498,17 @@
       <c r="B30" t="s">
         <v>93</v>
       </c>
-      <c r="C30">
-        <v>7.5</v>
-      </c>
-      <c r="D30">
-        <v>-146</v>
-      </c>
-      <c r="E30">
-        <v>115</v>
-      </c>
       <c r="F30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G30">
-        <v>823986</v>
+        <v>824961</v>
       </c>
       <c r="H30" t="s">
         <v>42</v>
       </c>
       <c r="I30">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3535,46 +3517,46 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>0.2767</v>
+        <v>0.253</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="P30">
-        <v>4.16</v>
+        <v>4.55</v>
       </c>
       <c r="Q30">
-        <v>0.3008</v>
+        <v>0.1964</v>
       </c>
       <c r="R30">
-        <v>0.381</v>
+        <v>0.359</v>
       </c>
       <c r="S30" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="T30">
-        <v>0.2658</v>
+        <v>0.2634</v>
       </c>
       <c r="U30">
-        <v>0.2427</v>
+        <v>0.2467</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2492</v>
+        <v>0.237</v>
       </c>
       <c r="X30">
-        <v>0.2182</v>
+        <v>0.2186</v>
       </c>
       <c r="Y30">
-        <v>1.0306</v>
+        <v>1.0246</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3583,22 +3565,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>9.32</v>
+        <v>6.02</v>
       </c>
       <c r="AE30" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AF30">
-        <v>0.2859</v>
+        <v>0.2327</v>
       </c>
       <c r="AG30">
-        <v>1.2183</v>
+        <v>1.2049</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="AM30">
-        <v>9.32</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3606,19 +3588,19 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31">
+        <v>7.5</v>
+      </c>
+      <c r="D31">
+        <v>-146</v>
+      </c>
+      <c r="E31">
+        <v>115</v>
+      </c>
+      <c r="F31" t="s">
         <v>95</v>
-      </c>
-      <c r="C31">
-        <v>3.5</v>
-      </c>
-      <c r="D31">
-        <v>102</v>
-      </c>
-      <c r="E31">
-        <v>-130</v>
-      </c>
-      <c r="F31" t="s">
-        <v>94</v>
       </c>
       <c r="G31">
         <v>823986</v>
@@ -3627,7 +3609,7 @@
         <v>42</v>
       </c>
       <c r="I31">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -3639,67 +3621,260 @@
         <v>2</v>
       </c>
       <c r="M31">
-        <v>0.1695</v>
+        <v>0.2767</v>
       </c>
       <c r="N31">
         <v>5</v>
       </c>
       <c r="O31">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="P31">
-        <v>4.38</v>
+        <v>4.16</v>
       </c>
       <c r="Q31">
-        <v>0.1509</v>
+        <v>0.3008</v>
       </c>
       <c r="R31">
-        <v>0.346</v>
+        <v>0.381</v>
       </c>
       <c r="S31" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="T31">
-        <v>0.1503</v>
+        <v>0.2658</v>
       </c>
       <c r="U31">
-        <v>0.153</v>
+        <v>0.2427</v>
       </c>
       <c r="V31">
         <v>9</v>
       </c>
       <c r="W31">
+        <v>0.2492</v>
+      </c>
+      <c r="X31">
+        <v>0.2186</v>
+      </c>
+      <c r="Y31">
+        <v>1.0306</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD31">
+        <v>9.3</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF31">
+        <v>0.2859</v>
+      </c>
+      <c r="AG31">
+        <v>1.2157</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>9.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32">
+        <v>3.5</v>
+      </c>
+      <c r="D32">
+        <v>102</v>
+      </c>
+      <c r="E32">
+        <v>-130</v>
+      </c>
+      <c r="F32" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32">
+        <v>823986</v>
+      </c>
+      <c r="H32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32">
+        <v>4.8</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32">
+        <v>0.1695</v>
+      </c>
+      <c r="N32">
+        <v>5</v>
+      </c>
+      <c r="O32">
+        <v>106</v>
+      </c>
+      <c r="P32">
+        <v>4.38</v>
+      </c>
+      <c r="Q32">
+        <v>0.1509</v>
+      </c>
+      <c r="R32">
+        <v>0.346</v>
+      </c>
+      <c r="S32" t="s">
+        <v>56</v>
+      </c>
+      <c r="T32">
+        <v>0.1503</v>
+      </c>
+      <c r="U32">
+        <v>0.153</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
         <v>0.222</v>
       </c>
-      <c r="X31">
+      <c r="X32">
+        <v>0.2186</v>
+      </c>
+      <c r="Y32">
+        <v>0.9978</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD32">
+        <v>2.35</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF32">
+        <v>0.1631</v>
+      </c>
+      <c r="AG32">
+        <v>0.6876</v>
+      </c>
+      <c r="AH32">
+        <v>0.22</v>
+      </c>
+      <c r="AM32">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>97</v>
+      </c>
+      <c r="F33" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33">
+        <v>824874</v>
+      </c>
+      <c r="H33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33">
+        <v>4.9</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0.1606</v>
+      </c>
+      <c r="N33">
+        <v>5</v>
+      </c>
+      <c r="O33">
+        <v>128</v>
+      </c>
+      <c r="P33">
+        <v>4.46</v>
+      </c>
+      <c r="Q33">
+        <v>0.125</v>
+      </c>
+      <c r="R33">
+        <v>0.39</v>
+      </c>
+      <c r="S33" t="s">
+        <v>56</v>
+      </c>
+      <c r="T33">
+        <v>0.225</v>
+      </c>
+      <c r="U33">
+        <v>0.2215</v>
+      </c>
+      <c r="V33">
+        <v>9</v>
+      </c>
+      <c r="W33">
+        <v>0.2205</v>
+      </c>
+      <c r="X33">
         <v>0.2182</v>
       </c>
-      <c r="Y31">
-        <v>0.9978</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD31">
-        <v>2.36</v>
-      </c>
-      <c r="AE31" t="s">
+      <c r="Y33">
+        <v>0.9749</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD33">
+        <v>3.21</v>
+      </c>
+      <c r="AE33" t="s">
         <v>45</v>
       </c>
-      <c r="AF31">
-        <v>0.1631</v>
-      </c>
-      <c r="AG31">
-        <v>0.6891</v>
-      </c>
-      <c r="AH31">
+      <c r="AF33">
+        <v>0.1467</v>
+      </c>
+      <c r="AG33">
+        <v>1.0312</v>
+      </c>
+      <c r="AH33">
         <v>0.22</v>
       </c>
-      <c r="AM31">
-        <v>2.58</v>
+      <c r="AM33">
+        <v>3.43</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -133,175 +133,175 @@
     <t>08/29/2026</t>
   </si>
   <si>
+    <t>Max Fried</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>Alec Gamboa</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Blake Snell</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Erick Fedde</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Toronto Blue Jays</t>
+  </si>
+  <si>
     <t>Merrill Kelly</t>
   </si>
   <si>
     <t>Arizona Diamondbacks @ San Francisco Giants</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>team_season_vs_hand</t>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Daniel Lynch IV</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Bennett Sousa</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Mets</t>
+  </si>
+  <si>
+    <t>Nolan McLean</t>
+  </si>
+  <si>
+    <t>Walker Buehler</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Zach Agnos</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Shane Drohan</t>
+  </si>
+  <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Athletics</t>
+  </si>
+  <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
   </si>
   <si>
     <t>Matt Wilkinson</t>
-  </si>
-  <si>
-    <t>Martin Perez</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>team_season_vs_hand</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Carlos Rodón</t>
-  </si>
-  <si>
-    <t>Max Fried</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Blake Snell</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Erick Fedde</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
-    <t>Daniel Lynch IV</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Bennett Sousa</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Mets</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
-  </si>
-  <si>
-    <t>Nolan McLean</t>
-  </si>
-  <si>
-    <t>Walker Buehler</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
-    <t>Zach Agnos</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Shane Drohan</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Athletics</t>
-  </si>
-  <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
   </si>
   <si>
     <t>Ryan Feltner</t>
@@ -685,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM33"/>
+  <dimension ref="A1:AM34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -821,22 +821,22 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>134</v>
+        <v>-130</v>
       </c>
       <c r="E2">
-        <v>-170</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823177</v>
+        <v>823501</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -848,43 +848,43 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.1492</v>
+        <v>0.238</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="P2">
-        <v>4.38</v>
+        <v>3.85</v>
       </c>
       <c r="Q2">
-        <v>0.1453</v>
+        <v>0.3152</v>
       </c>
       <c r="R2">
-        <v>0.369</v>
+        <v>0.315</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2333</v>
+        <v>0.1883</v>
       </c>
       <c r="U2">
-        <v>0.2173</v>
+        <v>0.1838</v>
       </c>
       <c r="V2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W2">
-        <v>0.2049</v>
+        <v>0.21</v>
       </c>
       <c r="X2">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y2">
-        <v>0.9313</v>
+        <v>0.9794</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -893,22 +893,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.61</v>
+        <v>4.88</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1477</v>
+        <v>0.2623</v>
       </c>
       <c r="AG2">
-        <v>1.0672</v>
+        <v>0.8586</v>
       </c>
       <c r="AH2">
         <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>3.83</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -919,31 +919,73 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>134</v>
+        <v>-116</v>
       </c>
       <c r="E3">
-        <v>-155</v>
+        <v>-106</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" t="s">
-        <v>44</v>
+      <c r="G3">
+        <v>823539</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>5.9</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>0.1984</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>117</v>
+      </c>
+      <c r="P3">
+        <v>3.98</v>
+      </c>
+      <c r="Q3">
+        <v>0.2393</v>
+      </c>
+      <c r="R3">
+        <v>0.369</v>
       </c>
       <c r="S3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="T3">
+        <v>0.2529</v>
+      </c>
+      <c r="U3">
+        <v>0.2729</v>
+      </c>
+      <c r="V3">
+        <v>9</v>
+      </c>
+      <c r="W3">
+        <v>0.2499</v>
+      </c>
+      <c r="X3">
+        <v>0.2193</v>
+      </c>
+      <c r="Y3">
+        <v>1.0351</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -951,8 +993,23 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
+      <c r="AD3">
+        <v>5.94</v>
+      </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF3">
+        <v>0.2135</v>
+      </c>
+      <c r="AG3">
+        <v>1.1531</v>
+      </c>
+      <c r="AH3">
+        <v>0.22</v>
+      </c>
+      <c r="AM3">
+        <v>6.16</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -960,28 +1017,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D4">
-        <v>110</v>
+        <v>-108</v>
       </c>
       <c r="E4">
-        <v>-107</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>824874</v>
+        <v>823539</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -990,46 +1047,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>0.1789</v>
+        <v>0.2551</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="P4">
-        <v>4.12</v>
+        <v>4.19</v>
       </c>
       <c r="Q4">
-        <v>0.1569</v>
+        <v>0.2292</v>
       </c>
       <c r="R4">
-        <v>0.338</v>
+        <v>0.324</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T4">
-        <v>0.241</v>
+        <v>0.1914</v>
       </c>
       <c r="U4">
-        <v>0.2256</v>
+        <v>0.1846</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2484</v>
+        <v>0.21</v>
       </c>
       <c r="X4">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y4">
-        <v>1.0258</v>
+        <v>0.9697</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1038,22 +1095,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.03</v>
+        <v>4.3</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1715</v>
+        <v>0.2467</v>
       </c>
       <c r="AG4">
-        <v>1.1021</v>
+        <v>0.8729</v>
       </c>
       <c r="AH4">
         <v>0.22</v>
       </c>
       <c r="AM4">
-        <v>4.25</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1063,68 +1120,65 @@
       <c r="B5" t="s">
         <v>49</v>
       </c>
-      <c r="C5">
-        <v>3.5</v>
-      </c>
-      <c r="D5">
-        <v>-138</v>
-      </c>
-      <c r="E5">
-        <v>110</v>
-      </c>
       <c r="F5" t="s">
         <v>41</v>
       </c>
       <c r="G5">
-        <v>823176</v>
+        <v>823501</v>
       </c>
       <c r="H5" t="s">
         <v>50</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.1591</v>
+        <v>0.175</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>4.44</v>
+        <v>3.87</v>
       </c>
       <c r="Q5">
-        <v>0.1818</v>
+        <v>0.25</v>
       </c>
       <c r="R5">
-        <v>0.331</v>
+        <v>0.02</v>
       </c>
       <c r="S5" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="T5">
+        <v>0.2426</v>
+      </c>
+      <c r="U5">
+        <v>0.2535</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2353</v>
+        <v>0.2499</v>
       </c>
       <c r="X5">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y5">
-        <v>1.0233</v>
+        <v>1.0025</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1133,22 +1187,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.47</v>
+        <v>1.01</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1666</v>
+        <v>0.1765</v>
       </c>
       <c r="AG5">
-        <v>1.0398</v>
+        <v>1.1062</v>
       </c>
       <c r="AH5">
         <v>0.22</v>
       </c>
       <c r="AM5">
-        <v>3.69</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1156,28 +1210,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6">
+        <v>6.5</v>
+      </c>
+      <c r="D6">
+        <v>-120</v>
+      </c>
+      <c r="E6">
+        <v>-105</v>
+      </c>
+      <c r="F6" t="s">
         <v>52</v>
       </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-      <c r="D6">
-        <v>-116</v>
-      </c>
-      <c r="E6">
-        <v>-106</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
       <c r="G6">
-        <v>823539</v>
+        <v>824230</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1186,46 +1240,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>0.1967</v>
+        <v>0.3303</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P6">
-        <v>3.99</v>
+        <v>4.19</v>
       </c>
       <c r="Q6">
-        <v>0.2364</v>
+        <v>0.3303</v>
       </c>
       <c r="R6">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T6">
-        <v>0.2529</v>
+        <v>0.2179</v>
       </c>
       <c r="U6">
-        <v>0.2729</v>
+        <v>0.211</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2486</v>
+        <v>0.2313</v>
       </c>
       <c r="X6">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y6">
-        <v>1.0351</v>
+        <v>0.9742</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1234,22 +1288,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>5.77</v>
+        <v>6.97</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AF6">
-        <v>0.2108</v>
+        <v>0.3303</v>
       </c>
       <c r="AG6">
-        <v>1.1567</v>
+        <v>0.9936</v>
       </c>
       <c r="AH6">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM6">
-        <v>5.99</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1260,25 +1314,25 @@
         <v>54</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
         <v>-108</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>-115</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7">
-        <v>823539</v>
+        <v>824230</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1287,46 +1341,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>0.2551</v>
+        <v>0.1655</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="P7">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>0.2292</v>
+        <v>0.115</v>
       </c>
       <c r="R7">
-        <v>0.324</v>
+        <v>0.361</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T7">
-        <v>0.1914</v>
+        <v>0.2129</v>
       </c>
       <c r="U7">
-        <v>0.1846</v>
+        <v>0.2125</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2101</v>
+        <v>0.2058</v>
       </c>
       <c r="X7">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y7">
-        <v>0.9697</v>
+        <v>0.991</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1335,22 +1389,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.31</v>
+        <v>3.21</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2467</v>
+        <v>0.1473</v>
       </c>
       <c r="AG7">
-        <v>0.8756</v>
+        <v>0.9708</v>
       </c>
       <c r="AH7">
         <v>0.22</v>
       </c>
       <c r="AM7">
-        <v>4.53</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1361,16 +1415,16 @@
         <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>823501</v>
+        <v>823665</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1382,43 +1436,43 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0.238</v>
+        <v>0.1654</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="P8">
-        <v>3.85</v>
+        <v>4.31</v>
       </c>
       <c r="Q8">
-        <v>0.3152</v>
+        <v>0.2211</v>
       </c>
       <c r="R8">
-        <v>0.315</v>
+        <v>0.322</v>
       </c>
       <c r="S8" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="T8">
-        <v>0.1883</v>
+        <v>0.2021</v>
       </c>
       <c r="U8">
-        <v>0.1838</v>
+        <v>0.1907</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2101</v>
+        <v>0.2072</v>
       </c>
       <c r="X8">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y8">
-        <v>0.9794</v>
+        <v>0.936</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1427,22 +1481,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.9</v>
+        <v>3.29</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2623</v>
+        <v>0.1833</v>
       </c>
       <c r="AG8">
-        <v>0.8613</v>
+        <v>0.9215</v>
       </c>
       <c r="AH8">
         <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>5.12</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1452,26 +1506,17 @@
       <c r="B9" t="s">
         <v>57</v>
       </c>
-      <c r="C9">
-        <v>6.5</v>
-      </c>
-      <c r="D9">
-        <v>-120</v>
-      </c>
-      <c r="E9">
-        <v>-105</v>
-      </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>824230</v>
+        <v>823665</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1480,46 +1525,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>0.3241</v>
+        <v>0.1656</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="P9">
         <v>4.21</v>
       </c>
       <c r="Q9">
-        <v>0.3271</v>
+        <v>0.1441</v>
       </c>
       <c r="R9">
-        <v>0.349</v>
+        <v>0.357</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T9">
-        <v>0.2179</v>
+        <v>0.2522</v>
       </c>
       <c r="U9">
-        <v>0.211</v>
+        <v>0.2525</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2294</v>
+        <v>0.2363</v>
       </c>
       <c r="X9">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y9">
-        <v>0.9742</v>
+        <v>1.0323</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1528,22 +1573,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>6.82</v>
+        <v>4.26</v>
       </c>
       <c r="AE9" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.3251</v>
+        <v>0.158</v>
       </c>
       <c r="AG9">
-        <v>0.9967</v>
+        <v>1.1501</v>
       </c>
       <c r="AH9">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM9">
-        <v>6.27</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1551,76 +1596,67 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10">
-        <v>3.5</v>
-      </c>
-      <c r="D10">
-        <v>-108</v>
-      </c>
-      <c r="E10">
-        <v>-115</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10">
-        <v>824230</v>
+        <v>823011</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I10">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.1667</v>
+        <v>0.25</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="P10">
-        <v>3.98</v>
+        <v>4.09</v>
       </c>
       <c r="Q10">
-        <v>0.1193</v>
+        <v>0.2609</v>
       </c>
       <c r="R10">
-        <v>0.353</v>
+        <v>0.187</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T10">
-        <v>0.2129</v>
+        <v>0.2511</v>
       </c>
       <c r="U10">
-        <v>0.2125</v>
+        <v>0.2169</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2062</v>
+        <v>0.2158</v>
       </c>
       <c r="X10">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y10">
-        <v>0.991</v>
+        <v>0.8961</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1629,22 +1665,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.26</v>
+        <v>2.47</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1499</v>
+        <v>0.252</v>
       </c>
       <c r="AG10">
-        <v>0.9738</v>
+        <v>1.1448</v>
       </c>
       <c r="AH10">
         <v>0.22</v>
       </c>
       <c r="AM10">
-        <v>3.48</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1652,19 +1688,19 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G11">
-        <v>823665</v>
+        <v>823011</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1676,43 +1712,43 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.1631</v>
+        <v>0.2165</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="P11">
-        <v>4.34</v>
+        <v>4.21</v>
       </c>
       <c r="Q11">
-        <v>0.2237</v>
+        <v>0.3034</v>
       </c>
       <c r="R11">
-        <v>0.275</v>
+        <v>0.308</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T11">
-        <v>0.2021</v>
+        <v>0.2509</v>
       </c>
       <c r="U11">
-        <v>0.1907</v>
+        <v>0.2463</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2072</v>
+        <v>0.2373</v>
       </c>
       <c r="X11">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y11">
-        <v>0.936</v>
+        <v>1.0293</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1721,22 +1757,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>2.99</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AF11">
-        <v>0.1798</v>
+        <v>0.2433</v>
       </c>
       <c r="AG11">
-        <v>0.9244</v>
+        <v>1.144</v>
       </c>
       <c r="AH11">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM11">
-        <v>3.21</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1744,19 +1780,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>3.5</v>
+      </c>
+      <c r="D12">
+        <v>-156</v>
+      </c>
+      <c r="E12">
+        <v>126</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
       </c>
       <c r="G12">
-        <v>823665</v>
+        <v>824637</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1765,46 +1810,46 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>0.162</v>
+        <v>0.1772</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="P12">
-        <v>4.23</v>
+        <v>4.38</v>
       </c>
       <c r="Q12">
-        <v>0.1237</v>
+        <v>0.1653</v>
       </c>
       <c r="R12">
-        <v>0.327</v>
+        <v>0.377</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T12">
-        <v>0.2522</v>
+        <v>0.1662</v>
       </c>
       <c r="U12">
-        <v>0.2525</v>
+        <v>0.1874</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2363</v>
+        <v>0.2192</v>
       </c>
       <c r="X12">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y12">
-        <v>1.0323</v>
+        <v>0.8905</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1813,22 +1858,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.92</v>
+        <v>2.7</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.1495</v>
+        <v>0.1727</v>
       </c>
       <c r="AG12">
-        <v>1.1536</v>
+        <v>0.7579</v>
       </c>
       <c r="AH12">
         <v>0.22</v>
       </c>
       <c r="AM12">
-        <v>4.14</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1836,67 +1881,76 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="C13">
+        <v>6.5</v>
+      </c>
+      <c r="D13">
+        <v>112</v>
+      </c>
+      <c r="E13">
+        <v>-130</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G13">
-        <v>823011</v>
+        <v>824637</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="I13">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>0.2508</v>
+        <v>0.2378</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="P13">
-        <v>4.09</v>
+        <v>4.22</v>
       </c>
       <c r="Q13">
-        <v>0.2683</v>
+        <v>0.25</v>
       </c>
       <c r="R13">
-        <v>0.17</v>
+        <v>0.367</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T13">
-        <v>0.2511</v>
+        <v>0.2556</v>
       </c>
       <c r="U13">
-        <v>0.2169</v>
+        <v>0.2652</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2158</v>
+        <v>0.2542</v>
       </c>
       <c r="X13">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y13">
-        <v>0.8961</v>
+        <v>1.12</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1905,22 +1959,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>2.29</v>
+        <v>7.41</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="AF13">
-        <v>0.2538</v>
+        <v>0.2423</v>
       </c>
       <c r="AG13">
-        <v>1.1484</v>
+        <v>1.1655</v>
       </c>
       <c r="AH13">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>2.51</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1928,19 +1982,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="C14">
+        <v>5.5</v>
+      </c>
+      <c r="D14">
+        <v>102</v>
+      </c>
+      <c r="E14">
+        <v>-130</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14">
-        <v>823011</v>
+        <v>822770</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1949,46 +2012,46 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>0.216</v>
+        <v>0.2349</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="P14">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="Q14">
-        <v>0.3125</v>
+        <v>0.1667</v>
       </c>
       <c r="R14">
-        <v>0.286</v>
+        <v>0.338</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T14">
-        <v>0.2509</v>
+        <v>0.2675</v>
       </c>
       <c r="U14">
-        <v>0.2463</v>
+        <v>0.233</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2373</v>
+        <v>0.2259</v>
       </c>
       <c r="X14">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y14">
-        <v>1.0293</v>
+        <v>0.9726</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1997,22 +2060,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.94</v>
+        <v>5.71</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2436</v>
+        <v>0.2119</v>
       </c>
       <c r="AG14">
-        <v>1.1476</v>
+        <v>1.2198</v>
       </c>
       <c r="AH14">
         <v>0.22</v>
       </c>
       <c r="AM14">
-        <v>6.16</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2020,28 +2083,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15">
+        <v>4.5</v>
+      </c>
+      <c r="D15">
+        <v>134</v>
+      </c>
+      <c r="E15">
+        <v>-170</v>
+      </c>
+      <c r="F15" t="s">
         <v>68</v>
       </c>
-      <c r="C15">
-        <v>3.5</v>
-      </c>
-      <c r="D15">
-        <v>-156</v>
-      </c>
-      <c r="E15">
-        <v>126</v>
-      </c>
-      <c r="F15" t="s">
-        <v>69</v>
-      </c>
       <c r="G15">
-        <v>824637</v>
+        <v>823177</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2050,46 +2113,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1792</v>
+        <v>0.1498</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="P15">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="Q15">
-        <v>0.1776</v>
+        <v>0.1354</v>
       </c>
       <c r="R15">
-        <v>0.349</v>
+        <v>0.324</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T15">
-        <v>0.1662</v>
+        <v>0.2333</v>
       </c>
       <c r="U15">
-        <v>0.1874</v>
+        <v>0.2173</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2192</v>
+        <v>0.2049</v>
       </c>
       <c r="X15">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y15">
-        <v>0.8905</v>
+        <v>0.9313</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2098,22 +2161,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1787</v>
+        <v>0.1452</v>
       </c>
       <c r="AG15">
-        <v>0.7603</v>
+        <v>1.0639</v>
       </c>
       <c r="AH15">
         <v>0.22</v>
       </c>
       <c r="AM15">
-        <v>2.97</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2121,28 +2184,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16">
+        <v>3.5</v>
+      </c>
+      <c r="D16">
+        <v>-138</v>
+      </c>
+      <c r="E16">
+        <v>110</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16">
+        <v>823176</v>
+      </c>
+      <c r="H16" t="s">
         <v>70</v>
       </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-      <c r="D16">
-        <v>112</v>
-      </c>
-      <c r="E16">
-        <v>-130</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16">
-        <v>824637</v>
-      </c>
-      <c r="H16" t="s">
-        <v>42</v>
-      </c>
       <c r="I16">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2151,46 +2214,40 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M16">
-        <v>0.2374</v>
+        <v>0.1591</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="P16">
-        <v>4.2</v>
+        <v>4.44</v>
       </c>
       <c r="Q16">
-        <v>0.25</v>
+        <v>0.1818</v>
       </c>
       <c r="R16">
-        <v>0.324</v>
+        <v>0.331</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
-      </c>
-      <c r="T16">
-        <v>0.2556</v>
-      </c>
-      <c r="U16">
-        <v>0.2652</v>
+        <v>71</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>0.2542</v>
+        <v>0.2353</v>
       </c>
       <c r="X16">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y16">
-        <v>1.12</v>
+        <v>1.0233</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2199,22 +2256,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>7.18</v>
+        <v>3.47</v>
       </c>
       <c r="AE16" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.2415</v>
+        <v>0.1666</v>
       </c>
       <c r="AG16">
-        <v>1.1691</v>
+        <v>1.0394</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AM16">
-        <v>7.18</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2225,25 +2282,25 @@
         <v>72</v>
       </c>
       <c r="C17">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D17">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="E17">
-        <v>-130</v>
+        <v>-150</v>
       </c>
       <c r="F17" t="s">
         <v>73</v>
       </c>
       <c r="G17">
-        <v>822770</v>
+        <v>822690</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2252,46 +2309,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>0.2371</v>
+        <v>0.1798</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P17">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="Q17">
-        <v>0.1875</v>
+        <v>0.1504</v>
       </c>
       <c r="R17">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T17">
-        <v>0.2675</v>
+        <v>0.2314</v>
       </c>
       <c r="U17">
-        <v>0.233</v>
+        <v>0.2363</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2259</v>
+        <v>0.2064</v>
       </c>
       <c r="X17">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y17">
-        <v>0.9726</v>
+        <v>0.9921</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2300,22 +2357,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>6.05</v>
+        <v>4.65</v>
       </c>
       <c r="AE17" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.2193</v>
+        <v>0.1692</v>
       </c>
       <c r="AG17">
-        <v>1.2236</v>
+        <v>1.055</v>
       </c>
       <c r="AH17">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM17">
-        <v>5.5</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2326,16 +2383,16 @@
         <v>74</v>
       </c>
       <c r="C18">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D18">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="E18">
-        <v>-150</v>
+        <v>-128</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>822690</v>
@@ -2344,7 +2401,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2356,43 +2413,43 @@
         <v>2</v>
       </c>
       <c r="M18">
-        <v>0.181</v>
+        <v>0.273</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="P18">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="Q18">
-        <v>0.1667</v>
+        <v>0.375</v>
       </c>
       <c r="R18">
-        <v>0.398</v>
+        <v>0.342</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T18">
-        <v>0.2314</v>
+        <v>0.2086</v>
       </c>
       <c r="U18">
-        <v>0.2363</v>
+        <v>0.1957</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2064</v>
+        <v>0.2107</v>
       </c>
       <c r="X18">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y18">
-        <v>0.9921</v>
+        <v>0.9439</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2401,22 +2458,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.98</v>
+        <v>6.01</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AF18">
-        <v>0.1753</v>
+        <v>0.3079</v>
       </c>
       <c r="AG18">
-        <v>1.0583</v>
+        <v>0.9513</v>
       </c>
       <c r="AH18">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM18">
-        <v>5.2</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2424,76 +2481,76 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19">
+        <v>2.5</v>
+      </c>
+      <c r="D19">
+        <v>-120</v>
+      </c>
+      <c r="E19">
+        <v>-107</v>
+      </c>
+      <c r="F19" t="s">
         <v>76</v>
       </c>
-      <c r="C19">
-        <v>6.5</v>
-      </c>
-      <c r="D19">
-        <v>100</v>
-      </c>
-      <c r="E19">
-        <v>-128</v>
-      </c>
-      <c r="F19" t="s">
-        <v>75</v>
-      </c>
       <c r="G19">
-        <v>822690</v>
+        <v>824392</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I19">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>0.2708</v>
+        <v>0.1849</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
       <c r="Q19">
-        <v>0.3223</v>
+        <v>0.1636</v>
       </c>
       <c r="R19">
-        <v>0.377</v>
+        <v>0.216</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T19">
-        <v>0.2086</v>
+        <v>0.1994</v>
       </c>
       <c r="U19">
-        <v>0.1957</v>
+        <v>0.1738</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2107</v>
+        <v>0.2241</v>
       </c>
       <c r="X19">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y19">
-        <v>0.9439</v>
+        <v>0.88</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2502,22 +2559,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.83</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2902</v>
+        <v>0.1803</v>
       </c>
       <c r="AG19">
-        <v>0.9543</v>
+        <v>0.9091</v>
       </c>
       <c r="AH19">
         <v>0.22</v>
       </c>
       <c r="AM19">
-        <v>6.05</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2528,28 +2585,28 @@
         <v>77</v>
       </c>
       <c r="C20">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D20">
-        <v>-120</v>
+        <v>-119</v>
       </c>
       <c r="E20">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G20">
         <v>824392</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -2558,43 +2615,43 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>0.183</v>
+        <v>0.2201</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="P20">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="Q20">
-        <v>0.1538</v>
+        <v>0.2151</v>
       </c>
       <c r="R20">
-        <v>0.206</v>
+        <v>0.317</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T20">
-        <v>0.1994</v>
+        <v>0.2084</v>
       </c>
       <c r="U20">
-        <v>0.1738</v>
+        <v>0.207</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2241</v>
+        <v>0.2139</v>
       </c>
       <c r="X20">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y20">
-        <v>0.88</v>
+        <v>1.0087</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2603,22 +2660,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>1.72</v>
+        <v>4.79</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.177</v>
+        <v>0.2185</v>
       </c>
       <c r="AG20">
-        <v>0.9119</v>
+        <v>0.95</v>
       </c>
       <c r="AH20">
         <v>0.22</v>
       </c>
       <c r="AM20">
-        <v>1.94</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2626,76 +2683,67 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" t="s">
         <v>79</v>
       </c>
-      <c r="C21">
-        <v>5.5</v>
-      </c>
-      <c r="D21">
-        <v>-119</v>
-      </c>
-      <c r="E21">
-        <v>-108</v>
-      </c>
-      <c r="F21" t="s">
-        <v>78</v>
-      </c>
       <c r="G21">
-        <v>824392</v>
+        <v>823582</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I21">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0.2258</v>
+      </c>
+      <c r="N21">
         <v>1</v>
       </c>
-      <c r="M21">
-        <v>0.2209</v>
-      </c>
-      <c r="N21">
+      <c r="O21">
         <v>5</v>
       </c>
-      <c r="O21">
-        <v>112</v>
-      </c>
       <c r="P21">
-        <v>4.09</v>
+        <v>4.8</v>
       </c>
       <c r="Q21">
-        <v>0.1964</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>0.359</v>
+        <v>0.024</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T21">
-        <v>0.2084</v>
+        <v>0.2425</v>
       </c>
       <c r="U21">
-        <v>0.207</v>
+        <v>0.237</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2139</v>
+        <v>0.2339</v>
       </c>
       <c r="X21">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y21">
-        <v>1.0087</v>
+        <v>0.9768</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2704,22 +2752,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.79</v>
+        <v>1.14</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2121</v>
+        <v>0.2203</v>
       </c>
       <c r="AG21">
-        <v>0.953</v>
+        <v>1.1059</v>
       </c>
       <c r="AH21">
         <v>0.22</v>
       </c>
       <c r="AM21">
-        <v>5.01</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2729,53 +2777,74 @@
       <c r="B22" t="s">
         <v>80</v>
       </c>
+      <c r="C22">
+        <v>5.5</v>
+      </c>
+      <c r="D22">
+        <v>-148</v>
+      </c>
+      <c r="E22">
+        <v>116</v>
+      </c>
       <c r="F22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G22">
         <v>823582</v>
       </c>
       <c r="H22" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="I22">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22">
-        <v>0.2386</v>
+        <v>0.2697</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>101</v>
       </c>
       <c r="P22">
-        <v>4.71</v>
+        <v>4.16</v>
+      </c>
+      <c r="Q22">
+        <v>0.198</v>
+      </c>
+      <c r="R22">
+        <v>0.336</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T22">
-        <v>0.2425</v>
+        <v>0.2057</v>
       </c>
       <c r="U22">
-        <v>0.237</v>
+        <v>0.2018</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2339</v>
+        <v>0.2191</v>
       </c>
       <c r="X22">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y22">
-        <v>0.9768</v>
+        <v>0.9509</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2784,22 +2853,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.49</v>
+        <v>5.05</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2386</v>
+        <v>0.2456</v>
       </c>
       <c r="AG22">
-        <v>1.1094</v>
+        <v>0.9377</v>
       </c>
       <c r="AH22">
         <v>0.22</v>
       </c>
       <c r="AM22">
-        <v>5.71</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2807,28 +2876,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C23">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D23">
-        <v>-148</v>
+        <v>106</v>
       </c>
       <c r="E23">
-        <v>116</v>
+        <v>-122</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G23">
-        <v>823582</v>
+        <v>822936</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2837,46 +2906,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M23">
-        <v>0.2718</v>
+        <v>0.1985</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="P23">
-        <v>4.16</v>
+        <v>4.27</v>
       </c>
       <c r="Q23">
-        <v>0.2131</v>
+        <v>0.1798</v>
       </c>
       <c r="R23">
-        <v>0.379</v>
+        <v>0.308</v>
       </c>
       <c r="S23" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T23">
-        <v>0.2057</v>
+        <v>0.1524</v>
       </c>
       <c r="U23">
-        <v>0.2018</v>
+        <v>0.1519</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2191</v>
+        <v>0.1865</v>
       </c>
       <c r="X23">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y23">
-        <v>0.9509</v>
+        <v>0.88</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2885,22 +2954,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.31</v>
+        <v>2.37</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2496</v>
+        <v>0.1928</v>
       </c>
       <c r="AG23">
-        <v>0.9406</v>
+        <v>0.6947</v>
       </c>
       <c r="AH23">
         <v>0.22</v>
       </c>
       <c r="AM23">
-        <v>5.53</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2908,19 +2977,19 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24">
         <v>3.5</v>
       </c>
       <c r="D24">
-        <v>106</v>
+        <v>-110</v>
       </c>
       <c r="E24">
-        <v>-122</v>
+        <v>-111</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G24">
         <v>822936</v>
@@ -2929,7 +2998,7 @@
         <v>42</v>
       </c>
       <c r="I24">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2941,43 +3010,43 @@
         <v>3</v>
       </c>
       <c r="M24">
-        <v>0.2007</v>
+        <v>0.1481</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P24">
-        <v>4.26</v>
+        <v>4.02</v>
       </c>
       <c r="Q24">
-        <v>0.1635</v>
+        <v>0.1881</v>
       </c>
       <c r="R24">
-        <v>0.342</v>
+        <v>0.336</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T24">
-        <v>0.1524</v>
+        <v>0.1918</v>
       </c>
       <c r="U24">
-        <v>0.1519</v>
+        <v>0.1995</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.1865</v>
+        <v>0.2154</v>
       </c>
       <c r="X24">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y24">
-        <v>0.88</v>
+        <v>1.0075</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2986,22 +3055,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>2.39</v>
+        <v>3.29</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.188</v>
+        <v>0.1615</v>
       </c>
       <c r="AG24">
-        <v>0.6968</v>
+        <v>0.8745</v>
       </c>
       <c r="AH24">
         <v>0.22</v>
       </c>
       <c r="AM24">
-        <v>2.61</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3009,28 +3078,19 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25">
-        <v>3.5</v>
-      </c>
-      <c r="D25">
-        <v>-110</v>
-      </c>
-      <c r="E25">
-        <v>-111</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
         <v>85</v>
       </c>
       <c r="G25">
-        <v>822936</v>
+        <v>824874</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="I25">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3039,46 +3099,46 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>0.1467</v>
+        <v>0.1522</v>
       </c>
       <c r="N25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O25">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="P25">
-        <v>4.02</v>
+        <v>4.41</v>
       </c>
       <c r="Q25">
-        <v>0.1667</v>
+        <v>0.1563</v>
       </c>
       <c r="R25">
-        <v>0.375</v>
+        <v>0.138</v>
       </c>
       <c r="S25" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T25">
-        <v>0.1918</v>
+        <v>0.2331</v>
       </c>
       <c r="U25">
-        <v>0.1995</v>
+        <v>0.2231</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2154</v>
+        <v>0.2205</v>
       </c>
       <c r="X25">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y25">
-        <v>1.0075</v>
+        <v>0.988</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3087,22 +3147,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>3.23</v>
+        <v>2.83</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.1542</v>
+        <v>0.1528</v>
       </c>
       <c r="AG25">
-        <v>0.8773</v>
+        <v>1.063</v>
       </c>
       <c r="AH25">
         <v>0.22</v>
       </c>
       <c r="AM25">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3110,19 +3170,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="C26">
+        <v>4.5</v>
+      </c>
+      <c r="D26">
+        <v>110</v>
+      </c>
+      <c r="E26">
+        <v>-107</v>
       </c>
       <c r="F26" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="G26">
         <v>824874</v>
       </c>
       <c r="H26" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3131,46 +3200,46 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1522</v>
+        <v>0.1775</v>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="P26">
-        <v>4.41</v>
+        <v>4.12</v>
       </c>
       <c r="Q26">
-        <v>0.1563</v>
+        <v>0.125</v>
       </c>
       <c r="R26">
-        <v>0.138</v>
+        <v>0.286</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T26">
-        <v>0.2331</v>
+        <v>0.241</v>
       </c>
       <c r="U26">
-        <v>0.2231</v>
+        <v>0.2256</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2205</v>
+        <v>0.2484</v>
       </c>
       <c r="X26">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y26">
-        <v>0.988</v>
+        <v>1.0258</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3179,22 +3248,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>2.84</v>
+        <v>3.66</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.1528</v>
+        <v>0.1625</v>
       </c>
       <c r="AG26">
-        <v>1.0663</v>
+        <v>1.0987</v>
       </c>
       <c r="AH26">
         <v>0.22</v>
       </c>
       <c r="AM26">
-        <v>3.06</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3202,7 +3271,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3214,7 +3283,7 @@
         <v>-170</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>823741</v>
@@ -3253,13 +3322,13 @@
         <v>0.363</v>
       </c>
       <c r="S27" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="T27">
-        <v>0.2081</v>
+        <v>0.2241</v>
       </c>
       <c r="U27">
-        <v>0.2138</v>
+        <v>0.2201</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -3268,10 +3337,10 @@
         <v>0.2135</v>
       </c>
       <c r="X27">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y27">
-        <v>0.9955</v>
+        <v>1.0476</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3280,7 +3349,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.93</v>
+        <v>4.44</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
@@ -3289,13 +3358,13 @@
         <v>0.1988</v>
       </c>
       <c r="AG27">
-        <v>0.9519</v>
+        <v>1.0217</v>
       </c>
       <c r="AH27">
         <v>0.22</v>
       </c>
       <c r="AM27">
-        <v>4.15</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3303,7 +3372,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -3315,7 +3384,7 @@
         <v>-113</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G28">
         <v>823741</v>
@@ -3354,25 +3423,25 @@
         <v>0.371</v>
       </c>
       <c r="S28" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="T28">
-        <v>0.2381</v>
+        <v>0.2284</v>
       </c>
       <c r="U28">
-        <v>0.2401</v>
+        <v>0.2271</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>0.2412</v>
       </c>
       <c r="X28">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y28">
-        <v>1.039</v>
+        <v>1.0739</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3381,7 +3450,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.81</v>
+        <v>5.74</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3390,13 +3459,13 @@
         <v>0.2322</v>
       </c>
       <c r="AG28">
-        <v>1.0891</v>
+        <v>1.0416</v>
       </c>
       <c r="AH28">
         <v>0.22</v>
       </c>
       <c r="AM28">
-        <v>6.03</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3404,10 +3473,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" t="s">
         <v>91</v>
-      </c>
-      <c r="F29" t="s">
-        <v>92</v>
       </c>
       <c r="G29">
         <v>824961</v>
@@ -3446,7 +3515,7 @@
         <v>0.373</v>
       </c>
       <c r="S29" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T29">
         <v>0.2561</v>
@@ -3461,7 +3530,7 @@
         <v>0.2143</v>
       </c>
       <c r="X29">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y29">
         <v>1.0571</v>
@@ -3473,22 +3542,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>6.73</v>
+        <v>6.71</v>
       </c>
       <c r="AE29" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="AF29">
         <v>0.219</v>
       </c>
       <c r="AG29">
-        <v>1.1711</v>
+        <v>1.1675</v>
       </c>
       <c r="AH29">
         <v>-0.55</v>
       </c>
       <c r="AM29">
-        <v>6.18</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3496,10 +3565,10 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>824961</v>
@@ -3538,7 +3607,7 @@
         <v>0.359</v>
       </c>
       <c r="S30" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T30">
         <v>0.2634</v>
@@ -3553,7 +3622,7 @@
         <v>0.237</v>
       </c>
       <c r="X30">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y30">
         <v>1.0246</v>
@@ -3565,22 +3634,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="AF30">
         <v>0.2327</v>
       </c>
       <c r="AG30">
-        <v>1.2049</v>
+        <v>1.2012</v>
       </c>
       <c r="AH30">
         <v>-0.55</v>
       </c>
       <c r="AM30">
-        <v>5.47</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3588,7 +3657,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31">
         <v>7.5</v>
@@ -3600,7 +3669,7 @@
         <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G31">
         <v>823986</v>
@@ -3639,7 +3708,7 @@
         <v>0.381</v>
       </c>
       <c r="S31" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T31">
         <v>0.2658</v>
@@ -3654,7 +3723,7 @@
         <v>0.2492</v>
       </c>
       <c r="X31">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y31">
         <v>1.0306</v>
@@ -3666,22 +3735,22 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>9.3</v>
+        <v>9.27</v>
       </c>
       <c r="AE31" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="AF31">
         <v>0.2859</v>
       </c>
       <c r="AG31">
-        <v>1.2157</v>
+        <v>1.2119</v>
       </c>
       <c r="AH31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>9.3</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3689,7 +3758,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -3701,7 +3770,7 @@
         <v>-130</v>
       </c>
       <c r="F32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G32">
         <v>823986</v>
@@ -3740,7 +3809,7 @@
         <v>0.346</v>
       </c>
       <c r="S32" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T32">
         <v>0.1503</v>
@@ -3755,7 +3824,7 @@
         <v>0.222</v>
       </c>
       <c r="X32">
-        <v>0.2186</v>
+        <v>0.2193</v>
       </c>
       <c r="Y32">
         <v>0.9978</v>
@@ -3767,7 +3836,7 @@
         <v>44</v>
       </c>
       <c r="AD32">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AE32" t="s">
         <v>45</v>
@@ -3776,13 +3845,13 @@
         <v>0.1631</v>
       </c>
       <c r="AG32">
-        <v>0.6876</v>
+        <v>0.6854</v>
       </c>
       <c r="AH32">
         <v>0.22</v>
       </c>
       <c r="AM32">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3790,90 +3859,134 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33">
+        <v>3.5</v>
+      </c>
+      <c r="D33">
+        <v>134</v>
+      </c>
+      <c r="E33">
+        <v>-155</v>
+      </c>
+      <c r="F33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" t="s">
+        <v>44</v>
+      </c>
+      <c r="L33">
+        <v>6</v>
+      </c>
+      <c r="S33" t="s">
+        <v>44</v>
+      </c>
+      <c r="V33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
         <v>97</v>
       </c>
-      <c r="F33" t="s">
-        <v>48</v>
-      </c>
-      <c r="G33">
+      <c r="F34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34">
         <v>824874</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H34" t="s">
         <v>42</v>
       </c>
-      <c r="I33">
+      <c r="I34">
         <v>4.9</v>
       </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>0.1606</v>
       </c>
-      <c r="N33">
+      <c r="N34">
         <v>5</v>
       </c>
-      <c r="O33">
+      <c r="O34">
         <v>128</v>
       </c>
-      <c r="P33">
+      <c r="P34">
         <v>4.46</v>
       </c>
-      <c r="Q33">
+      <c r="Q34">
         <v>0.125</v>
       </c>
-      <c r="R33">
+      <c r="R34">
         <v>0.39</v>
       </c>
-      <c r="S33" t="s">
-        <v>56</v>
-      </c>
-      <c r="T33">
+      <c r="S34" t="s">
+        <v>43</v>
+      </c>
+      <c r="T34">
         <v>0.225</v>
       </c>
-      <c r="U33">
+      <c r="U34">
         <v>0.2215</v>
       </c>
-      <c r="V33">
+      <c r="V34">
         <v>9</v>
       </c>
-      <c r="W33">
+      <c r="W34">
         <v>0.2205</v>
       </c>
-      <c r="X33">
+      <c r="X34">
         <v>0.2182</v>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <v>0.9749</v>
       </c>
-      <c r="AA33" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD33">
+      <c r="AA34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD34">
         <v>3.21</v>
       </c>
-      <c r="AE33" t="s">
+      <c r="AE34" t="s">
         <v>45</v>
       </c>
-      <c r="AF33">
+      <c r="AF34">
         <v>0.1467</v>
       </c>
-      <c r="AG33">
+      <c r="AG34">
         <v>1.0312</v>
       </c>
-      <c r="AH33">
+      <c r="AH34">
         <v>0.22</v>
       </c>
-      <c r="AM33">
+      <c r="AM34">
         <v>3.43</v>
       </c>
     </row>

--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -133,160 +133,160 @@
     <t>08/29/2026</t>
   </si>
   <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>Alec Gamboa</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
     <t>Max Fried</t>
   </si>
   <si>
-    <t>Boston Red Sox @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
+    <t>Blake Snell</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Erick Fedde</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>team_season_vs_hand</t>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Daniel Lynch IV</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Bennett Sousa</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Mets</t>
+  </si>
+  <si>
+    <t>Nolan McLean</t>
+  </si>
+  <si>
+    <t>Walker Buehler</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Zach Agnos</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Shane Drohan</t>
+  </si>
+  <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Athletics</t>
   </si>
   <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>Carlos Rodón</t>
-  </si>
-  <si>
-    <t>Alec Gamboa</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Blake Snell</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Erick Fedde</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>team_season_vs_hand</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
-    <t>Daniel Lynch IV</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Bennett Sousa</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Mets</t>
-  </si>
-  <si>
-    <t>Nolan McLean</t>
-  </si>
-  <si>
-    <t>Walker Buehler</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
-    <t>Zach Agnos</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Shane Drohan</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Athletics</t>
   </si>
   <si>
     <t>Jack Perkins</t>
@@ -821,22 +821,22 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-130</v>
+        <v>-116</v>
       </c>
       <c r="E2">
-        <v>105</v>
+        <v>-106</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823501</v>
+        <v>823539</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -845,46 +845,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>0.238</v>
+        <v>0.1984</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="P2">
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="Q2">
-        <v>0.3152</v>
+        <v>0.2393</v>
       </c>
       <c r="R2">
-        <v>0.315</v>
+        <v>0.369</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1883</v>
+        <v>0.2529</v>
       </c>
       <c r="U2">
-        <v>0.1838</v>
+        <v>0.2729</v>
       </c>
       <c r="V2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W2">
-        <v>0.21</v>
+        <v>0.2499</v>
       </c>
       <c r="X2">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y2">
-        <v>0.9794</v>
+        <v>1.0351</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -893,22 +893,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.88</v>
+        <v>5.9</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2623</v>
+        <v>0.2135</v>
       </c>
       <c r="AG2">
-        <v>0.8586</v>
+        <v>1.1455</v>
       </c>
       <c r="AH2">
         <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>5.1</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -919,13 +919,13 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
-        <v>-116</v>
+        <v>-108</v>
       </c>
       <c r="E3">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -937,7 +937,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -949,43 +949,43 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>0.1984</v>
+        <v>0.2551</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="P3">
-        <v>3.98</v>
+        <v>4.19</v>
       </c>
       <c r="Q3">
-        <v>0.2393</v>
+        <v>0.2292</v>
       </c>
       <c r="R3">
-        <v>0.369</v>
+        <v>0.324</v>
       </c>
       <c r="S3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2529</v>
+        <v>0.1914</v>
       </c>
       <c r="U3">
-        <v>0.2729</v>
+        <v>0.1846</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2499</v>
+        <v>0.21</v>
       </c>
       <c r="X3">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y3">
-        <v>1.0351</v>
+        <v>0.9697</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -994,22 +994,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.94</v>
+        <v>4.27</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2135</v>
+        <v>0.2467</v>
       </c>
       <c r="AG3">
-        <v>1.1531</v>
+        <v>0.8672</v>
       </c>
       <c r="AH3">
         <v>0.22</v>
       </c>
       <c r="AM3">
-        <v>6.16</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1017,76 +1017,67 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-      <c r="D4">
-        <v>-108</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
         <v>41</v>
       </c>
       <c r="G4">
-        <v>823539</v>
+        <v>823501</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.2551</v>
+        <v>0.175</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>4.19</v>
+        <v>3.87</v>
       </c>
       <c r="Q4">
-        <v>0.2292</v>
+        <v>0.25</v>
       </c>
       <c r="R4">
-        <v>0.324</v>
+        <v>0.02</v>
       </c>
       <c r="S4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1914</v>
+        <v>0.2693</v>
       </c>
       <c r="U4">
-        <v>0.1846</v>
+        <v>0.2681</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.21</v>
+        <v>0.2499</v>
       </c>
       <c r="X4">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y4">
-        <v>0.9697</v>
+        <v>1.0597</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1095,22 +1086,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2467</v>
+        <v>0.1765</v>
       </c>
       <c r="AG4">
-        <v>0.8729</v>
+        <v>1.22</v>
       </c>
       <c r="AH4">
         <v>0.22</v>
       </c>
       <c r="AM4">
-        <v>4.52</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1120,6 +1111,15 @@
       <c r="B5" t="s">
         <v>49</v>
       </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+      <c r="D5">
+        <v>-130</v>
+      </c>
+      <c r="E5">
+        <v>105</v>
+      </c>
       <c r="F5" t="s">
         <v>41</v>
       </c>
@@ -1127,58 +1127,58 @@
         <v>823501</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I5">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>0.175</v>
+        <v>0.238</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="P5">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="Q5">
-        <v>0.25</v>
+        <v>0.3152</v>
       </c>
       <c r="R5">
-        <v>0.02</v>
+        <v>0.315</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2426</v>
+        <v>0.1859</v>
       </c>
       <c r="U5">
-        <v>0.2535</v>
+        <v>0.1814</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2499</v>
+        <v>0.21</v>
       </c>
       <c r="X5">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y5">
-        <v>1.0025</v>
+        <v>0.9794</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1187,22 +1187,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>1.01</v>
+        <v>4.79</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1765</v>
+        <v>0.2623</v>
       </c>
       <c r="AG5">
-        <v>1.1062</v>
+        <v>0.842</v>
       </c>
       <c r="AH5">
         <v>0.22</v>
       </c>
       <c r="AM5">
-        <v>1.23</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1210,7 +1210,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>6.5</v>
@@ -1222,7 +1222,7 @@
         <v>-105</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>824230</v>
@@ -1261,7 +1261,7 @@
         <v>0.353</v>
       </c>
       <c r="S6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T6">
         <v>0.2179</v>
@@ -1276,7 +1276,7 @@
         <v>0.2313</v>
       </c>
       <c r="X6">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y6">
         <v>0.9742</v>
@@ -1288,22 +1288,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>6.97</v>
+        <v>6.92</v>
       </c>
       <c r="AE6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF6">
         <v>0.3303</v>
       </c>
       <c r="AG6">
-        <v>0.9936</v>
+        <v>0.9871</v>
       </c>
       <c r="AH6">
         <v>-0.55</v>
       </c>
       <c r="AM6">
-        <v>6.42</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1311,7 +1311,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -1323,7 +1323,7 @@
         <v>-115</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>824230</v>
@@ -1362,7 +1362,7 @@
         <v>0.361</v>
       </c>
       <c r="S7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T7">
         <v>0.2129</v>
@@ -1377,7 +1377,7 @@
         <v>0.2058</v>
       </c>
       <c r="X7">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y7">
         <v>0.991</v>
@@ -1389,7 +1389,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
@@ -1398,13 +1398,13 @@
         <v>0.1473</v>
       </c>
       <c r="AG7">
-        <v>0.9708</v>
+        <v>0.9644</v>
       </c>
       <c r="AH7">
         <v>0.22</v>
       </c>
       <c r="AM7">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1412,10 +1412,10 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
         <v>55</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
       </c>
       <c r="G8">
         <v>823665</v>
@@ -1454,7 +1454,7 @@
         <v>0.322</v>
       </c>
       <c r="S8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T8">
         <v>0.2021</v>
@@ -1466,10 +1466,10 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2072</v>
+        <v>0.2071</v>
       </c>
       <c r="X8">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y8">
         <v>0.936</v>
@@ -1481,7 +1481,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1490,13 +1490,13 @@
         <v>0.1833</v>
       </c>
       <c r="AG8">
-        <v>0.9215</v>
+        <v>0.9155</v>
       </c>
       <c r="AH8">
         <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1504,10 +1504,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>823665</v>
@@ -1546,7 +1546,7 @@
         <v>0.357</v>
       </c>
       <c r="S9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T9">
         <v>0.2522</v>
@@ -1558,10 +1558,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2363</v>
+        <v>0.2367</v>
       </c>
       <c r="X9">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y9">
         <v>1.0323</v>
@@ -1573,7 +1573,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1582,13 +1582,13 @@
         <v>0.158</v>
       </c>
       <c r="AG9">
-        <v>1.1501</v>
+        <v>1.1425</v>
       </c>
       <c r="AH9">
         <v>0.22</v>
       </c>
       <c r="AM9">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1596,16 +1596,16 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
         <v>58</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
       </c>
       <c r="G10">
         <v>823011</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I10">
         <v>2.3</v>
@@ -1638,7 +1638,7 @@
         <v>0.187</v>
       </c>
       <c r="S10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T10">
         <v>0.2511</v>
@@ -1650,10 +1650,10 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2158</v>
+        <v>0.2156</v>
       </c>
       <c r="X10">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y10">
         <v>0.8961</v>
@@ -1665,7 +1665,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1674,13 +1674,13 @@
         <v>0.252</v>
       </c>
       <c r="AG10">
-        <v>1.1448</v>
+        <v>1.1373</v>
       </c>
       <c r="AH10">
         <v>0.22</v>
       </c>
       <c r="AM10">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1688,10 +1688,10 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>823011</v>
@@ -1730,7 +1730,7 @@
         <v>0.308</v>
       </c>
       <c r="S11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T11">
         <v>0.2509</v>
@@ -1742,10 +1742,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2373</v>
+        <v>0.237</v>
       </c>
       <c r="X11">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y11">
         <v>1.0293</v>
@@ -1757,22 +1757,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="AE11" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AF11">
         <v>0.2433</v>
       </c>
       <c r="AG11">
-        <v>1.144</v>
+        <v>1.1366</v>
       </c>
       <c r="AH11">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM11">
-        <v>5.45</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1780,7 +1780,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12">
         <v>3.5</v>
@@ -1792,7 +1792,7 @@
         <v>126</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>824637</v>
@@ -1831,7 +1831,7 @@
         <v>0.377</v>
       </c>
       <c r="S12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T12">
         <v>0.1662</v>
@@ -1843,10 +1843,10 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2192</v>
+        <v>0.2172</v>
       </c>
       <c r="X12">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y12">
         <v>0.8905</v>
@@ -1858,7 +1858,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1867,13 +1867,13 @@
         <v>0.1727</v>
       </c>
       <c r="AG12">
-        <v>0.7579</v>
+        <v>0.753</v>
       </c>
       <c r="AH12">
         <v>0.22</v>
       </c>
       <c r="AM12">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1881,7 +1881,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13">
         <v>6.5</v>
@@ -1893,7 +1893,7 @@
         <v>-130</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>824637</v>
@@ -1932,7 +1932,7 @@
         <v>0.367</v>
       </c>
       <c r="S13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T13">
         <v>0.2556</v>
@@ -1944,10 +1944,10 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2542</v>
+        <v>0.2548</v>
       </c>
       <c r="X13">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y13">
         <v>1.12</v>
@@ -1959,22 +1959,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.41</v>
+        <v>7.36</v>
       </c>
       <c r="AE13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AF13">
         <v>0.2423</v>
       </c>
       <c r="AG13">
-        <v>1.1655</v>
+        <v>1.1579</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>7.41</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1982,7 +1982,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -1994,7 +1994,7 @@
         <v>-130</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>822770</v>
@@ -2003,7 +2003,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2015,25 +2015,25 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <v>0.2349</v>
+        <v>0.2344</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="P14">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="Q14">
-        <v>0.1667</v>
+        <v>0.1724</v>
       </c>
       <c r="R14">
-        <v>0.338</v>
+        <v>0.367</v>
       </c>
       <c r="S14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T14">
         <v>0.2675</v>
@@ -2048,7 +2048,7 @@
         <v>0.2259</v>
       </c>
       <c r="X14">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y14">
         <v>0.9726</v>
@@ -2060,22 +2060,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.71</v>
+        <v>5.79</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2119</v>
+        <v>0.2117</v>
       </c>
       <c r="AG14">
-        <v>1.2198</v>
+        <v>1.2118</v>
       </c>
       <c r="AH14">
         <v>0.22</v>
       </c>
       <c r="AM14">
-        <v>5.93</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2083,7 +2083,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2095,7 +2095,7 @@
         <v>-170</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>823177</v>
@@ -2104,7 +2104,7 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2116,25 +2116,25 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1498</v>
+        <v>0.1517</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="P15">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="Q15">
-        <v>0.1354</v>
+        <v>0.1478</v>
       </c>
       <c r="R15">
-        <v>0.324</v>
+        <v>0.365</v>
       </c>
       <c r="S15" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T15">
         <v>0.2333</v>
@@ -2149,7 +2149,7 @@
         <v>0.2049</v>
       </c>
       <c r="X15">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y15">
         <v>0.9313</v>
@@ -2161,22 +2161,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1452</v>
+        <v>0.1503</v>
       </c>
       <c r="AG15">
-        <v>1.0639</v>
+        <v>1.0569</v>
       </c>
       <c r="AH15">
         <v>0.22</v>
       </c>
       <c r="AM15">
-        <v>3.64</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2184,7 +2184,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2196,13 +2196,13 @@
         <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16">
         <v>823176</v>
       </c>
       <c r="H16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I16">
         <v>4.4</v>
@@ -2235,7 +2235,7 @@
         <v>0.331</v>
       </c>
       <c r="S16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -2244,7 +2244,7 @@
         <v>0.2353</v>
       </c>
       <c r="X16">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y16">
         <v>1.0233</v>
@@ -2279,7 +2279,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2291,7 +2291,7 @@
         <v>-150</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G17">
         <v>822690</v>
@@ -2300,7 +2300,7 @@
         <v>42</v>
       </c>
       <c r="I17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2312,25 +2312,25 @@
         <v>2</v>
       </c>
       <c r="M17">
-        <v>0.1798</v>
+        <v>0.1793</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="P17">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="Q17">
-        <v>0.1504</v>
+        <v>0.1462</v>
       </c>
       <c r="R17">
-        <v>0.361</v>
+        <v>0.394</v>
       </c>
       <c r="S17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T17">
         <v>0.2314</v>
@@ -2345,7 +2345,7 @@
         <v>0.2064</v>
       </c>
       <c r="X17">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y17">
         <v>0.9921</v>
@@ -2363,10 +2363,10 @@
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.1692</v>
+        <v>0.1662</v>
       </c>
       <c r="AG17">
-        <v>1.055</v>
+        <v>1.0481</v>
       </c>
       <c r="AH17">
         <v>0.22</v>
@@ -2380,7 +2380,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18">
         <v>6.5</v>
@@ -2392,7 +2392,7 @@
         <v>-128</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G18">
         <v>822690</v>
@@ -2401,7 +2401,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2413,25 +2413,25 @@
         <v>2</v>
       </c>
       <c r="M18">
-        <v>0.273</v>
+        <v>0.2766</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="P18">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="Q18">
-        <v>0.375</v>
+        <v>0.386</v>
       </c>
       <c r="R18">
-        <v>0.342</v>
+        <v>0.363</v>
       </c>
       <c r="S18" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T18">
         <v>0.2086</v>
@@ -2446,7 +2446,7 @@
         <v>0.2107</v>
       </c>
       <c r="X18">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y18">
         <v>0.9439</v>
@@ -2458,22 +2458,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.01</v>
+        <v>6.23</v>
       </c>
       <c r="AE18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF18">
-        <v>0.3079</v>
+        <v>0.3163</v>
       </c>
       <c r="AG18">
-        <v>0.9513</v>
+        <v>0.9451</v>
       </c>
       <c r="AH18">
         <v>-0.55</v>
       </c>
       <c r="AM18">
-        <v>5.46</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2481,7 +2481,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>2.5</v>
@@ -2493,16 +2493,16 @@
         <v>-107</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19">
         <v>824392</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I19">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2514,25 +2514,25 @@
         <v>1</v>
       </c>
       <c r="M19">
-        <v>0.1849</v>
+        <v>0.184</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="P19">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="Q19">
-        <v>0.1636</v>
+        <v>0.1642</v>
       </c>
       <c r="R19">
-        <v>0.216</v>
+        <v>0.251</v>
       </c>
       <c r="S19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T19">
         <v>0.1994</v>
@@ -2547,7 +2547,7 @@
         <v>0.2241</v>
       </c>
       <c r="X19">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y19">
         <v>0.88</v>
@@ -2559,22 +2559,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.1803</v>
+        <v>0.179</v>
       </c>
       <c r="AG19">
-        <v>0.9091</v>
+        <v>0.9031</v>
       </c>
       <c r="AH19">
         <v>0.22</v>
       </c>
       <c r="AM19">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2582,7 +2582,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>5.5</v>
@@ -2594,7 +2594,7 @@
         <v>-108</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G20">
         <v>824392</v>
@@ -2603,7 +2603,7 @@
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2615,25 +2615,25 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>0.2201</v>
+        <v>0.2206</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="P20">
         <v>4.08</v>
       </c>
       <c r="Q20">
-        <v>0.2151</v>
+        <v>0.217</v>
       </c>
       <c r="R20">
-        <v>0.317</v>
+        <v>0.346</v>
       </c>
       <c r="S20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T20">
         <v>0.2084</v>
@@ -2648,7 +2648,7 @@
         <v>0.2139</v>
       </c>
       <c r="X20">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y20">
         <v>1.0087</v>
@@ -2660,22 +2660,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.79</v>
+        <v>4.87</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2185</v>
+        <v>0.2194</v>
       </c>
       <c r="AG20">
-        <v>0.95</v>
+        <v>0.9438</v>
       </c>
       <c r="AH20">
         <v>0.22</v>
       </c>
       <c r="AM20">
-        <v>5.01</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2683,16 +2683,16 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" t="s">
         <v>78</v>
-      </c>
-      <c r="F21" t="s">
-        <v>79</v>
       </c>
       <c r="G21">
         <v>823582</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -2725,7 +2725,7 @@
         <v>0.024</v>
       </c>
       <c r="S21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T21">
         <v>0.2425</v>
@@ -2740,7 +2740,7 @@
         <v>0.2339</v>
       </c>
       <c r="X21">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y21">
         <v>0.9768</v>
@@ -2752,7 +2752,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2761,13 +2761,13 @@
         <v>0.2203</v>
       </c>
       <c r="AG21">
-        <v>1.1059</v>
+        <v>1.0987</v>
       </c>
       <c r="AH21">
         <v>0.22</v>
       </c>
       <c r="AM21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2775,7 +2775,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2787,7 +2787,7 @@
         <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22">
         <v>823582</v>
@@ -2796,7 +2796,7 @@
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2808,25 +2808,25 @@
         <v>2</v>
       </c>
       <c r="M22">
-        <v>0.2697</v>
+        <v>0.2657</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="P22">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="Q22">
-        <v>0.198</v>
+        <v>0.1842</v>
       </c>
       <c r="R22">
-        <v>0.336</v>
+        <v>0.363</v>
       </c>
       <c r="S22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T22">
         <v>0.2057</v>
@@ -2841,7 +2841,7 @@
         <v>0.2191</v>
       </c>
       <c r="X22">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y22">
         <v>0.9509</v>
@@ -2853,22 +2853,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.05</v>
+        <v>4.93</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2456</v>
+        <v>0.2361</v>
       </c>
       <c r="AG22">
-        <v>0.9377</v>
+        <v>0.9316</v>
       </c>
       <c r="AH22">
         <v>0.22</v>
       </c>
       <c r="AM22">
-        <v>5.27</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2876,7 +2876,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>3.5</v>
@@ -2888,7 +2888,7 @@
         <v>-122</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G23">
         <v>822936</v>
@@ -2897,7 +2897,7 @@
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2909,25 +2909,25 @@
         <v>3</v>
       </c>
       <c r="M23">
-        <v>0.1985</v>
+        <v>0.1986</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="P23">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="Q23">
-        <v>0.1798</v>
+        <v>0.1827</v>
       </c>
       <c r="R23">
-        <v>0.308</v>
+        <v>0.342</v>
       </c>
       <c r="S23" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T23">
         <v>0.1524</v>
@@ -2942,7 +2942,7 @@
         <v>0.1865</v>
       </c>
       <c r="X23">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y23">
         <v>0.88</v>
@@ -2954,22 +2954,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.1928</v>
+        <v>0.1931</v>
       </c>
       <c r="AG23">
-        <v>0.6947</v>
+        <v>0.6901</v>
       </c>
       <c r="AH23">
         <v>0.22</v>
       </c>
       <c r="AM23">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2977,7 +2977,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -2989,7 +2989,7 @@
         <v>-111</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G24">
         <v>822936</v>
@@ -2998,7 +2998,7 @@
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3010,25 +3010,25 @@
         <v>3</v>
       </c>
       <c r="M24">
-        <v>0.1481</v>
+        <v>0.1472</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="P24">
         <v>4.02</v>
       </c>
       <c r="Q24">
-        <v>0.1881</v>
+        <v>0.1818</v>
       </c>
       <c r="R24">
-        <v>0.336</v>
+        <v>0.377</v>
       </c>
       <c r="S24" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T24">
         <v>0.1918</v>
@@ -3043,7 +3043,7 @@
         <v>0.2154</v>
       </c>
       <c r="X24">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y24">
         <v>1.0075</v>
@@ -3055,22 +3055,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.1615</v>
+        <v>0.1603</v>
       </c>
       <c r="AG24">
-        <v>0.8745</v>
+        <v>0.8688</v>
       </c>
       <c r="AH24">
         <v>0.22</v>
       </c>
       <c r="AM24">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3078,22 +3078,22 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" t="s">
         <v>84</v>
-      </c>
-      <c r="F25" t="s">
-        <v>85</v>
       </c>
       <c r="G25">
         <v>824874</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3102,25 +3102,25 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.1522</v>
+        <v>0.1503</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O25">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="P25">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="Q25">
-        <v>0.1563</v>
+        <v>0.1395</v>
       </c>
       <c r="R25">
-        <v>0.138</v>
+        <v>0.177</v>
       </c>
       <c r="S25" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T25">
         <v>0.2331</v>
@@ -3135,7 +3135,7 @@
         <v>0.2205</v>
       </c>
       <c r="X25">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y25">
         <v>0.988</v>
@@ -3147,22 +3147,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.1528</v>
+        <v>0.1484</v>
       </c>
       <c r="AG25">
-        <v>1.063</v>
+        <v>1.056</v>
       </c>
       <c r="AH25">
         <v>0.22</v>
       </c>
       <c r="AM25">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3170,7 +3170,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3182,7 +3182,7 @@
         <v>-107</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G26">
         <v>824874</v>
@@ -3191,7 +3191,7 @@
         <v>42</v>
       </c>
       <c r="I26">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3203,25 +3203,25 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1775</v>
+        <v>0.1846</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="P26">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="Q26">
-        <v>0.125</v>
+        <v>0.1684</v>
       </c>
       <c r="R26">
-        <v>0.286</v>
+        <v>0.322</v>
       </c>
       <c r="S26" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T26">
         <v>0.241</v>
@@ -3236,7 +3236,7 @@
         <v>0.2484</v>
       </c>
       <c r="X26">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y26">
         <v>1.0258</v>
@@ -3248,22 +3248,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.1625</v>
+        <v>0.1794</v>
       </c>
       <c r="AG26">
-        <v>1.0987</v>
+        <v>1.0915</v>
       </c>
       <c r="AH26">
         <v>0.22</v>
       </c>
       <c r="AM26">
-        <v>3.88</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3271,7 +3271,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3283,7 +3283,7 @@
         <v>-170</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G27">
         <v>823741</v>
@@ -3322,7 +3322,7 @@
         <v>0.363</v>
       </c>
       <c r="S27" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T27">
         <v>0.2241</v>
@@ -3337,7 +3337,7 @@
         <v>0.2135</v>
       </c>
       <c r="X27">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y27">
         <v>1.0476</v>
@@ -3349,7 +3349,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
@@ -3358,13 +3358,13 @@
         <v>0.1988</v>
       </c>
       <c r="AG27">
-        <v>1.0217</v>
+        <v>1.015</v>
       </c>
       <c r="AH27">
         <v>0.22</v>
       </c>
       <c r="AM27">
-        <v>4.66</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3372,7 +3372,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -3384,7 +3384,7 @@
         <v>-113</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G28">
         <v>823741</v>
@@ -3423,7 +3423,7 @@
         <v>0.371</v>
       </c>
       <c r="S28" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T28">
         <v>0.2284</v>
@@ -3438,7 +3438,7 @@
         <v>0.2412</v>
       </c>
       <c r="X28">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y28">
         <v>1.0739</v>
@@ -3450,7 +3450,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.74</v>
+        <v>5.7</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3459,13 +3459,13 @@
         <v>0.2322</v>
       </c>
       <c r="AG28">
-        <v>1.0416</v>
+        <v>1.0348</v>
       </c>
       <c r="AH28">
         <v>0.22</v>
       </c>
       <c r="AM28">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3473,10 +3473,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" t="s">
         <v>90</v>
-      </c>
-      <c r="F29" t="s">
-        <v>91</v>
       </c>
       <c r="G29">
         <v>824961</v>
@@ -3515,7 +3515,7 @@
         <v>0.373</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="T29">
         <v>0.2561</v>
@@ -3530,7 +3530,7 @@
         <v>0.2143</v>
       </c>
       <c r="X29">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y29">
         <v>1.0571</v>
@@ -3542,22 +3542,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>6.71</v>
+        <v>6.66</v>
       </c>
       <c r="AE29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF29">
         <v>0.219</v>
       </c>
       <c r="AG29">
-        <v>1.1675</v>
+        <v>1.1599</v>
       </c>
       <c r="AH29">
         <v>-0.55</v>
       </c>
       <c r="AM29">
-        <v>6.16</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3568,7 +3568,7 @@
         <v>92</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G30">
         <v>824961</v>
@@ -3607,7 +3607,7 @@
         <v>0.359</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="T30">
         <v>0.2634</v>
@@ -3622,7 +3622,7 @@
         <v>0.237</v>
       </c>
       <c r="X30">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y30">
         <v>1.0246</v>
@@ -3634,22 +3634,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>5.96</v>
       </c>
       <c r="AE30" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AF30">
         <v>0.2327</v>
       </c>
       <c r="AG30">
-        <v>1.2012</v>
+        <v>1.1933</v>
       </c>
       <c r="AH30">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM30">
-        <v>5.45</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3711,10 +3711,10 @@
         <v>43</v>
       </c>
       <c r="T31">
-        <v>0.2658</v>
+        <v>0.2892</v>
       </c>
       <c r="U31">
-        <v>0.2427</v>
+        <v>0.2769</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3723,10 +3723,10 @@
         <v>0.2492</v>
       </c>
       <c r="X31">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y31">
-        <v>1.0306</v>
+        <v>1.12</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3735,22 +3735,22 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>9.27</v>
+        <v>10.89</v>
       </c>
       <c r="AE31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AF31">
         <v>0.2859</v>
       </c>
       <c r="AG31">
-        <v>1.2119</v>
+        <v>1.3101</v>
       </c>
       <c r="AH31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>9.27</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3809,7 +3809,7 @@
         <v>0.346</v>
       </c>
       <c r="S32" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="T32">
         <v>0.1503</v>
@@ -3824,7 +3824,7 @@
         <v>0.222</v>
       </c>
       <c r="X32">
-        <v>0.2193</v>
+        <v>0.2208</v>
       </c>
       <c r="Y32">
         <v>0.9978</v>
@@ -3836,7 +3836,7 @@
         <v>44</v>
       </c>
       <c r="AD32">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AE32" t="s">
         <v>45</v>
@@ -3845,13 +3845,13 @@
         <v>0.1631</v>
       </c>
       <c r="AG32">
-        <v>0.6854</v>
+        <v>0.681</v>
       </c>
       <c r="AH32">
         <v>0.22</v>
       </c>
       <c r="AM32">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3871,7 +3871,7 @@
         <v>-155</v>
       </c>
       <c r="F33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
         <v>44</v>
@@ -3906,7 +3906,7 @@
         <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G34">
         <v>824874</v>
@@ -3945,7 +3945,7 @@
         <v>0.39</v>
       </c>
       <c r="S34" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="T34">
         <v>0.225</v>

--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -286,19 +286,19 @@
     <t>Baltimore Orioles @ Athletics</t>
   </si>
   <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
   </si>
   <si>
     <t>Matt Wilkinson</t>
@@ -881,7 +881,7 @@
         <v>0.2499</v>
       </c>
       <c r="X2">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y2">
         <v>1.0351</v>
@@ -893,7 +893,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>5.9</v>
+        <v>5.94</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -902,13 +902,13 @@
         <v>0.2135</v>
       </c>
       <c r="AG2">
-        <v>1.1455</v>
+        <v>1.1524</v>
       </c>
       <c r="AH2">
         <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>6.12</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -982,7 +982,7 @@
         <v>0.21</v>
       </c>
       <c r="X3">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y3">
         <v>0.9697</v>
@@ -994,7 +994,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -1003,13 +1003,13 @@
         <v>0.2467</v>
       </c>
       <c r="AG3">
-        <v>0.8672</v>
+        <v>0.8724</v>
       </c>
       <c r="AH3">
         <v>0.22</v>
       </c>
       <c r="AM3">
-        <v>4.49</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1074,7 +1074,7 @@
         <v>0.2499</v>
       </c>
       <c r="X4">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y4">
         <v>1.0597</v>
@@ -1095,7 +1095,7 @@
         <v>0.1765</v>
       </c>
       <c r="AG4">
-        <v>1.22</v>
+        <v>1.2273</v>
       </c>
       <c r="AH4">
         <v>0.22</v>
@@ -1175,7 +1175,7 @@
         <v>0.21</v>
       </c>
       <c r="X5">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y5">
         <v>0.9794</v>
@@ -1187,7 +1187,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.79</v>
+        <v>4.82</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
@@ -1196,13 +1196,13 @@
         <v>0.2623</v>
       </c>
       <c r="AG5">
-        <v>0.842</v>
+        <v>0.8471</v>
       </c>
       <c r="AH5">
         <v>0.22</v>
       </c>
       <c r="AM5">
-        <v>5.01</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1276,7 +1276,7 @@
         <v>0.2313</v>
       </c>
       <c r="X6">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y6">
         <v>0.9742</v>
@@ -1288,7 +1288,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>6.92</v>
+        <v>6.97</v>
       </c>
       <c r="AE6" t="s">
         <v>52</v>
@@ -1297,13 +1297,13 @@
         <v>0.3303</v>
       </c>
       <c r="AG6">
-        <v>0.9871</v>
+        <v>0.993</v>
       </c>
       <c r="AH6">
         <v>-0.55</v>
       </c>
       <c r="AM6">
-        <v>6.37</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1377,7 +1377,7 @@
         <v>0.2058</v>
       </c>
       <c r="X7">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y7">
         <v>0.991</v>
@@ -1389,7 +1389,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
@@ -1398,13 +1398,13 @@
         <v>0.1473</v>
       </c>
       <c r="AG7">
-        <v>0.9644</v>
+        <v>0.9702</v>
       </c>
       <c r="AH7">
         <v>0.22</v>
       </c>
       <c r="AM7">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1469,7 +1469,7 @@
         <v>0.2071</v>
       </c>
       <c r="X8">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y8">
         <v>0.936</v>
@@ -1481,7 +1481,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1490,13 +1490,13 @@
         <v>0.1833</v>
       </c>
       <c r="AG8">
-        <v>0.9155</v>
+        <v>0.921</v>
       </c>
       <c r="AH8">
         <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1561,7 +1561,7 @@
         <v>0.2367</v>
       </c>
       <c r="X9">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y9">
         <v>1.0323</v>
@@ -1573,7 +1573,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1582,13 +1582,13 @@
         <v>0.158</v>
       </c>
       <c r="AG9">
-        <v>1.1425</v>
+        <v>1.1494</v>
       </c>
       <c r="AH9">
         <v>0.22</v>
       </c>
       <c r="AM9">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1653,7 +1653,7 @@
         <v>0.2156</v>
       </c>
       <c r="X10">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y10">
         <v>0.8961</v>
@@ -1665,7 +1665,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1674,13 +1674,13 @@
         <v>0.252</v>
       </c>
       <c r="AG10">
-        <v>1.1373</v>
+        <v>1.1442</v>
       </c>
       <c r="AH10">
         <v>0.22</v>
       </c>
       <c r="AM10">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1745,7 +1745,7 @@
         <v>0.237</v>
       </c>
       <c r="X11">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y11">
         <v>1.0293</v>
@@ -1757,22 +1757,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.97</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF11">
         <v>0.2433</v>
       </c>
       <c r="AG11">
-        <v>1.1366</v>
+        <v>1.1434</v>
       </c>
       <c r="AH11">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM11">
-        <v>6.19</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1846,7 +1846,7 @@
         <v>0.2172</v>
       </c>
       <c r="X12">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y12">
         <v>0.8905</v>
@@ -1858,7 +1858,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1867,13 +1867,13 @@
         <v>0.1727</v>
       </c>
       <c r="AG12">
-        <v>0.753</v>
+        <v>0.7575</v>
       </c>
       <c r="AH12">
         <v>0.22</v>
       </c>
       <c r="AM12">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1947,7 +1947,7 @@
         <v>0.2548</v>
       </c>
       <c r="X13">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y13">
         <v>1.12</v>
@@ -1959,7 +1959,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.36</v>
+        <v>7.41</v>
       </c>
       <c r="AE13" t="s">
         <v>63</v>
@@ -1968,13 +1968,13 @@
         <v>0.2423</v>
       </c>
       <c r="AG13">
-        <v>1.1579</v>
+        <v>1.1648</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>7.36</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2015,22 +2015,22 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <v>0.2344</v>
+        <v>0.2365</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="P14">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q14">
-        <v>0.1724</v>
+        <v>0.1849</v>
       </c>
       <c r="R14">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
@@ -2045,10 +2045,10 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2259</v>
+        <v>0.2264</v>
       </c>
       <c r="X14">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y14">
         <v>0.9726</v>
@@ -2060,22 +2060,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.79</v>
+        <v>6.01</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF14">
-        <v>0.2117</v>
+        <v>0.2172</v>
       </c>
       <c r="AG14">
-        <v>1.2118</v>
+        <v>1.2191</v>
       </c>
       <c r="AH14">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM14">
-        <v>6.01</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2104,7 +2104,7 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2116,22 +2116,22 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1517</v>
+        <v>0.1542</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P15">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="Q15">
-        <v>0.1478</v>
+        <v>0.161</v>
       </c>
       <c r="R15">
-        <v>0.365</v>
+        <v>0.371</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
@@ -2146,10 +2146,10 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2049</v>
+        <v>0.2053</v>
       </c>
       <c r="X15">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y15">
         <v>0.9313</v>
@@ -2161,22 +2161,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.63</v>
+        <v>3.82</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1503</v>
+        <v>0.1567</v>
       </c>
       <c r="AG15">
-        <v>1.0569</v>
+        <v>1.0633</v>
       </c>
       <c r="AH15">
         <v>0.22</v>
       </c>
       <c r="AM15">
-        <v>3.85</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2241,10 +2241,10 @@
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.2353</v>
+        <v>0.2355</v>
       </c>
       <c r="X16">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y16">
         <v>1.0233</v>
@@ -2265,7 +2265,7 @@
         <v>0.1666</v>
       </c>
       <c r="AG16">
-        <v>1.0394</v>
+        <v>1.041</v>
       </c>
       <c r="AH16">
         <v>0.22</v>
@@ -2312,22 +2312,22 @@
         <v>2</v>
       </c>
       <c r="M17">
-        <v>0.1793</v>
+        <v>0.1786</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="P17">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="Q17">
-        <v>0.1462</v>
+        <v>0.1481</v>
       </c>
       <c r="R17">
-        <v>0.394</v>
+        <v>0.403</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
@@ -2345,7 +2345,7 @@
         <v>0.2064</v>
       </c>
       <c r="X17">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y17">
         <v>0.9921</v>
@@ -2357,22 +2357,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.1662</v>
+        <v>0.1663</v>
       </c>
       <c r="AG17">
-        <v>1.0481</v>
+        <v>1.0544</v>
       </c>
       <c r="AH17">
         <v>0.22</v>
       </c>
       <c r="AM17">
-        <v>4.87</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2446,7 +2446,7 @@
         <v>0.2107</v>
       </c>
       <c r="X18">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y18">
         <v>0.9439</v>
@@ -2458,7 +2458,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.23</v>
+        <v>6.26</v>
       </c>
       <c r="AE18" t="s">
         <v>52</v>
@@ -2467,13 +2467,13 @@
         <v>0.3163</v>
       </c>
       <c r="AG18">
-        <v>0.9451</v>
+        <v>0.9508</v>
       </c>
       <c r="AH18">
         <v>-0.55</v>
       </c>
       <c r="AM18">
-        <v>5.68</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2544,10 +2544,10 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2241</v>
+        <v>0.2232</v>
       </c>
       <c r="X19">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y19">
         <v>0.88</v>
@@ -2559,7 +2559,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2568,13 +2568,13 @@
         <v>0.179</v>
       </c>
       <c r="AG19">
-        <v>0.9031</v>
+        <v>0.9086</v>
       </c>
       <c r="AH19">
         <v>0.22</v>
       </c>
       <c r="AM19">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2645,10 +2645,10 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2139</v>
+        <v>0.2135</v>
       </c>
       <c r="X20">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y20">
         <v>1.0087</v>
@@ -2660,7 +2660,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.87</v>
+        <v>4.9</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2669,13 +2669,13 @@
         <v>0.2194</v>
       </c>
       <c r="AG20">
-        <v>0.9438</v>
+        <v>0.9495</v>
       </c>
       <c r="AH20">
         <v>0.22</v>
       </c>
       <c r="AM20">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2737,10 +2737,10 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2339</v>
+        <v>0.2331</v>
       </c>
       <c r="X21">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y21">
         <v>0.9768</v>
@@ -2752,7 +2752,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2761,13 +2761,13 @@
         <v>0.2203</v>
       </c>
       <c r="AG21">
-        <v>1.0987</v>
+        <v>1.1053</v>
       </c>
       <c r="AH21">
         <v>0.22</v>
       </c>
       <c r="AM21">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2796,7 +2796,7 @@
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2808,22 +2808,22 @@
         <v>2</v>
       </c>
       <c r="M22">
-        <v>0.2657</v>
+        <v>0.2671</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="P22">
         <v>4.14</v>
       </c>
       <c r="Q22">
-        <v>0.1842</v>
+        <v>0.1967</v>
       </c>
       <c r="R22">
-        <v>0.363</v>
+        <v>0.379</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
@@ -2838,10 +2838,10 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2191</v>
+        <v>0.2188</v>
       </c>
       <c r="X22">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y22">
         <v>0.9509</v>
@@ -2853,22 +2853,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.93</v>
+        <v>5.11</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2361</v>
+        <v>0.2404</v>
       </c>
       <c r="AG22">
-        <v>0.9316</v>
+        <v>0.9372</v>
       </c>
       <c r="AH22">
         <v>0.22</v>
       </c>
       <c r="AM22">
-        <v>5.15</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2942,7 +2942,7 @@
         <v>0.1865</v>
       </c>
       <c r="X23">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y23">
         <v>0.88</v>
@@ -2954,7 +2954,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -2963,13 +2963,13 @@
         <v>0.1931</v>
       </c>
       <c r="AG23">
-        <v>0.6901</v>
+        <v>0.6943</v>
       </c>
       <c r="AH23">
         <v>0.22</v>
       </c>
       <c r="AM23">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3043,7 +3043,7 @@
         <v>0.2154</v>
       </c>
       <c r="X24">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y24">
         <v>1.0075</v>
@@ -3055,7 +3055,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -3064,13 +3064,13 @@
         <v>0.1603</v>
       </c>
       <c r="AG24">
-        <v>0.8688</v>
+        <v>0.8741</v>
       </c>
       <c r="AH24">
         <v>0.22</v>
       </c>
       <c r="AM24">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3135,7 +3135,7 @@
         <v>0.2205</v>
       </c>
       <c r="X25">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y25">
         <v>0.988</v>
@@ -3147,7 +3147,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
@@ -3156,13 +3156,13 @@
         <v>0.1484</v>
       </c>
       <c r="AG25">
-        <v>1.056</v>
+        <v>1.0624</v>
       </c>
       <c r="AH25">
         <v>0.22</v>
       </c>
       <c r="AM25">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3191,7 +3191,7 @@
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3203,22 +3203,22 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1846</v>
+        <v>0.1824</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="P26">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="Q26">
-        <v>0.1684</v>
+        <v>0.1584</v>
       </c>
       <c r="R26">
-        <v>0.322</v>
+        <v>0.336</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
@@ -3236,7 +3236,7 @@
         <v>0.2484</v>
       </c>
       <c r="X26">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y26">
         <v>1.0258</v>
@@ -3248,22 +3248,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.1794</v>
+        <v>0.1743</v>
       </c>
       <c r="AG26">
-        <v>1.0915</v>
+        <v>1.098</v>
       </c>
       <c r="AH26">
         <v>0.22</v>
       </c>
       <c r="AM26">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3337,7 +3337,7 @@
         <v>0.2135</v>
       </c>
       <c r="X27">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y27">
         <v>1.0476</v>
@@ -3349,7 +3349,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
@@ -3358,13 +3358,13 @@
         <v>0.1988</v>
       </c>
       <c r="AG27">
-        <v>1.015</v>
+        <v>1.0212</v>
       </c>
       <c r="AH27">
         <v>0.22</v>
       </c>
       <c r="AM27">
-        <v>4.63</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3438,7 +3438,7 @@
         <v>0.2412</v>
       </c>
       <c r="X28">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y28">
         <v>1.0739</v>
@@ -3450,7 +3450,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.7</v>
+        <v>5.74</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3459,13 +3459,13 @@
         <v>0.2322</v>
       </c>
       <c r="AG28">
-        <v>1.0348</v>
+        <v>1.041</v>
       </c>
       <c r="AH28">
         <v>0.22</v>
       </c>
       <c r="AM28">
-        <v>5.92</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3515,25 +3515,25 @@
         <v>0.373</v>
       </c>
       <c r="S29" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.2561</v>
+        <v>0.2083</v>
       </c>
       <c r="U29">
-        <v>0.2265</v>
+        <v>0.2079</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>0.2143</v>
       </c>
       <c r="X29">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y29">
-        <v>1.0571</v>
+        <v>1.0603</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3542,22 +3542,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>6.66</v>
+        <v>5.47</v>
       </c>
       <c r="AE29" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF29">
         <v>0.219</v>
       </c>
       <c r="AG29">
-        <v>1.1599</v>
+        <v>0.9494</v>
       </c>
       <c r="AH29">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM29">
-        <v>6.11</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3565,7 +3565,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s">
         <v>90</v>
@@ -3607,13 +3607,13 @@
         <v>0.359</v>
       </c>
       <c r="S30" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="T30">
-        <v>0.2634</v>
+        <v>0.2675</v>
       </c>
       <c r="U30">
-        <v>0.2467</v>
+        <v>0.2513</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3622,10 +3622,10 @@
         <v>0.237</v>
       </c>
       <c r="X30">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y30">
-        <v>1.0246</v>
+        <v>1.0306</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3634,22 +3634,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>5.96</v>
+        <v>6.13</v>
       </c>
       <c r="AE30" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF30">
         <v>0.2327</v>
       </c>
       <c r="AG30">
-        <v>1.1933</v>
+        <v>1.2189</v>
       </c>
       <c r="AH30">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM30">
-        <v>6.18</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3657,7 +3657,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31">
         <v>7.5</v>
@@ -3669,7 +3669,7 @@
         <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31">
         <v>823986</v>
@@ -3723,7 +3723,7 @@
         <v>0.2492</v>
       </c>
       <c r="X31">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y31">
         <v>1.12</v>
@@ -3735,7 +3735,7 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>10.89</v>
+        <v>10.96</v>
       </c>
       <c r="AE31" t="s">
         <v>63</v>
@@ -3744,13 +3744,13 @@
         <v>0.2859</v>
       </c>
       <c r="AG31">
-        <v>1.3101</v>
+        <v>1.318</v>
       </c>
       <c r="AH31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>10.89</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3758,7 +3758,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -3770,7 +3770,7 @@
         <v>-130</v>
       </c>
       <c r="F32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G32">
         <v>823986</v>
@@ -3809,7 +3809,7 @@
         <v>0.346</v>
       </c>
       <c r="S32" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="T32">
         <v>0.1503</v>
@@ -3824,7 +3824,7 @@
         <v>0.222</v>
       </c>
       <c r="X32">
-        <v>0.2208</v>
+        <v>0.2194</v>
       </c>
       <c r="Y32">
         <v>0.9978</v>
@@ -3836,7 +3836,7 @@
         <v>44</v>
       </c>
       <c r="AD32">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AE32" t="s">
         <v>45</v>
@@ -3845,13 +3845,13 @@
         <v>0.1631</v>
       </c>
       <c r="AG32">
-        <v>0.681</v>
+        <v>0.6851</v>
       </c>
       <c r="AH32">
         <v>0.22</v>
       </c>
       <c r="AM32">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>0.39</v>
       </c>
       <c r="S34" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="T34">
         <v>0.225</v>

--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -298,13 +298,13 @@
     <t>Ryan Johnson</t>
   </si>
   <si>
+    <t>Matt Wilkinson</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Matt Wilkinson</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
   </si>
 </sst>
 </file>
@@ -2265,7 +2265,7 @@
         <v>0.1666</v>
       </c>
       <c r="AG16">
-        <v>1.041</v>
+        <v>1.0409</v>
       </c>
       <c r="AH16">
         <v>0.22</v>
@@ -2342,7 +2342,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2064</v>
+        <v>0.206</v>
       </c>
       <c r="X17">
         <v>0.2194</v>
@@ -2443,7 +2443,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2107</v>
+        <v>0.2128</v>
       </c>
       <c r="X18">
         <v>0.2194</v>
@@ -2939,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.1865</v>
+        <v>0.1861</v>
       </c>
       <c r="X23">
         <v>0.2194</v>
@@ -3040,7 +3040,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2154</v>
+        <v>0.2151</v>
       </c>
       <c r="X24">
         <v>0.2194</v>
@@ -3809,7 +3809,7 @@
         <v>0.346</v>
       </c>
       <c r="S32" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="T32">
         <v>0.1503</v>
@@ -3827,7 +3827,7 @@
         <v>0.2194</v>
       </c>
       <c r="Y32">
-        <v>0.9978</v>
+        <v>0.9957</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3859,7 +3859,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33">
         <v>3.5</v>
@@ -3903,7 +3903,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
         <v>84</v>
@@ -3945,7 +3945,7 @@
         <v>0.39</v>
       </c>
       <c r="S34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="T34">
         <v>0.225</v>

--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -133,6 +133,24 @@
     <t>08/29/2026</t>
   </si>
   <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>team_season_vs_hand</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
     <t>Jake Bennett</t>
   </si>
   <si>
@@ -145,12 +163,6 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Carlos Rodón</t>
   </si>
   <si>
@@ -212,18 +224,6 @@
   </si>
   <si>
     <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>team_season_vs_hand</t>
   </si>
   <si>
     <t>Sandy Alcantara</t>
@@ -818,25 +818,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D2">
-        <v>-116</v>
+        <v>-111</v>
       </c>
       <c r="E2">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823539</v>
+        <v>823176</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -848,43 +848,37 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>0.1984</v>
+        <v>0.1591</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="P2">
-        <v>3.98</v>
+        <v>4.44</v>
       </c>
       <c r="Q2">
-        <v>0.2393</v>
+        <v>0.1818</v>
       </c>
       <c r="R2">
-        <v>0.369</v>
+        <v>0.331</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
-      <c r="T2">
-        <v>0.2529</v>
-      </c>
-      <c r="U2">
-        <v>0.2729</v>
-      </c>
       <c r="V2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.2499</v>
+        <v>0.2355</v>
       </c>
       <c r="X2">
         <v>0.2194</v>
       </c>
       <c r="Y2">
-        <v>1.0351</v>
+        <v>1.0233</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -893,22 +887,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>5.94</v>
+        <v>3.47</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2135</v>
+        <v>0.1666</v>
       </c>
       <c r="AG2">
-        <v>1.1524</v>
+        <v>1.0409</v>
       </c>
       <c r="AH2">
         <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>6.16</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -919,25 +913,25 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-108</v>
+        <v>-116</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>823539</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I3">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -949,43 +943,43 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>0.2551</v>
+        <v>0.1984</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="P3">
-        <v>4.19</v>
+        <v>3.98</v>
       </c>
       <c r="Q3">
-        <v>0.2292</v>
+        <v>0.2393</v>
       </c>
       <c r="R3">
-        <v>0.324</v>
+        <v>0.369</v>
       </c>
       <c r="S3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T3">
-        <v>0.1914</v>
+        <v>0.2529</v>
       </c>
       <c r="U3">
-        <v>0.1846</v>
+        <v>0.2729</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.21</v>
+        <v>0.2499</v>
       </c>
       <c r="X3">
         <v>0.2194</v>
       </c>
       <c r="Y3">
-        <v>0.9697</v>
+        <v>1.0351</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -994,22 +988,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.29</v>
+        <v>5.94</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2467</v>
+        <v>0.2135</v>
       </c>
       <c r="AG3">
-        <v>0.8724</v>
+        <v>1.1524</v>
       </c>
       <c r="AH3">
         <v>0.22</v>
       </c>
       <c r="AM3">
-        <v>4.51</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1017,67 +1011,76 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+      <c r="D4">
+        <v>-108</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
       <c r="G4">
-        <v>823501</v>
+        <v>823539</v>
       </c>
       <c r="H4" t="s">
         <v>48</v>
       </c>
       <c r="I4">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>0.175</v>
+        <v>0.2551</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="P4">
-        <v>3.87</v>
+        <v>4.19</v>
       </c>
       <c r="Q4">
-        <v>0.25</v>
+        <v>0.2292</v>
       </c>
       <c r="R4">
-        <v>0.02</v>
+        <v>0.324</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T4">
-        <v>0.2693</v>
+        <v>0.1914</v>
       </c>
       <c r="U4">
-        <v>0.2681</v>
+        <v>0.1846</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2499</v>
+        <v>0.21</v>
       </c>
       <c r="X4">
         <v>0.2194</v>
       </c>
       <c r="Y4">
-        <v>1.0597</v>
+        <v>0.9697</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1086,22 +1089,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>1.18</v>
+        <v>4.29</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1765</v>
+        <v>0.2467</v>
       </c>
       <c r="AG4">
-        <v>1.2273</v>
+        <v>0.8724</v>
       </c>
       <c r="AH4">
         <v>0.22</v>
       </c>
       <c r="AM4">
-        <v>1.4</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1109,76 +1112,67 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-      <c r="D5">
-        <v>-130</v>
-      </c>
-      <c r="E5">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>823501</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.238</v>
+        <v>0.175</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="Q5">
-        <v>0.3152</v>
+        <v>0.25</v>
       </c>
       <c r="R5">
-        <v>0.315</v>
+        <v>0.02</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T5">
-        <v>0.1859</v>
+        <v>0.2693</v>
       </c>
       <c r="U5">
-        <v>0.1814</v>
+        <v>0.2681</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.21</v>
+        <v>0.2499</v>
       </c>
       <c r="X5">
         <v>0.2194</v>
       </c>
       <c r="Y5">
-        <v>0.9794</v>
+        <v>1.0597</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1187,22 +1181,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.82</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2623</v>
+        <v>0.1765</v>
       </c>
       <c r="AG5">
-        <v>0.8471</v>
+        <v>1.2273</v>
       </c>
       <c r="AH5">
         <v>0.22</v>
       </c>
       <c r="AM5">
-        <v>5.04</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1210,28 +1204,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D6">
-        <v>-120</v>
+        <v>-130</v>
       </c>
       <c r="E6">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G6">
-        <v>824230</v>
+        <v>823501</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I6">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1240,46 +1234,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>0.3303</v>
+        <v>0.238</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="P6">
-        <v>4.19</v>
+        <v>3.85</v>
       </c>
       <c r="Q6">
-        <v>0.3303</v>
+        <v>0.3152</v>
       </c>
       <c r="R6">
-        <v>0.353</v>
+        <v>0.315</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T6">
-        <v>0.2179</v>
+        <v>0.1859</v>
       </c>
       <c r="U6">
-        <v>0.211</v>
+        <v>0.1814</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2313</v>
+        <v>0.21</v>
       </c>
       <c r="X6">
         <v>0.2194</v>
       </c>
       <c r="Y6">
-        <v>0.9742</v>
+        <v>0.9794</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1288,22 +1282,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>6.97</v>
+        <v>4.82</v>
       </c>
       <c r="AE6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.3303</v>
+        <v>0.2623</v>
       </c>
       <c r="AG6">
-        <v>0.993</v>
+        <v>0.8471</v>
       </c>
       <c r="AH6">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM6">
-        <v>6.42</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1311,28 +1305,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D7">
-        <v>-108</v>
+        <v>-120</v>
       </c>
       <c r="E7">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>824230</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I7">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1344,43 +1338,43 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>0.1655</v>
+        <v>0.3303</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="Q7">
-        <v>0.115</v>
+        <v>0.3303</v>
       </c>
       <c r="R7">
-        <v>0.361</v>
+        <v>0.353</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T7">
-        <v>0.2129</v>
+        <v>0.2179</v>
       </c>
       <c r="U7">
-        <v>0.2125</v>
+        <v>0.211</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2058</v>
+        <v>0.2313</v>
       </c>
       <c r="X7">
         <v>0.2194</v>
       </c>
       <c r="Y7">
-        <v>0.991</v>
+        <v>0.9742</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1389,22 +1383,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.21</v>
+        <v>6.97</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AF7">
-        <v>0.1473</v>
+        <v>0.3303</v>
       </c>
       <c r="AG7">
-        <v>0.9702</v>
+        <v>0.993</v>
       </c>
       <c r="AH7">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM7">
-        <v>3.43</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1412,19 +1406,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>3.5</v>
+      </c>
+      <c r="D8">
+        <v>-108</v>
+      </c>
+      <c r="E8">
+        <v>-115</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
       </c>
       <c r="G8">
-        <v>823665</v>
+        <v>824230</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I8">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1433,46 +1436,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>0.1654</v>
+        <v>0.1655</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="P8">
-        <v>4.31</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>0.2211</v>
+        <v>0.115</v>
       </c>
       <c r="R8">
-        <v>0.322</v>
+        <v>0.361</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T8">
-        <v>0.2021</v>
+        <v>0.2129</v>
       </c>
       <c r="U8">
-        <v>0.1907</v>
+        <v>0.2125</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2071</v>
+        <v>0.2058</v>
       </c>
       <c r="X8">
         <v>0.2194</v>
       </c>
       <c r="Y8">
-        <v>0.936</v>
+        <v>0.991</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1481,22 +1484,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1833</v>
+        <v>0.1473</v>
       </c>
       <c r="AG8">
-        <v>0.921</v>
+        <v>0.9702</v>
       </c>
       <c r="AH8">
         <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>3.51</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1504,19 +1507,19 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>823665</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I9">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1528,43 +1531,43 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0.1656</v>
+        <v>0.1654</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="P9">
-        <v>4.21</v>
+        <v>4.31</v>
       </c>
       <c r="Q9">
-        <v>0.1441</v>
+        <v>0.2211</v>
       </c>
       <c r="R9">
-        <v>0.357</v>
+        <v>0.322</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T9">
-        <v>0.2522</v>
+        <v>0.2021</v>
       </c>
       <c r="U9">
-        <v>0.2525</v>
+        <v>0.1907</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2367</v>
+        <v>0.2071</v>
       </c>
       <c r="X9">
         <v>0.2194</v>
       </c>
       <c r="Y9">
-        <v>1.0323</v>
+        <v>0.936</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1573,22 +1576,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.26</v>
+        <v>3.29</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.158</v>
+        <v>0.1833</v>
       </c>
       <c r="AG9">
-        <v>1.1494</v>
+        <v>0.921</v>
       </c>
       <c r="AH9">
         <v>0.22</v>
       </c>
       <c r="AM9">
-        <v>4.48</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1596,22 +1599,22 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10">
-        <v>823011</v>
+        <v>823665</v>
       </c>
       <c r="H10" t="s">
         <v>48</v>
       </c>
       <c r="I10">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1620,43 +1623,43 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0.25</v>
+        <v>0.1656</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="P10">
-        <v>4.09</v>
+        <v>4.21</v>
       </c>
       <c r="Q10">
-        <v>0.2609</v>
+        <v>0.1441</v>
       </c>
       <c r="R10">
-        <v>0.187</v>
+        <v>0.357</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T10">
-        <v>0.2511</v>
+        <v>0.2522</v>
       </c>
       <c r="U10">
-        <v>0.2169</v>
+        <v>0.2525</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2156</v>
+        <v>0.2367</v>
       </c>
       <c r="X10">
         <v>0.2194</v>
       </c>
       <c r="Y10">
-        <v>0.8961</v>
+        <v>1.0323</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1665,22 +1668,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.47</v>
+        <v>4.26</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.252</v>
+        <v>0.158</v>
       </c>
       <c r="AG10">
-        <v>1.1442</v>
+        <v>1.1494</v>
       </c>
       <c r="AH10">
         <v>0.22</v>
       </c>
       <c r="AM10">
-        <v>2.69</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1688,22 +1691,22 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>823011</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1712,43 +1715,43 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.2165</v>
+        <v>0.25</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="P11">
-        <v>4.21</v>
+        <v>4.09</v>
       </c>
       <c r="Q11">
-        <v>0.3034</v>
+        <v>0.2609</v>
       </c>
       <c r="R11">
-        <v>0.308</v>
+        <v>0.187</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T11">
-        <v>0.2509</v>
+        <v>0.2511</v>
       </c>
       <c r="U11">
-        <v>0.2463</v>
+        <v>0.2169</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.237</v>
+        <v>0.2156</v>
       </c>
       <c r="X11">
         <v>0.2194</v>
       </c>
       <c r="Y11">
-        <v>1.0293</v>
+        <v>0.8961</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1757,22 +1760,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>6</v>
+        <v>2.47</v>
       </c>
       <c r="AE11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2433</v>
+        <v>0.252</v>
       </c>
       <c r="AG11">
-        <v>1.1434</v>
+        <v>1.1442</v>
       </c>
       <c r="AH11">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM11">
-        <v>5.45</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1780,28 +1783,19 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12">
-        <v>3.5</v>
-      </c>
-      <c r="D12">
-        <v>-156</v>
-      </c>
-      <c r="E12">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12">
-        <v>824637</v>
+        <v>823011</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I12">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1810,46 +1804,46 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>0.1772</v>
+        <v>0.2165</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="P12">
-        <v>4.38</v>
+        <v>4.21</v>
       </c>
       <c r="Q12">
-        <v>0.1653</v>
+        <v>0.3034</v>
       </c>
       <c r="R12">
-        <v>0.377</v>
+        <v>0.308</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T12">
-        <v>0.1662</v>
+        <v>0.2509</v>
       </c>
       <c r="U12">
-        <v>0.1874</v>
+        <v>0.2463</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2172</v>
+        <v>0.237</v>
       </c>
       <c r="X12">
         <v>0.2194</v>
       </c>
       <c r="Y12">
-        <v>0.8905</v>
+        <v>1.0293</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1858,22 +1852,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AF12">
-        <v>0.1727</v>
+        <v>0.2433</v>
       </c>
       <c r="AG12">
-        <v>0.7575</v>
+        <v>1.1434</v>
       </c>
       <c r="AH12">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM12">
-        <v>2.92</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1881,28 +1875,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D13">
-        <v>112</v>
+        <v>-156</v>
       </c>
       <c r="E13">
-        <v>-130</v>
+        <v>126</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>824637</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I13">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1914,43 +1908,43 @@
         <v>4</v>
       </c>
       <c r="M13">
-        <v>0.2378</v>
+        <v>0.1772</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="P13">
-        <v>4.22</v>
+        <v>4.38</v>
       </c>
       <c r="Q13">
-        <v>0.25</v>
+        <v>0.1653</v>
       </c>
       <c r="R13">
-        <v>0.367</v>
+        <v>0.377</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T13">
-        <v>0.2556</v>
+        <v>0.1662</v>
       </c>
       <c r="U13">
-        <v>0.2652</v>
+        <v>0.1874</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2548</v>
+        <v>0.2172</v>
       </c>
       <c r="X13">
         <v>0.2194</v>
       </c>
       <c r="Y13">
-        <v>1.12</v>
+        <v>0.8905</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1959,22 +1953,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.41</v>
+        <v>2.7</v>
       </c>
       <c r="AE13" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2423</v>
+        <v>0.1727</v>
       </c>
       <c r="AG13">
-        <v>1.1648</v>
+        <v>0.7575</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AM13">
-        <v>7.41</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1982,13 +1976,13 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D14">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E14">
         <v>-130</v>
@@ -1997,13 +1991,13 @@
         <v>65</v>
       </c>
       <c r="G14">
-        <v>822770</v>
+        <v>824637</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I14">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2012,46 +2006,46 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M14">
-        <v>0.2365</v>
+        <v>0.2378</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P14">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
       <c r="Q14">
-        <v>0.1849</v>
+        <v>0.25</v>
       </c>
       <c r="R14">
-        <v>0.373</v>
+        <v>0.367</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T14">
-        <v>0.2675</v>
+        <v>0.2556</v>
       </c>
       <c r="U14">
-        <v>0.233</v>
+        <v>0.2652</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2264</v>
+        <v>0.2548</v>
       </c>
       <c r="X14">
         <v>0.2194</v>
       </c>
       <c r="Y14">
-        <v>0.9726</v>
+        <v>1.12</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2060,22 +2054,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.01</v>
+        <v>7.41</v>
       </c>
       <c r="AE14" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AF14">
-        <v>0.2172</v>
+        <v>0.2423</v>
       </c>
       <c r="AG14">
-        <v>1.2191</v>
+        <v>1.1648</v>
       </c>
       <c r="AH14">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.46</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2083,28 +2077,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D15">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="E15">
-        <v>-170</v>
+        <v>-130</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15">
-        <v>823177</v>
+        <v>822770</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I15">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2113,46 +2107,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>0.1542</v>
+        <v>0.2365</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P15">
-        <v>4.35</v>
+        <v>4.16</v>
       </c>
       <c r="Q15">
-        <v>0.161</v>
+        <v>0.1849</v>
       </c>
       <c r="R15">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T15">
-        <v>0.2333</v>
+        <v>0.2675</v>
       </c>
       <c r="U15">
-        <v>0.2173</v>
+        <v>0.233</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2053</v>
+        <v>0.2264</v>
       </c>
       <c r="X15">
         <v>0.2194</v>
       </c>
       <c r="Y15">
-        <v>0.9313</v>
+        <v>0.9726</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2161,22 +2155,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.82</v>
+        <v>6.01</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AF15">
-        <v>0.1567</v>
+        <v>0.2172</v>
       </c>
       <c r="AG15">
-        <v>1.0633</v>
+        <v>1.2191</v>
       </c>
       <c r="AH15">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM15">
-        <v>4.04</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2184,28 +2178,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C16">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-138</v>
+        <v>134</v>
       </c>
       <c r="E16">
-        <v>110</v>
+        <v>-170</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="G16">
-        <v>823176</v>
+        <v>823177</v>
       </c>
       <c r="H16" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="I16">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2214,40 +2208,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>0.1591</v>
+        <v>0.1542</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="P16">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="Q16">
-        <v>0.1818</v>
+        <v>0.161</v>
       </c>
       <c r="R16">
-        <v>0.331</v>
+        <v>0.371</v>
       </c>
       <c r="S16" t="s">
-        <v>70</v>
+        <v>49</v>
+      </c>
+      <c r="T16">
+        <v>0.2333</v>
+      </c>
+      <c r="U16">
+        <v>0.2173</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2355</v>
+        <v>0.2053</v>
       </c>
       <c r="X16">
         <v>0.2194</v>
       </c>
       <c r="Y16">
-        <v>1.0233</v>
+        <v>0.9313</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2256,22 +2256,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.47</v>
+        <v>3.82</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.1666</v>
+        <v>0.1567</v>
       </c>
       <c r="AG16">
-        <v>1.0409</v>
+        <v>1.0633</v>
       </c>
       <c r="AH16">
         <v>0.22</v>
       </c>
       <c r="AM16">
-        <v>3.69</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2297,7 +2297,7 @@
         <v>822690</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I17">
         <v>6.5</v>
@@ -2330,7 +2330,7 @@
         <v>0.403</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T17">
         <v>0.2314</v>
@@ -2398,7 +2398,7 @@
         <v>822690</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I18">
         <v>5.3</v>
@@ -2431,7 +2431,7 @@
         <v>0.363</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T18">
         <v>0.2086</v>
@@ -2461,7 +2461,7 @@
         <v>6.26</v>
       </c>
       <c r="AE18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AF18">
         <v>0.3163</v>
@@ -2499,7 +2499,7 @@
         <v>824392</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I19">
         <v>3</v>
@@ -2532,7 +2532,7 @@
         <v>0.251</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T19">
         <v>0.1994</v>
@@ -2600,7 +2600,7 @@
         <v>824392</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I20">
         <v>5.7</v>
@@ -2633,7 +2633,7 @@
         <v>0.346</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T20">
         <v>0.2084</v>
@@ -2692,7 +2692,7 @@
         <v>823582</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -2725,7 +2725,7 @@
         <v>0.024</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T21">
         <v>0.2425</v>
@@ -2793,7 +2793,7 @@
         <v>823582</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I22">
         <v>5.8</v>
@@ -2826,7 +2826,7 @@
         <v>0.379</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T22">
         <v>0.2057</v>
@@ -2894,7 +2894,7 @@
         <v>822936</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I23">
         <v>4.9</v>
@@ -2927,7 +2927,7 @@
         <v>0.342</v>
       </c>
       <c r="S23" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T23">
         <v>0.1524</v>
@@ -2995,7 +2995,7 @@
         <v>822936</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I24">
         <v>5.9</v>
@@ -3028,7 +3028,7 @@
         <v>0.377</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T24">
         <v>0.1918</v>
@@ -3087,7 +3087,7 @@
         <v>824874</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I25">
         <v>3</v>
@@ -3120,7 +3120,7 @@
         <v>0.177</v>
       </c>
       <c r="S25" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T25">
         <v>0.2331</v>
@@ -3188,7 +3188,7 @@
         <v>824874</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I26">
         <v>5.1</v>
@@ -3221,7 +3221,7 @@
         <v>0.336</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T26">
         <v>0.241</v>
@@ -3289,7 +3289,7 @@
         <v>823741</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -3322,7 +3322,7 @@
         <v>0.363</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T27">
         <v>0.2241</v>
@@ -3390,7 +3390,7 @@
         <v>823741</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I28">
         <v>5.2</v>
@@ -3423,7 +3423,7 @@
         <v>0.371</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T28">
         <v>0.2284</v>
@@ -3482,7 +3482,7 @@
         <v>824961</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I29">
         <v>5.8</v>
@@ -3515,7 +3515,7 @@
         <v>0.373</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T29">
         <v>0.2083</v>
@@ -3574,7 +3574,7 @@
         <v>824961</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I30">
         <v>4.6</v>
@@ -3607,7 +3607,7 @@
         <v>0.359</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T30">
         <v>0.2675</v>
@@ -3637,7 +3637,7 @@
         <v>6.13</v>
       </c>
       <c r="AE30" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AF30">
         <v>0.2327</v>
@@ -3675,7 +3675,7 @@
         <v>823986</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I31">
         <v>6.2</v>
@@ -3708,7 +3708,7 @@
         <v>0.381</v>
       </c>
       <c r="S31" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T31">
         <v>0.2892</v>
@@ -3738,7 +3738,7 @@
         <v>10.96</v>
       </c>
       <c r="AE31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AF31">
         <v>0.2859</v>
@@ -3776,7 +3776,7 @@
         <v>823986</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I32">
         <v>4.8</v>
@@ -3809,7 +3809,7 @@
         <v>0.346</v>
       </c>
       <c r="S32" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T32">
         <v>0.1503</v>
@@ -3871,7 +3871,7 @@
         <v>-155</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="G33" t="s">
         <v>44</v>
@@ -3912,7 +3912,7 @@
         <v>824874</v>
       </c>
       <c r="H34" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I34">
         <v>4.9</v>

--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="97">
   <si>
     <t>date</t>
   </si>
@@ -133,97 +133,94 @@
     <t>08/29/2026</t>
   </si>
   <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>Alec Gamboa</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Max Fried</t>
+  </si>
+  <si>
+    <t>Blake Snell</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Erick Fedde</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ San Francisco Giants</t>
+  </si>
+  <si>
     <t>Mitch Bratt</t>
   </si>
   <si>
-    <t>Arizona Diamondbacks @ San Francisco Giants</t>
-  </si>
-  <si>
     <t>Limited starter</t>
-  </si>
-  <si>
-    <t>team_season_vs_hand</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>Carlos Rodón</t>
-  </si>
-  <si>
-    <t>Alec Gamboa</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Max Fried</t>
-  </si>
-  <si>
-    <t>Blake Snell</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Erick Fedde</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
   </si>
   <si>
     <t>Sandy Alcantara</t>
@@ -818,25 +815,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-111</v>
+        <v>-116</v>
       </c>
       <c r="E2">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823176</v>
+        <v>823539</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -848,37 +845,43 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>0.1591</v>
+        <v>0.1984</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="P2">
-        <v>4.44</v>
+        <v>3.98</v>
       </c>
       <c r="Q2">
-        <v>0.1818</v>
+        <v>0.2393</v>
       </c>
       <c r="R2">
-        <v>0.331</v>
+        <v>0.369</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
+      <c r="T2">
+        <v>0.2529</v>
+      </c>
+      <c r="U2">
+        <v>0.2729</v>
+      </c>
       <c r="V2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2355</v>
+        <v>0.2499</v>
       </c>
       <c r="X2">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y2">
-        <v>1.0233</v>
+        <v>1.0351</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -887,22 +890,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.47</v>
+        <v>5.9</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1666</v>
+        <v>0.2135</v>
       </c>
       <c r="AG2">
-        <v>1.0409</v>
+        <v>1.1462</v>
       </c>
       <c r="AH2">
         <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>3.69</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -913,25 +916,25 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
-        <v>-116</v>
+        <v>-108</v>
       </c>
       <c r="E3">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>823539</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I3">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -943,43 +946,43 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>0.1984</v>
+        <v>0.2551</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="P3">
-        <v>3.98</v>
+        <v>4.19</v>
       </c>
       <c r="Q3">
-        <v>0.2393</v>
+        <v>0.2292</v>
       </c>
       <c r="R3">
-        <v>0.369</v>
+        <v>0.324</v>
       </c>
       <c r="S3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2529</v>
+        <v>0.1914</v>
       </c>
       <c r="U3">
-        <v>0.2729</v>
+        <v>0.1846</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2499</v>
+        <v>0.21</v>
       </c>
       <c r="X3">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y3">
-        <v>1.0351</v>
+        <v>0.9697</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -988,22 +991,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.94</v>
+        <v>4.27</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2135</v>
+        <v>0.2467</v>
       </c>
       <c r="AG3">
-        <v>1.1524</v>
+        <v>0.8676</v>
       </c>
       <c r="AH3">
         <v>0.22</v>
       </c>
       <c r="AM3">
-        <v>6.16</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1011,76 +1014,67 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-      <c r="D4">
-        <v>-108</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>823539</v>
+        <v>823501</v>
       </c>
       <c r="H4" t="s">
         <v>48</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.2551</v>
+        <v>0.1765</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>4.19</v>
+        <v>3.86</v>
       </c>
       <c r="Q4">
-        <v>0.2292</v>
+        <v>0.2222</v>
       </c>
       <c r="R4">
-        <v>0.324</v>
+        <v>0.043</v>
       </c>
       <c r="S4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1914</v>
+        <v>0.2693</v>
       </c>
       <c r="U4">
-        <v>0.1846</v>
+        <v>0.2681</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.21</v>
+        <v>0.2499</v>
       </c>
       <c r="X4">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y4">
-        <v>0.9697</v>
+        <v>1.0597</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1089,22 +1083,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.29</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2467</v>
+        <v>0.1784</v>
       </c>
       <c r="AG4">
-        <v>0.8724</v>
+        <v>1.2206</v>
       </c>
       <c r="AH4">
         <v>0.22</v>
       </c>
       <c r="AM4">
-        <v>4.51</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1112,67 +1106,76 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+      <c r="D5">
+        <v>-130</v>
+      </c>
+      <c r="E5">
+        <v>105</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G5">
         <v>823501</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I5">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>0.175</v>
+        <v>0.2392</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="P5">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="Q5">
-        <v>0.25</v>
+        <v>0.2857</v>
       </c>
       <c r="R5">
-        <v>0.02</v>
+        <v>0.313</v>
       </c>
       <c r="S5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2693</v>
+        <v>0.1859</v>
       </c>
       <c r="U5">
-        <v>0.2681</v>
+        <v>0.1814</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2499</v>
+        <v>0.21</v>
       </c>
       <c r="X5">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y5">
-        <v>1.0597</v>
+        <v>0.9794</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1181,22 +1184,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>1.18</v>
+        <v>4.54</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1765</v>
+        <v>0.2537</v>
       </c>
       <c r="AG5">
-        <v>1.2273</v>
+        <v>0.8425</v>
       </c>
       <c r="AH5">
         <v>0.22</v>
       </c>
       <c r="AM5">
-        <v>1.4</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1204,28 +1207,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D6">
-        <v>-130</v>
+        <v>-120</v>
       </c>
       <c r="E6">
-        <v>105</v>
+        <v>-105</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>823501</v>
+        <v>824230</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I6">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1234,46 +1237,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>0.238</v>
+        <v>0.3303</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="P6">
-        <v>3.85</v>
+        <v>4.19</v>
       </c>
       <c r="Q6">
-        <v>0.3152</v>
+        <v>0.3303</v>
       </c>
       <c r="R6">
-        <v>0.315</v>
+        <v>0.353</v>
       </c>
       <c r="S6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.1859</v>
+        <v>0.2179</v>
       </c>
       <c r="U6">
-        <v>0.1814</v>
+        <v>0.211</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.21</v>
+        <v>0.2313</v>
       </c>
       <c r="X6">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y6">
-        <v>0.9794</v>
+        <v>0.9742</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1282,22 +1285,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.82</v>
+        <v>6.93</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF6">
-        <v>0.2623</v>
+        <v>0.3303</v>
       </c>
       <c r="AG6">
-        <v>0.8471</v>
+        <v>0.9876</v>
       </c>
       <c r="AH6">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="AM6">
-        <v>5.04</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1305,28 +1308,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
-        <v>-120</v>
+        <v>-108</v>
       </c>
       <c r="E7">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>824230</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1338,43 +1341,43 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>0.3303</v>
+        <v>0.1655</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P7">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>0.3303</v>
+        <v>0.115</v>
       </c>
       <c r="R7">
-        <v>0.353</v>
+        <v>0.361</v>
       </c>
       <c r="S7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2179</v>
+        <v>0.2129</v>
       </c>
       <c r="U7">
-        <v>0.211</v>
+        <v>0.2125</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2313</v>
+        <v>0.2058</v>
       </c>
       <c r="X7">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y7">
-        <v>0.9742</v>
+        <v>0.991</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1383,22 +1386,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.97</v>
+        <v>3.19</v>
       </c>
       <c r="AE7" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.3303</v>
+        <v>0.1473</v>
       </c>
       <c r="AG7">
-        <v>0.993</v>
+        <v>0.965</v>
       </c>
       <c r="AH7">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM7">
-        <v>6.42</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1406,28 +1409,19 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8">
-        <v>3.5</v>
-      </c>
-      <c r="D8">
-        <v>-108</v>
-      </c>
-      <c r="E8">
-        <v>-115</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
       </c>
       <c r="G8">
-        <v>824230</v>
+        <v>823665</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1436,46 +1430,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>0.1655</v>
+        <v>0.1654</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>4.31</v>
       </c>
       <c r="Q8">
-        <v>0.115</v>
+        <v>0.2211</v>
       </c>
       <c r="R8">
-        <v>0.361</v>
+        <v>0.322</v>
       </c>
       <c r="S8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2129</v>
+        <v>0.2021</v>
       </c>
       <c r="U8">
-        <v>0.2125</v>
+        <v>0.1907</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2058</v>
+        <v>0.2071</v>
       </c>
       <c r="X8">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y8">
-        <v>0.991</v>
+        <v>0.936</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1484,22 +1478,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1473</v>
+        <v>0.1833</v>
       </c>
       <c r="AG8">
-        <v>0.9702</v>
+        <v>0.916</v>
       </c>
       <c r="AH8">
         <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>3.43</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1507,19 +1501,19 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>823665</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1531,43 +1525,43 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0.1654</v>
+        <v>0.1656</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="P9">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="Q9">
-        <v>0.2211</v>
+        <v>0.1441</v>
       </c>
       <c r="R9">
-        <v>0.322</v>
+        <v>0.357</v>
       </c>
       <c r="S9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2021</v>
+        <v>0.2522</v>
       </c>
       <c r="U9">
-        <v>0.1907</v>
+        <v>0.2525</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2071</v>
+        <v>0.2367</v>
       </c>
       <c r="X9">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y9">
-        <v>0.936</v>
+        <v>1.0323</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1576,22 +1570,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.29</v>
+        <v>4.23</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.1833</v>
+        <v>0.158</v>
       </c>
       <c r="AG9">
-        <v>0.921</v>
+        <v>1.1432</v>
       </c>
       <c r="AH9">
         <v>0.22</v>
       </c>
       <c r="AM9">
-        <v>3.51</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1599,22 +1593,22 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>823665</v>
+        <v>823011</v>
       </c>
       <c r="H10" t="s">
         <v>48</v>
       </c>
       <c r="I10">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1623,43 +1617,43 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0.1656</v>
+        <v>0.25</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="P10">
-        <v>4.21</v>
+        <v>4.09</v>
       </c>
       <c r="Q10">
-        <v>0.1441</v>
+        <v>0.2609</v>
       </c>
       <c r="R10">
-        <v>0.357</v>
+        <v>0.187</v>
       </c>
       <c r="S10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2522</v>
+        <v>0.2511</v>
       </c>
       <c r="U10">
-        <v>0.2525</v>
+        <v>0.2169</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2367</v>
+        <v>0.2156</v>
       </c>
       <c r="X10">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y10">
-        <v>1.0323</v>
+        <v>0.8961</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1668,22 +1662,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.26</v>
+        <v>2.45</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.158</v>
+        <v>0.252</v>
       </c>
       <c r="AG10">
-        <v>1.1494</v>
+        <v>1.138</v>
       </c>
       <c r="AH10">
         <v>0.22</v>
       </c>
       <c r="AM10">
-        <v>4.48</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1691,22 +1685,22 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>823011</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1715,43 +1709,43 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.25</v>
+        <v>0.2165</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="P11">
-        <v>4.09</v>
+        <v>4.21</v>
       </c>
       <c r="Q11">
-        <v>0.2609</v>
+        <v>0.3034</v>
       </c>
       <c r="R11">
-        <v>0.187</v>
+        <v>0.308</v>
       </c>
       <c r="S11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2511</v>
+        <v>0.2509</v>
       </c>
       <c r="U11">
-        <v>0.2169</v>
+        <v>0.2463</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2156</v>
+        <v>0.237</v>
       </c>
       <c r="X11">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y11">
-        <v>0.8961</v>
+        <v>1.0293</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1760,22 +1754,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>2.47</v>
+        <v>5.97</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.252</v>
+        <v>0.2433</v>
       </c>
       <c r="AG11">
-        <v>1.1442</v>
+        <v>1.1372</v>
       </c>
       <c r="AH11">
         <v>0.22</v>
       </c>
       <c r="AM11">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1783,19 +1777,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="C12">
+        <v>3.5</v>
+      </c>
+      <c r="D12">
+        <v>-156</v>
+      </c>
+      <c r="E12">
+        <v>126</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
-        <v>823011</v>
+        <v>824637</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1804,46 +1807,46 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>0.2165</v>
+        <v>0.1772</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="P12">
-        <v>4.21</v>
+        <v>4.38</v>
       </c>
       <c r="Q12">
-        <v>0.3034</v>
+        <v>0.1653</v>
       </c>
       <c r="R12">
-        <v>0.308</v>
+        <v>0.377</v>
       </c>
       <c r="S12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2509</v>
+        <v>0.1662</v>
       </c>
       <c r="U12">
-        <v>0.2463</v>
+        <v>0.1874</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.237</v>
+        <v>0.2172</v>
       </c>
       <c r="X12">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y12">
-        <v>1.0293</v>
+        <v>0.8905</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1852,22 +1855,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>2.69</v>
       </c>
       <c r="AE12" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2433</v>
+        <v>0.1727</v>
       </c>
       <c r="AG12">
-        <v>1.1434</v>
+        <v>0.7534</v>
       </c>
       <c r="AH12">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM12">
-        <v>5.45</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1875,28 +1878,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C13">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D13">
-        <v>-156</v>
+        <v>112</v>
       </c>
       <c r="E13">
-        <v>126</v>
+        <v>-130</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>824637</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I13">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1908,43 +1911,43 @@
         <v>4</v>
       </c>
       <c r="M13">
-        <v>0.1772</v>
+        <v>0.2378</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="P13">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="Q13">
-        <v>0.1653</v>
+        <v>0.25</v>
       </c>
       <c r="R13">
-        <v>0.377</v>
+        <v>0.367</v>
       </c>
       <c r="S13" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1662</v>
+        <v>0.2556</v>
       </c>
       <c r="U13">
-        <v>0.1874</v>
+        <v>0.2652</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2172</v>
+        <v>0.2548</v>
       </c>
       <c r="X13">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y13">
-        <v>0.8905</v>
+        <v>1.12</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1953,22 +1956,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>2.7</v>
+        <v>7.37</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="AF13">
-        <v>0.1727</v>
+        <v>0.2423</v>
       </c>
       <c r="AG13">
-        <v>0.7575</v>
+        <v>1.1585</v>
       </c>
       <c r="AH13">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>2.92</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1976,13 +1979,13 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D14">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E14">
         <v>-130</v>
@@ -1991,13 +1994,13 @@
         <v>65</v>
       </c>
       <c r="G14">
-        <v>824637</v>
+        <v>822770</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2006,46 +2009,46 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>0.2378</v>
+        <v>0.2365</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="P14">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="Q14">
-        <v>0.25</v>
+        <v>0.1849</v>
       </c>
       <c r="R14">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="S14" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2556</v>
+        <v>0.2675</v>
       </c>
       <c r="U14">
-        <v>0.2652</v>
+        <v>0.233</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2548</v>
+        <v>0.2264</v>
       </c>
       <c r="X14">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y14">
-        <v>1.12</v>
+        <v>0.9726</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2054,22 +2057,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>7.41</v>
+        <v>5.98</v>
       </c>
       <c r="AE14" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2423</v>
+        <v>0.2172</v>
       </c>
       <c r="AG14">
-        <v>1.1648</v>
+        <v>1.2125</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AM14">
-        <v>7.41</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2077,28 +2080,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C15">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D15">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="E15">
-        <v>-130</v>
+        <v>-170</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G15">
-        <v>822770</v>
+        <v>823177</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2107,46 +2110,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2365</v>
+        <v>0.1542</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P15">
-        <v>4.16</v>
+        <v>4.35</v>
       </c>
       <c r="Q15">
-        <v>0.1849</v>
+        <v>0.161</v>
       </c>
       <c r="R15">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="S15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2675</v>
+        <v>0.2333</v>
       </c>
       <c r="U15">
-        <v>0.233</v>
+        <v>0.2173</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2264</v>
+        <v>0.2053</v>
       </c>
       <c r="X15">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y15">
-        <v>0.9726</v>
+        <v>0.9313</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2155,22 +2158,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>6.01</v>
+        <v>3.8</v>
       </c>
       <c r="AE15" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2172</v>
+        <v>0.1567</v>
       </c>
       <c r="AG15">
-        <v>1.2191</v>
+        <v>1.0575</v>
       </c>
       <c r="AH15">
-        <v>-0.55</v>
+        <v>0.22</v>
       </c>
       <c r="AM15">
-        <v>5.46</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2178,28 +2181,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D16">
-        <v>134</v>
+        <v>-111</v>
       </c>
       <c r="E16">
-        <v>-170</v>
+        <v>-104</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G16">
-        <v>823177</v>
+        <v>823176</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="I16">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2208,46 +2211,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>0.1542</v>
+        <v>0.1591</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="P16">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="Q16">
-        <v>0.161</v>
+        <v>0.1818</v>
       </c>
       <c r="R16">
-        <v>0.371</v>
+        <v>0.331</v>
       </c>
       <c r="S16" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2333</v>
+        <v>0.2497</v>
       </c>
       <c r="U16">
-        <v>0.2173</v>
+        <v>0.2222</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2053</v>
+        <v>0.2355</v>
       </c>
       <c r="X16">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y16">
-        <v>0.9313</v>
+        <v>1.0677</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2256,22 +2259,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.1567</v>
+        <v>0.1666</v>
       </c>
       <c r="AG16">
-        <v>1.0633</v>
+        <v>1.1319</v>
       </c>
       <c r="AH16">
         <v>0.22</v>
       </c>
       <c r="AM16">
-        <v>4.04</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2279,7 +2282,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2291,13 +2294,13 @@
         <v>-150</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17">
         <v>822690</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I17">
         <v>6.5</v>
@@ -2330,7 +2333,7 @@
         <v>0.403</v>
       </c>
       <c r="S17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T17">
         <v>0.2314</v>
@@ -2345,7 +2348,7 @@
         <v>0.206</v>
       </c>
       <c r="X17">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y17">
         <v>0.9921</v>
@@ -2357,7 +2360,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2366,13 +2369,13 @@
         <v>0.1663</v>
       </c>
       <c r="AG17">
-        <v>1.0544</v>
+        <v>1.0487</v>
       </c>
       <c r="AH17">
         <v>0.22</v>
       </c>
       <c r="AM17">
-        <v>4.92</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2380,7 +2383,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>6.5</v>
@@ -2392,13 +2395,13 @@
         <v>-128</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G18">
         <v>822690</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I18">
         <v>5.3</v>
@@ -2431,7 +2434,7 @@
         <v>0.363</v>
       </c>
       <c r="S18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T18">
         <v>0.2086</v>
@@ -2446,7 +2449,7 @@
         <v>0.2128</v>
       </c>
       <c r="X18">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y18">
         <v>0.9439</v>
@@ -2458,22 +2461,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.26</v>
+        <v>6.23</v>
       </c>
       <c r="AE18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AF18">
         <v>0.3163</v>
       </c>
       <c r="AG18">
-        <v>0.9508</v>
+        <v>0.9456</v>
       </c>
       <c r="AH18">
         <v>-0.55</v>
       </c>
       <c r="AM18">
-        <v>5.71</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2481,7 +2484,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19">
         <v>2.5</v>
@@ -2493,13 +2496,13 @@
         <v>-107</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G19">
         <v>824392</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I19">
         <v>3</v>
@@ -2532,7 +2535,7 @@
         <v>0.251</v>
       </c>
       <c r="S19" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T19">
         <v>0.1994</v>
@@ -2547,7 +2550,7 @@
         <v>0.2232</v>
       </c>
       <c r="X19">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y19">
         <v>0.88</v>
@@ -2559,7 +2562,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2568,13 +2571,13 @@
         <v>0.179</v>
       </c>
       <c r="AG19">
-        <v>0.9086</v>
+        <v>0.9036</v>
       </c>
       <c r="AH19">
         <v>0.22</v>
       </c>
       <c r="AM19">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2582,7 +2585,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>5.5</v>
@@ -2594,13 +2597,13 @@
         <v>-108</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G20">
         <v>824392</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I20">
         <v>5.7</v>
@@ -2633,7 +2636,7 @@
         <v>0.346</v>
       </c>
       <c r="S20" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T20">
         <v>0.2084</v>
@@ -2648,7 +2651,7 @@
         <v>0.2135</v>
       </c>
       <c r="X20">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y20">
         <v>1.0087</v>
@@ -2660,7 +2663,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2669,13 +2672,13 @@
         <v>0.2194</v>
       </c>
       <c r="AG20">
-        <v>0.9495</v>
+        <v>0.9443</v>
       </c>
       <c r="AH20">
         <v>0.22</v>
       </c>
       <c r="AM20">
-        <v>5.12</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2683,16 +2686,16 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" t="s">
         <v>77</v>
-      </c>
-      <c r="F21" t="s">
-        <v>78</v>
       </c>
       <c r="G21">
         <v>823582</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -2725,7 +2728,7 @@
         <v>0.024</v>
       </c>
       <c r="S21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T21">
         <v>0.2425</v>
@@ -2740,7 +2743,7 @@
         <v>0.2331</v>
       </c>
       <c r="X21">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y21">
         <v>0.9768</v>
@@ -2761,7 +2764,7 @@
         <v>0.2203</v>
       </c>
       <c r="AG21">
-        <v>1.1053</v>
+        <v>1.0993</v>
       </c>
       <c r="AH21">
         <v>0.22</v>
@@ -2775,7 +2778,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2787,13 +2790,13 @@
         <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G22">
         <v>823582</v>
       </c>
       <c r="H22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I22">
         <v>5.8</v>
@@ -2826,7 +2829,7 @@
         <v>0.379</v>
       </c>
       <c r="S22" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T22">
         <v>0.2057</v>
@@ -2841,7 +2844,7 @@
         <v>0.2188</v>
       </c>
       <c r="X22">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y22">
         <v>0.9509</v>
@@ -2853,7 +2856,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.11</v>
+        <v>5.08</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
@@ -2862,13 +2865,13 @@
         <v>0.2404</v>
       </c>
       <c r="AG22">
-        <v>0.9372</v>
+        <v>0.9321</v>
       </c>
       <c r="AH22">
         <v>0.22</v>
       </c>
       <c r="AM22">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2876,7 +2879,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C23">
         <v>3.5</v>
@@ -2888,13 +2891,13 @@
         <v>-122</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>822936</v>
       </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I23">
         <v>4.9</v>
@@ -2927,7 +2930,7 @@
         <v>0.342</v>
       </c>
       <c r="S23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T23">
         <v>0.1524</v>
@@ -2942,7 +2945,7 @@
         <v>0.1861</v>
       </c>
       <c r="X23">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y23">
         <v>0.88</v>
@@ -2954,7 +2957,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -2963,13 +2966,13 @@
         <v>0.1931</v>
       </c>
       <c r="AG23">
-        <v>0.6943</v>
+        <v>0.6905</v>
       </c>
       <c r="AH23">
         <v>0.22</v>
       </c>
       <c r="AM23">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2977,7 +2980,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -2989,13 +2992,13 @@
         <v>-111</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G24">
         <v>822936</v>
       </c>
       <c r="H24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I24">
         <v>5.9</v>
@@ -3028,7 +3031,7 @@
         <v>0.377</v>
       </c>
       <c r="S24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T24">
         <v>0.1918</v>
@@ -3043,7 +3046,7 @@
         <v>0.2151</v>
       </c>
       <c r="X24">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y24">
         <v>1.0075</v>
@@ -3055,7 +3058,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -3064,13 +3067,13 @@
         <v>0.1603</v>
       </c>
       <c r="AG24">
-        <v>0.8741</v>
+        <v>0.8693</v>
       </c>
       <c r="AH24">
         <v>0.22</v>
       </c>
       <c r="AM24">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3078,16 +3081,16 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" t="s">
         <v>83</v>
-      </c>
-      <c r="F25" t="s">
-        <v>84</v>
       </c>
       <c r="G25">
         <v>824874</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I25">
         <v>3</v>
@@ -3120,7 +3123,7 @@
         <v>0.177</v>
       </c>
       <c r="S25" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T25">
         <v>0.2331</v>
@@ -3132,10 +3135,10 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2205</v>
+        <v>0.2197</v>
       </c>
       <c r="X25">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y25">
         <v>0.988</v>
@@ -3147,7 +3150,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
@@ -3156,13 +3159,13 @@
         <v>0.1484</v>
       </c>
       <c r="AG25">
-        <v>1.0624</v>
+        <v>1.0566</v>
       </c>
       <c r="AH25">
         <v>0.22</v>
       </c>
       <c r="AM25">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3170,7 +3173,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3182,13 +3185,13 @@
         <v>-107</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G26">
         <v>824874</v>
       </c>
       <c r="H26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I26">
         <v>5.1</v>
@@ -3221,7 +3224,7 @@
         <v>0.336</v>
       </c>
       <c r="S26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T26">
         <v>0.241</v>
@@ -3233,10 +3236,10 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2484</v>
+        <v>0.2478</v>
       </c>
       <c r="X26">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y26">
         <v>1.0258</v>
@@ -3248,7 +3251,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3257,13 +3260,13 @@
         <v>0.1743</v>
       </c>
       <c r="AG26">
-        <v>1.098</v>
+        <v>1.0921</v>
       </c>
       <c r="AH26">
         <v>0.22</v>
       </c>
       <c r="AM26">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3271,7 +3274,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3283,16 +3286,16 @@
         <v>-170</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G27">
         <v>823741</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3304,25 +3307,25 @@
         <v>2</v>
       </c>
       <c r="M27">
-        <v>0.1729</v>
+        <v>0.1848</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P27">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Q27">
-        <v>0.2456</v>
+        <v>0.25</v>
       </c>
       <c r="R27">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="S27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T27">
         <v>0.2241</v>
@@ -3337,7 +3340,7 @@
         <v>0.2135</v>
       </c>
       <c r="X27">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y27">
         <v>1.0476</v>
@@ -3349,22 +3352,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.44</v>
+        <v>4.67</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.1988</v>
+        <v>0.2087</v>
       </c>
       <c r="AG27">
-        <v>1.0212</v>
+        <v>1.0156</v>
       </c>
       <c r="AH27">
         <v>0.22</v>
       </c>
       <c r="AM27">
-        <v>4.66</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3372,7 +3375,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -3384,13 +3387,13 @@
         <v>-113</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G28">
         <v>823741</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I28">
         <v>5.2</v>
@@ -3405,25 +3408,25 @@
         <v>2</v>
       </c>
       <c r="M28">
-        <v>0.2342</v>
+        <v>0.2361</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P28">
         <v>4.22</v>
       </c>
       <c r="Q28">
-        <v>0.2288</v>
+        <v>0.2348</v>
       </c>
       <c r="R28">
-        <v>0.371</v>
+        <v>0.365</v>
       </c>
       <c r="S28" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T28">
         <v>0.2284</v>
@@ -3438,7 +3441,7 @@
         <v>0.2412</v>
       </c>
       <c r="X28">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y28">
         <v>1.0739</v>
@@ -3450,22 +3453,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.74</v>
+        <v>5.79</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.2322</v>
+        <v>0.2356</v>
       </c>
       <c r="AG28">
-        <v>1.041</v>
+        <v>1.0354</v>
       </c>
       <c r="AH28">
         <v>0.22</v>
       </c>
       <c r="AM28">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3473,16 +3476,16 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" t="s">
         <v>89</v>
-      </c>
-      <c r="F29" t="s">
-        <v>90</v>
       </c>
       <c r="G29">
         <v>824961</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I29">
         <v>5.8</v>
@@ -3515,7 +3518,7 @@
         <v>0.373</v>
       </c>
       <c r="S29" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T29">
         <v>0.2083</v>
@@ -3530,7 +3533,7 @@
         <v>0.2143</v>
       </c>
       <c r="X29">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y29">
         <v>1.0603</v>
@@ -3542,7 +3545,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>5.47</v>
+        <v>5.44</v>
       </c>
       <c r="AE29" t="s">
         <v>45</v>
@@ -3551,13 +3554,13 @@
         <v>0.219</v>
       </c>
       <c r="AG29">
-        <v>0.9494</v>
+        <v>0.9443</v>
       </c>
       <c r="AH29">
         <v>0.22</v>
       </c>
       <c r="AM29">
-        <v>5.69</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3565,16 +3568,16 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G30">
         <v>824961</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I30">
         <v>4.6</v>
@@ -3607,7 +3610,7 @@
         <v>0.359</v>
       </c>
       <c r="S30" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T30">
         <v>0.2675</v>
@@ -3622,7 +3625,7 @@
         <v>0.237</v>
       </c>
       <c r="X30">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y30">
         <v>1.0306</v>
@@ -3634,22 +3637,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>6.13</v>
+        <v>6.09</v>
       </c>
       <c r="AE30" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AF30">
         <v>0.2327</v>
       </c>
       <c r="AG30">
-        <v>1.2189</v>
+        <v>1.2123</v>
       </c>
       <c r="AH30">
         <v>-0.55</v>
       </c>
       <c r="AM30">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3657,7 +3660,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C31">
         <v>7.5</v>
@@ -3669,13 +3672,13 @@
         <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G31">
         <v>823986</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I31">
         <v>6.2</v>
@@ -3708,7 +3711,7 @@
         <v>0.381</v>
       </c>
       <c r="S31" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T31">
         <v>0.2892</v>
@@ -3723,7 +3726,7 @@
         <v>0.2492</v>
       </c>
       <c r="X31">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y31">
         <v>1.12</v>
@@ -3735,22 +3738,22 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>10.96</v>
+        <v>10.9</v>
       </c>
       <c r="AE31" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AF31">
         <v>0.2859</v>
       </c>
       <c r="AG31">
-        <v>1.318</v>
+        <v>1.3109</v>
       </c>
       <c r="AH31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>10.96</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3758,7 +3761,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -3770,13 +3773,13 @@
         <v>-130</v>
       </c>
       <c r="F32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G32">
         <v>823986</v>
       </c>
       <c r="H32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I32">
         <v>4.8</v>
@@ -3809,7 +3812,7 @@
         <v>0.346</v>
       </c>
       <c r="S32" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T32">
         <v>0.1503</v>
@@ -3824,7 +3827,7 @@
         <v>0.222</v>
       </c>
       <c r="X32">
-        <v>0.2194</v>
+        <v>0.2206</v>
       </c>
       <c r="Y32">
         <v>0.9957</v>
@@ -3836,7 +3839,7 @@
         <v>44</v>
       </c>
       <c r="AD32">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AE32" t="s">
         <v>45</v>
@@ -3845,13 +3848,13 @@
         <v>0.1631</v>
       </c>
       <c r="AG32">
-        <v>0.6851</v>
+        <v>0.6813</v>
       </c>
       <c r="AH32">
         <v>0.22</v>
       </c>
       <c r="AM32">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3859,7 +3862,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33">
         <v>3.5</v>
@@ -3871,7 +3874,7 @@
         <v>-155</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
         <v>44</v>
@@ -3903,16 +3906,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G34">
         <v>824874</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I34">
         <v>4.9</v>
@@ -3945,7 +3948,7 @@
         <v>0.39</v>
       </c>
       <c r="S34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T34">
         <v>0.225</v>

--- a/data/k-props/2026-08-29.xlsx
+++ b/data/k-props/2026-08-29.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="101">
   <si>
     <t>date</t>
   </si>
@@ -145,21 +145,30 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Alec Gamboa</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Carlos Rodón</t>
-  </si>
-  <si>
-    <t>Alec Gamboa</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
     <t>Max Fried</t>
   </si>
   <si>
@@ -230,6 +239,9 @@
   </si>
   <si>
     <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>Daniel Lynch IV</t>
@@ -883,17 +895,23 @@
       <c r="Y2">
         <v>1.0351</v>
       </c>
+      <c r="Z2">
+        <v>7</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>1.62</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>5.9</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.2135</v>
@@ -903,6 +921,18 @@
       </c>
       <c r="AH2">
         <v>0.22</v>
+      </c>
+      <c r="AI2">
+        <v>1.1</v>
+      </c>
+      <c r="AJ2">
+        <v>1.1</v>
+      </c>
+      <c r="AK2">
+        <v>0.88</v>
+      </c>
+      <c r="AL2">
+        <v>0.88</v>
       </c>
       <c r="AM2">
         <v>6.12</v>
@@ -913,7 +943,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>5.5</v>
@@ -984,17 +1014,23 @@
       <c r="Y3">
         <v>0.9697</v>
       </c>
+      <c r="Z3">
+        <v>5</v>
+      </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>-1.01</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD3">
         <v>4.27</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.2467</v>
@@ -1004,6 +1040,18 @@
       </c>
       <c r="AH3">
         <v>0.22</v>
+      </c>
+      <c r="AI3">
+        <v>0.73</v>
+      </c>
+      <c r="AJ3">
+        <v>0.73</v>
+      </c>
+      <c r="AK3">
+        <v>0.51</v>
+      </c>
+      <c r="AL3">
+        <v>0.51</v>
       </c>
       <c r="AM3">
         <v>4.49</v>
@@ -1014,7 +1062,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>41</v>
@@ -1023,7 +1071,7 @@
         <v>823501</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <v>1.3</v>
@@ -1077,16 +1125,16 @@
         <v>1.0597</v>
       </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD4">
         <v>1.19</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>0.1784</v>
@@ -1106,7 +1154,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1177,17 +1225,23 @@
       <c r="Y5">
         <v>0.9794</v>
       </c>
+      <c r="Z5">
+        <v>4</v>
+      </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB5">
+        <v>0.26</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD5">
         <v>4.54</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>0.2537</v>
@@ -1197,6 +1251,18 @@
       </c>
       <c r="AH5">
         <v>0.22</v>
+      </c>
+      <c r="AI5">
+        <v>-0.54</v>
+      </c>
+      <c r="AJ5">
+        <v>0.54</v>
+      </c>
+      <c r="AK5">
+        <v>-0.76</v>
+      </c>
+      <c r="AL5">
+        <v>0.76</v>
       </c>
       <c r="AM5">
         <v>4.76</v>
@@ -1207,7 +1273,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>6.5</v>
@@ -1219,7 +1285,7 @@
         <v>-105</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>824230</v>
@@ -1278,17 +1344,23 @@
       <c r="Y6">
         <v>0.9742</v>
       </c>
+      <c r="Z6">
+        <v>10</v>
+      </c>
       <c r="AA6" t="s">
         <v>44</v>
       </c>
+      <c r="AB6">
+        <v>-0.12</v>
+      </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD6">
         <v>6.93</v>
       </c>
       <c r="AE6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AF6">
         <v>0.3303</v>
@@ -1298,6 +1370,18 @@
       </c>
       <c r="AH6">
         <v>-0.55</v>
+      </c>
+      <c r="AI6">
+        <v>3.07</v>
+      </c>
+      <c r="AJ6">
+        <v>3.07</v>
+      </c>
+      <c r="AK6">
+        <v>3.62</v>
+      </c>
+      <c r="AL6">
+        <v>3.62</v>
       </c>
       <c r="AM6">
         <v>6.38</v>
@@ -1308,7 +1392,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -1320,7 +1404,7 @@
         <v>-115</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>824230</v>
@@ -1379,17 +1463,23 @@
       <c r="Y7">
         <v>0.991</v>
       </c>
+      <c r="Z7">
+        <v>3</v>
+      </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB7">
+        <v>-0.09</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD7">
         <v>3.19</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>0.1473</v>
@@ -1399,6 +1489,18 @@
       </c>
       <c r="AH7">
         <v>0.22</v>
+      </c>
+      <c r="AI7">
+        <v>-0.19</v>
+      </c>
+      <c r="AJ7">
+        <v>0.19</v>
+      </c>
+      <c r="AK7">
+        <v>-0.41</v>
+      </c>
+      <c r="AL7">
+        <v>0.41</v>
       </c>
       <c r="AM7">
         <v>3.41</v>
@@ -1409,10 +1511,10 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>823665</v>
@@ -1472,16 +1574,16 @@
         <v>0.936</v>
       </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD8">
         <v>3.27</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.1833</v>
@@ -1501,10 +1603,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>823665</v>
@@ -1564,16 +1666,16 @@
         <v>1.0323</v>
       </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD9">
         <v>4.23</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.158</v>
@@ -1593,16 +1695,16 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>823011</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I10">
         <v>2.3</v>
@@ -1656,16 +1758,16 @@
         <v>0.8961</v>
       </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD10">
         <v>2.45</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.252</v>
@@ -1685,10 +1787,10 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>823011</v>
@@ -1748,16 +1850,16 @@
         <v>1.0293</v>
       </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD11">
         <v>5.97</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.2433</v>
@@ -1777,7 +1879,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>3.5</v>
@@ -1789,7 +1891,7 @@
         <v>126</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>824637</v>
@@ -1848,17 +1950,23 @@
       <c r="Y12">
         <v>0.8905</v>
       </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB12">
+        <v>-0.59</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD12">
         <v>2.69</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.1727</v>
@@ -1868,6 +1976,18 @@
       </c>
       <c r="AH12">
         <v>0.22</v>
+      </c>
+      <c r="AI12">
+        <v>-1.69</v>
+      </c>
+      <c r="AJ12">
+        <v>1.69</v>
+      </c>
+      <c r="AK12">
+        <v>-1.91</v>
+      </c>
+      <c r="AL12">
+        <v>1.91</v>
       </c>
       <c r="AM12">
         <v>2.91</v>
@@ -1878,7 +1998,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C13">
         <v>6.5</v>
@@ -1890,7 +2010,7 @@
         <v>-130</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>824637</v>
@@ -1949,17 +2069,23 @@
       <c r="Y13">
         <v>1.12</v>
       </c>
+      <c r="Z13">
+        <v>7</v>
+      </c>
       <c r="AA13" t="s">
         <v>44</v>
       </c>
+      <c r="AB13">
+        <v>0.87</v>
+      </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD13">
         <v>7.37</v>
       </c>
       <c r="AE13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AF13">
         <v>0.2423</v>
@@ -1969,6 +2095,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>-0.37</v>
+      </c>
+      <c r="AJ13">
+        <v>0.37</v>
+      </c>
+      <c r="AK13">
+        <v>-0.37</v>
+      </c>
+      <c r="AL13">
+        <v>0.37</v>
       </c>
       <c r="AM13">
         <v>7.37</v>
@@ -1979,7 +2117,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -1991,7 +2129,7 @@
         <v>-130</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>822770</v>
@@ -2050,17 +2188,23 @@
       <c r="Y14">
         <v>0.9726</v>
       </c>
+      <c r="Z14">
+        <v>6</v>
+      </c>
       <c r="AA14" t="s">
         <v>44</v>
       </c>
+      <c r="AB14">
+        <v>0.7</v>
+      </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD14">
         <v>5.98</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.2172</v>
@@ -2070,6 +2214,18 @@
       </c>
       <c r="AH14">
         <v>0.22</v>
+      </c>
+      <c r="AI14">
+        <v>0.02</v>
+      </c>
+      <c r="AJ14">
+        <v>0.02</v>
+      </c>
+      <c r="AK14">
+        <v>-0.2</v>
+      </c>
+      <c r="AL14">
+        <v>0.2</v>
       </c>
       <c r="AM14">
         <v>6.2</v>
@@ -2080,7 +2236,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2092,7 +2248,7 @@
         <v>-170</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>823177</v>
@@ -2151,17 +2307,23 @@
       <c r="Y15">
         <v>0.9313</v>
       </c>
+      <c r="Z15">
+        <v>7</v>
+      </c>
       <c r="AA15" t="s">
         <v>44</v>
       </c>
+      <c r="AB15">
+        <v>-0.48</v>
+      </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD15">
         <v>3.8</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>0.1567</v>
@@ -2171,6 +2333,18 @@
       </c>
       <c r="AH15">
         <v>0.22</v>
+      </c>
+      <c r="AI15">
+        <v>3.2</v>
+      </c>
+      <c r="AJ15">
+        <v>3.2</v>
+      </c>
+      <c r="AK15">
+        <v>2.98</v>
+      </c>
+      <c r="AL15">
+        <v>2.98</v>
       </c>
       <c r="AM15">
         <v>4.02</v>
@@ -2181,7 +2355,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2193,13 +2367,13 @@
         <v>-104</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G16">
         <v>823176</v>
       </c>
       <c r="H16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I16">
         <v>4.4</v>
@@ -2252,17 +2426,23 @@
       <c r="Y16">
         <v>1.0677</v>
       </c>
+      <c r="Z16">
+        <v>2</v>
+      </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB16">
+        <v>0.66</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD16">
         <v>3.94</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.1666</v>
@@ -2272,6 +2452,18 @@
       </c>
       <c r="AH16">
         <v>0.22</v>
+      </c>
+      <c r="AI16">
+        <v>-1.94</v>
+      </c>
+      <c r="AJ16">
+        <v>1.94</v>
+      </c>
+      <c r="AK16">
+        <v>-2.16</v>
+      </c>
+      <c r="AL16">
+        <v>2.16</v>
       </c>
       <c r="AM16">
         <v>4.16</v>
@@ -2282,7 +2474,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2294,7 +2486,7 @@
         <v>-150</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>822690</v>
@@ -2353,17 +2545,23 @@
       <c r="Y17">
         <v>0.9921</v>
       </c>
+      <c r="Z17">
+        <v>3</v>
+      </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB17">
+        <v>0.4</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD17">
         <v>4.68</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.1663</v>
@@ -2373,6 +2571,18 @@
       </c>
       <c r="AH17">
         <v>0.22</v>
+      </c>
+      <c r="AI17">
+        <v>-1.68</v>
+      </c>
+      <c r="AJ17">
+        <v>1.68</v>
+      </c>
+      <c r="AK17">
+        <v>-1.9</v>
+      </c>
+      <c r="AL17">
+        <v>1.9</v>
       </c>
       <c r="AM17">
         <v>4.9</v>
@@ -2383,7 +2593,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>6.5</v>
@@ -2395,7 +2605,7 @@
         <v>-128</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G18">
         <v>822690</v>
@@ -2454,17 +2664,23 @@
       <c r="Y18">
         <v>0.9439</v>
       </c>
+      <c r="Z18">
+        <v>8</v>
+      </c>
       <c r="AA18" t="s">
         <v>44</v>
       </c>
+      <c r="AB18">
+        <v>-0.82</v>
+      </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="AD18">
         <v>6.23</v>
       </c>
       <c r="AE18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AF18">
         <v>0.3163</v>
@@ -2474,6 +2690,18 @@
       </c>
       <c r="AH18">
         <v>-0.55</v>
+      </c>
+      <c r="AI18">
+        <v>1.77</v>
+      </c>
+      <c r="AJ18">
+        <v>1.77</v>
+      </c>
+      <c r="AK18">
+        <v>2.32</v>
+      </c>
+      <c r="AL18">
+        <v>2.32</v>
       </c>
       <c r="AM18">
         <v>5.68</v>
@@ -2484,7 +2712,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C19">
         <v>2.5</v>
@@ -2496,13 +2724,13 @@
         <v>-107</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G19">
         <v>824392</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I19">
         <v>3</v>
@@ -2555,17 +2783,23 @@
       <c r="Y19">
         <v>0.88</v>
       </c>
+      <c r="Z19">
+        <v>3</v>
+      </c>
       <c r="AA19" t="s">
         <v>44</v>
       </c>
+      <c r="AB19">
+        <v>-0.55</v>
+      </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD19">
         <v>1.73</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.179</v>
@@ -2575,6 +2809,18 @@
       </c>
       <c r="AH19">
         <v>0.22</v>
+      </c>
+      <c r="AI19">
+        <v>1.27</v>
+      </c>
+      <c r="AJ19">
+        <v>1.27</v>
+      </c>
+      <c r="AK19">
+        <v>1.05</v>
+      </c>
+      <c r="AL19">
+        <v>1.05</v>
       </c>
       <c r="AM19">
         <v>1.95</v>
@@ -2585,7 +2831,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20">
         <v>5.5</v>
@@ -2597,7 +2843,7 @@
         <v>-108</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G20">
         <v>824392</v>
@@ -2656,17 +2902,23 @@
       <c r="Y20">
         <v>1.0087</v>
       </c>
+      <c r="Z20">
+        <v>4</v>
+      </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB20">
+        <v>-0.4</v>
       </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD20">
         <v>4.88</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.2194</v>
@@ -2676,6 +2928,18 @@
       </c>
       <c r="AH20">
         <v>0.22</v>
+      </c>
+      <c r="AI20">
+        <v>-0.88</v>
+      </c>
+      <c r="AJ20">
+        <v>0.88</v>
+      </c>
+      <c r="AK20">
+        <v>-1.1</v>
+      </c>
+      <c r="AL20">
+        <v>1.1</v>
       </c>
       <c r="AM20">
         <v>5.1</v>
@@ -2686,16 +2950,16 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G21">
         <v>823582</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -2749,16 +3013,16 @@
         <v>0.9768</v>
       </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD21">
         <v>1.14</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>0.2203</v>
@@ -2778,7 +3042,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2790,7 +3054,7 @@
         <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G22">
         <v>823582</v>
@@ -2849,17 +3113,23 @@
       <c r="Y22">
         <v>0.9509</v>
       </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB22">
+        <v>-0.2</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD22">
         <v>5.08</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.2404</v>
@@ -2869,6 +3139,18 @@
       </c>
       <c r="AH22">
         <v>0.22</v>
+      </c>
+      <c r="AI22">
+        <v>-1.08</v>
+      </c>
+      <c r="AJ22">
+        <v>1.08</v>
+      </c>
+      <c r="AK22">
+        <v>-1.3</v>
+      </c>
+      <c r="AL22">
+        <v>1.3</v>
       </c>
       <c r="AM22">
         <v>5.3</v>
@@ -2879,7 +3161,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C23">
         <v>3.5</v>
@@ -2891,7 +3173,7 @@
         <v>-122</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G23">
         <v>822936</v>
@@ -2950,17 +3232,23 @@
       <c r="Y23">
         <v>0.88</v>
       </c>
+      <c r="Z23">
+        <v>3</v>
+      </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB23">
+        <v>-0.85</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD23">
         <v>2.43</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF23">
         <v>0.1931</v>
@@ -2970,6 +3258,18 @@
       </c>
       <c r="AH23">
         <v>0.22</v>
+      </c>
+      <c r="AI23">
+        <v>0.57</v>
+      </c>
+      <c r="AJ23">
+        <v>0.57</v>
+      </c>
+      <c r="AK23">
+        <v>0.35</v>
+      </c>
+      <c r="AL23">
+        <v>0.35</v>
       </c>
       <c r="AM23">
         <v>2.65</v>
@@ -2980,7 +3280,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -2992,7 +3292,7 @@
         <v>-111</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G24">
         <v>822936</v>
@@ -3051,17 +3351,23 @@
       <c r="Y24">
         <v>1.0075</v>
       </c>
+      <c r="Z24">
+        <v>4</v>
+      </c>
       <c r="AA24" t="s">
         <v>44</v>
       </c>
+      <c r="AB24">
+        <v>0.06</v>
+      </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD24">
         <v>3.34</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>0.1603</v>
@@ -3071,6 +3377,18 @@
       </c>
       <c r="AH24">
         <v>0.22</v>
+      </c>
+      <c r="AI24">
+        <v>0.66</v>
+      </c>
+      <c r="AJ24">
+        <v>0.66</v>
+      </c>
+      <c r="AK24">
+        <v>0.44</v>
+      </c>
+      <c r="AL24">
+        <v>0.44</v>
       </c>
       <c r="AM24">
         <v>3.56</v>
@@ -3081,16 +3399,16 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G25">
         <v>824874</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I25">
         <v>3</v>
@@ -3144,16 +3462,16 @@
         <v>0.988</v>
       </c>
       <c r="AA25" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD25">
         <v>2.04</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF25">
         <v>0.1484</v>
@@ -3173,7 +3491,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3185,7 +3503,7 @@
         <v>-107</v>
       </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G26">
         <v>824874</v>
@@ -3244,17 +3562,23 @@
       <c r="Y26">
         <v>1.0258</v>
       </c>
+      <c r="Z26">
+        <v>6</v>
+      </c>
       <c r="AA26" t="s">
         <v>44</v>
       </c>
+      <c r="AB26">
+        <v>-0.19</v>
+      </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD26">
         <v>4.09</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF26">
         <v>0.1743</v>
@@ -3264,6 +3588,18 @@
       </c>
       <c r="AH26">
         <v>0.22</v>
+      </c>
+      <c r="AI26">
+        <v>1.91</v>
+      </c>
+      <c r="AJ26">
+        <v>1.91</v>
+      </c>
+      <c r="AK26">
+        <v>1.69</v>
+      </c>
+      <c r="AL26">
+        <v>1.69</v>
       </c>
       <c r="AM26">
         <v>4.31</v>
@@ -3274,7 +3610,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3286,7 +3622,7 @@
         <v>-170</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G27">
         <v>823741</v>
@@ -3345,17 +3681,23 @@
       <c r="Y27">
         <v>1.0476</v>
       </c>
+      <c r="Z27">
+        <v>8</v>
+      </c>
       <c r="AA27" t="s">
         <v>44</v>
       </c>
+      <c r="AB27">
+        <v>0.39</v>
+      </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD27">
         <v>4.67</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>0.2087</v>
@@ -3365,6 +3707,18 @@
       </c>
       <c r="AH27">
         <v>0.22</v>
+      </c>
+      <c r="AI27">
+        <v>3.33</v>
+      </c>
+      <c r="AJ27">
+        <v>3.33</v>
+      </c>
+      <c r="AK27">
+        <v>3.11</v>
+      </c>
+      <c r="AL27">
+        <v>3.11</v>
       </c>
       <c r="AM27">
         <v>4.89</v>
@@ -3375,7 +3729,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -3387,7 +3741,7 @@
         <v>-113</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G28">
         <v>823741</v>
@@ -3446,17 +3800,23 @@
       <c r="Y28">
         <v>1.0739</v>
       </c>
+      <c r="Z28">
+        <v>6</v>
+      </c>
       <c r="AA28" t="s">
         <v>44</v>
       </c>
+      <c r="AB28">
+        <v>0.51</v>
+      </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD28">
         <v>5.79</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF28">
         <v>0.2356</v>
@@ -3466,6 +3826,18 @@
       </c>
       <c r="AH28">
         <v>0.22</v>
+      </c>
+      <c r="AI28">
+        <v>0.21</v>
+      </c>
+      <c r="AJ28">
+        <v>0.21</v>
+      </c>
+      <c r="AK28">
+        <v>-0.01</v>
+      </c>
+      <c r="AL28">
+        <v>0.01</v>
       </c>
       <c r="AM28">
         <v>6.01</v>
@@ -3476,10 +3848,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G29">
         <v>824961</v>
@@ -3539,16 +3911,16 @@
         <v>1.0603</v>
       </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD29">
         <v>5.44</v>
       </c>
       <c r="AE29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF29">
         <v>0.219</v>
@@ -3568,10 +3940,10 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G30">
         <v>824961</v>
@@ -3631,16 +4003,16 @@
         <v>1.0306</v>
       </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD30">
         <v>6.09</v>
       </c>
       <c r="AE30" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AF30">
         <v>0.2327</v>
@@ -3660,7 +4032,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C31">
         <v>7.5</v>
@@ -3672,7 +4044,7 @@
         <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G31">
         <v>823986</v>
@@ -3731,17 +4103,23 @@
       <c r="Y31">
         <v>1.12</v>
       </c>
+      <c r="Z31">
+        <v>8</v>
+      </c>
       <c r="AA31" t="s">
         <v>44</v>
       </c>
+      <c r="AB31">
+        <v>3.4</v>
+      </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD31">
         <v>10.9</v>
       </c>
       <c r="AE31" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AF31">
         <v>0.2859</v>
@@ -3751,6 +4129,18 @@
       </c>
       <c r="AH31">
         <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>-2.9</v>
+      </c>
+      <c r="AJ31">
+        <v>2.9</v>
+      </c>
+      <c r="AK31">
+        <v>-2.9</v>
+      </c>
+      <c r="AL31">
+        <v>2.9</v>
       </c>
       <c r="AM31">
         <v>10.9</v>
@@ -3761,7 +4151,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -3773,7 +4163,7 @@
         <v>-130</v>
       </c>
       <c r="F32" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G32">
         <v>823986</v>
@@ -3832,17 +4222,23 @@
       <c r="Y32">
         <v>0.9957</v>
       </c>
+      <c r="Z32">
+        <v>2</v>
+      </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB32">
+        <v>-0.96</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD32">
         <v>2.32</v>
       </c>
       <c r="AE32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF32">
         <v>0.1631</v>
@@ -3852,6 +4248,18 @@
       </c>
       <c r="AH32">
         <v>0.22</v>
+      </c>
+      <c r="AI32">
+        <v>-0.32</v>
+      </c>
+      <c r="AJ32">
+        <v>0.32</v>
+      </c>
+      <c r="AK32">
+        <v>-0.54</v>
+      </c>
+      <c r="AL32">
+        <v>0.54</v>
       </c>
       <c r="AM32">
         <v>2.54</v>
@@ -3862,7 +4270,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C33">
         <v>3.5</v>
@@ -3874,31 +4282,31 @@
         <v>-155</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G33" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L33">
         <v>6</v>
       </c>
       <c r="S33" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="V33" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AA33" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC33" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AE33" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
@@ -3906,10 +4314,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F34" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G34">
         <v>824874</v>
@@ -3948,7 +4356,7 @@
         <v>0.39</v>
       </c>
       <c r="S34" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T34">
         <v>0.225</v>
@@ -3969,16 +4377,16 @@
         <v>0.9749</v>
       </c>
       <c r="AA34" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC34" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD34">
         <v>3.21</v>
       </c>
       <c r="AE34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF34">
         <v>0.1467</v>
